--- a/data/finAlign/File1/RPT_RPT9853920998378DH_finAlign.xlsx
+++ b/data/finAlign/File1/RPT_RPT9853920998378DH_finAlign.xlsx
@@ -2135,13 +2135,13 @@
         <v>33351.27945285301</v>
       </c>
       <c r="X5" t="n">
-        <v>27926.38310350292</v>
+        <v>27926.38310350291</v>
       </c>
       <c r="Z5" t="n">
         <v>14597.04676423593</v>
       </c>
       <c r="AA5" t="n">
-        <v>27926.38310350292</v>
+        <v>27926.38310350291</v>
       </c>
       <c r="AB5" t="n">
         <v>0.5226973614927229</v>
@@ -2225,13 +2225,13 @@
         <v>35514.81254130832</v>
       </c>
       <c r="BG5" t="n">
-        <v>19170.8951547612</v>
+        <v>19170.89515476119</v>
       </c>
       <c r="BH5" t="n">
         <v>35514.81254130832</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BK5" t="n">
         <v>17934.9803333607</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>19170.8951547612</v>
+        <v>19170.89515476119</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BY5" t="n">
         <v>0</v>
@@ -2306,22 +2306,22 @@
         <v>12.81477889749592</v>
       </c>
       <c r="CK5" t="n">
-        <v>51416.82715089616</v>
+        <v>51416.82715089614</v>
       </c>
       <c r="CL5" t="n">
-        <v>43053.40114499516</v>
+        <v>43053.40114499515</v>
       </c>
       <c r="CN5" t="n">
         <v>23959.3792062096</v>
       </c>
       <c r="CO5" t="n">
-        <v>43053.40114499516</v>
+        <v>43053.40114499515</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358658</v>
       </c>
       <c r="CR5" t="n">
-        <v>21741.96757822256</v>
+        <v>21741.96757822255</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358658</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -2486,13 +2486,13 @@
         <v>63258.72524856364</v>
       </c>
       <c r="FB5" t="n">
-        <v>37079.61776080814</v>
+        <v>37079.61776080815</v>
       </c>
       <c r="FC5" t="n">
         <v>63258.72524856364</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FF5" t="n">
         <v>31945.65625052464</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>37079.61776080814</v>
+        <v>37079.61776080815</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FT5" t="n">
         <v>0</v>
@@ -2619,13 +2619,13 @@
         <v>10.59422858589279</v>
       </c>
       <c r="W6" t="n">
-        <v>13896.36643868876</v>
+        <v>13896.36643868875</v>
       </c>
       <c r="X6" t="n">
         <v>11635.99295979288</v>
       </c>
       <c r="Z6" t="n">
-        <v>6082.102818431639</v>
+        <v>6082.102818431638</v>
       </c>
       <c r="AA6" t="n">
         <v>11635.99295979288</v>
@@ -2634,7 +2634,7 @@
         <v>0.5226973614927229</v>
       </c>
       <c r="AD6" t="n">
-        <v>5876.176444695406</v>
+        <v>5876.176444695405</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>6082.102818431639</v>
+        <v>6082.102818431638</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -2706,22 +2706,22 @@
         <v>13.34872801822492</v>
       </c>
       <c r="BD6" t="n">
-        <v>17672.42278551476</v>
+        <v>17672.42278551477</v>
       </c>
       <c r="BE6" t="n">
-        <v>14797.83855887846</v>
+        <v>14797.83855887847</v>
       </c>
       <c r="BG6" t="n">
-        <v>7987.872981150499</v>
+        <v>7987.872981150498</v>
       </c>
       <c r="BH6" t="n">
-        <v>14797.83855887846</v>
+        <v>14797.83855887847</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.5397999815559485</v>
+        <v>0.5397999815559484</v>
       </c>
       <c r="BK6" t="n">
-        <v>7472.908472233625</v>
+        <v>7472.908472233626</v>
       </c>
       <c r="BL6" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>7987.872981150499</v>
+        <v>7987.872981150498</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.5397999815559485</v>
+        <v>0.5397999815559484</v>
       </c>
       <c r="BY6" t="n">
         <v>0</v>
@@ -2793,22 +2793,22 @@
         <v>16.0184736218699</v>
       </c>
       <c r="CK6" t="n">
-        <v>21423.67797954007</v>
+        <v>21423.67797954006</v>
       </c>
       <c r="CL6" t="n">
-        <v>17938.91714374799</v>
+        <v>17938.91714374798</v>
       </c>
       <c r="CN6" t="n">
         <v>9983.074669254001</v>
       </c>
       <c r="CO6" t="n">
-        <v>17938.91714374799</v>
+        <v>17938.91714374798</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.556503750435866</v>
       </c>
       <c r="CR6" t="n">
-        <v>9059.153157592733</v>
+        <v>9059.153157592729</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.556503750435866</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>26357.80218690152</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FF6" t="n">
         <v>13310.69010438527</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FT6" t="n">
         <v>0</v>
@@ -3106,22 +3106,22 @@
         <v>4.237691434357116</v>
       </c>
       <c r="W7" t="n">
-        <v>16675.63972642651</v>
+        <v>16675.6397264265</v>
       </c>
       <c r="X7" t="n">
-        <v>13963.19155175146</v>
+        <v>13963.19155175145</v>
       </c>
       <c r="Z7" t="n">
-        <v>7298.523382117966</v>
+        <v>7298.523382117965</v>
       </c>
       <c r="AA7" t="n">
-        <v>13963.19155175146</v>
+        <v>13963.19155175145</v>
       </c>
       <c r="AB7" t="n">
         <v>0.5226973614927229</v>
       </c>
       <c r="AD7" t="n">
-        <v>7051.411733634486</v>
+        <v>7051.411733634484</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>7298.523382117966</v>
+        <v>7298.523382117965</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -3199,13 +3199,13 @@
         <v>17757.40627065416</v>
       </c>
       <c r="BG7" t="n">
-        <v>9585.447577380599</v>
+        <v>9585.447577380595</v>
       </c>
       <c r="BH7" t="n">
         <v>17757.40627065416</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BK7" t="n">
         <v>8967.490166680349</v>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>9585.447577380599</v>
+        <v>9585.447577380595</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BY7" t="n">
         <v>0</v>
@@ -3292,10 +3292,10 @@
         <v>21526.70057249758</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358658</v>
       </c>
       <c r="CR7" t="n">
-        <v>10870.98378911128</v>
+        <v>10870.98378911127</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358658</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>31629.36262428182</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FF7" t="n">
         <v>15972.82812526232</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FT7" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>6.528034379806908</v>
       </c>
       <c r="W8" t="n">
-        <v>25688.31429226057</v>
+        <v>25688.31429226056</v>
       </c>
       <c r="X8" t="n">
         <v>21509.87062499306</v>
@@ -3686,13 +3686,13 @@
         <v>27183.63949919382</v>
       </c>
       <c r="BG8" t="n">
-        <v>14673.72810028838</v>
+        <v>14673.72810028837</v>
       </c>
       <c r="BH8" t="n">
         <v>27183.63949919382</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BK8" t="n">
         <v>13727.73794709288</v>
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>14673.72810028838</v>
+        <v>14673.72810028837</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.5397999815559484</v>
+        <v>0.5397999815559483</v>
       </c>
       <c r="BY8" t="n">
         <v>0</v>
@@ -3767,22 +3767,22 @@
         <v>9.769136018696708</v>
       </c>
       <c r="CK8" t="n">
-        <v>39196.77289048462</v>
+        <v>39196.7728904846</v>
       </c>
       <c r="CL8" t="n">
-        <v>32821.05256885524</v>
+        <v>32821.05256885523</v>
       </c>
       <c r="CN8" t="n">
-        <v>18265.03884782064</v>
+        <v>18265.03884782065</v>
       </c>
       <c r="CO8" t="n">
-        <v>32821.05256885524</v>
+        <v>32821.05256885523</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.5565037504358658</v>
+        <v>0.556503750435866</v>
       </c>
       <c r="CR8" t="n">
-        <v>16574.6315472719</v>
+        <v>16574.63154727189</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="DA8" t="n">
-        <v>18265.03884782064</v>
+        <v>18265.03884782065</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.5565037504358658</v>
+        <v>0.556503750435866</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>47755.26054432151</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FF8" t="n">
         <v>24116.40657488236</v>
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FT8" t="n">
         <v>0</v>
@@ -4080,16 +4080,16 @@
         <v>4.237691434357116</v>
       </c>
       <c r="W9" t="n">
-        <v>5558.546575475503</v>
+        <v>5558.546575475502</v>
       </c>
       <c r="X9" t="n">
-        <v>4654.397183917153</v>
+        <v>4654.397183917152</v>
       </c>
       <c r="Z9" t="n">
-        <v>2432.841127372656</v>
+        <v>2432.841127372655</v>
       </c>
       <c r="AA9" t="n">
-        <v>4654.397183917153</v>
+        <v>4654.397183917152</v>
       </c>
       <c r="AB9" t="n">
         <v>0.5226973614927229</v>
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2432.841127372656</v>
+        <v>2432.841127372655</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -4167,19 +4167,19 @@
         <v>5.339491207289967</v>
       </c>
       <c r="BD9" t="n">
-        <v>7068.969114205906</v>
+        <v>7068.969114205907</v>
       </c>
       <c r="BE9" t="n">
-        <v>5919.135423551385</v>
+        <v>5919.135423551386</v>
       </c>
       <c r="BG9" t="n">
-        <v>3195.1491924602</v>
+        <v>3195.149192460199</v>
       </c>
       <c r="BH9" t="n">
-        <v>5919.135423551385</v>
+        <v>5919.135423551386</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.5397999815559485</v>
+        <v>0.5397999815559484</v>
       </c>
       <c r="BK9" t="n">
         <v>2989.16338889345</v>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>3195.1491924602</v>
+        <v>3195.149192460199</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.5397999815559485</v>
+        <v>0.5397999815559484</v>
       </c>
       <c r="BY9" t="n">
         <v>0</v>
@@ -4254,22 +4254,22 @@
         <v>6.40738944874796</v>
       </c>
       <c r="CK9" t="n">
-        <v>8569.471191816026</v>
+        <v>8569.471191816023</v>
       </c>
       <c r="CL9" t="n">
-        <v>7175.566857499193</v>
+        <v>7175.566857499191</v>
       </c>
       <c r="CN9" t="n">
         <v>3993.2298677016</v>
       </c>
       <c r="CO9" t="n">
-        <v>7175.566857499193</v>
+        <v>7175.566857499191</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358659</v>
       </c>
       <c r="CR9" t="n">
-        <v>3623.661263037093</v>
+        <v>3623.661263037091</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.5565037504358656</v>
+        <v>0.5565037504358659</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4434,13 +4434,13 @@
         <v>10543.12087476061</v>
       </c>
       <c r="FB9" t="n">
-        <v>6179.936293468025</v>
+        <v>6179.936293468026</v>
       </c>
       <c r="FC9" t="n">
         <v>10543.12087476061</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FF9" t="n">
         <v>5324.276041754108</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>6179.936293468025</v>
+        <v>6179.936293468026</v>
       </c>
       <c r="FP9" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.5861581562876984</v>
+        <v>0.5861581562876985</v>
       </c>
       <c r="FT9" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1503.362517453784</v>
+        <v>1503.362517453783</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>1927.507993302661</v>
+        <v>1927.507993302662</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>2372.951796047239</v>
+        <v>2372.951796047238</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>2891.261989953992</v>
+        <v>2891.261989953993</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="CO11" t="n">
-        <v>3559.427694070859</v>
+        <v>3559.427694070858</v>
       </c>
       <c r="CP11" t="n">
         <v>0</v>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>751.6812587268918</v>
+        <v>751.6812587268915</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>963.7539966513307</v>
+        <v>963.7539966513308</v>
       </c>
       <c r="BI12" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>501.1208391512612</v>
+        <v>501.1208391512611</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>642.5026644342206</v>
+        <v>642.5026644342207</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="CO13" t="n">
-        <v>790.9839320157461</v>
+        <v>790.9839320157458</v>
       </c>
       <c r="CP13" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>904.4716459403661</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01047271686151331</v>
+        <v>0.01047271686151339</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>4.530047594084101</v>
       </c>
       <c r="W14" t="n">
-        <v>4478.087317105273</v>
+        <v>4478.087317105272</v>
       </c>
       <c r="X14" t="n">
-        <v>902.0294802080758</v>
+        <v>902.0294802080757</v>
       </c>
       <c r="Z14" t="n">
-        <v>84.02764086417271</v>
+        <v>84.0276408641727</v>
       </c>
       <c r="AA14" t="n">
-        <v>902.0294802080758</v>
+        <v>902.0294802080757</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.09315398521652488</v>
+        <v>0.09315398521652486</v>
       </c>
       <c r="AD14" t="n">
-        <v>81.18265321872683</v>
+        <v>81.18265321872681</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>84.02764086417271</v>
+        <v>84.0276408641727</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.09315398521652488</v>
+        <v>0.09315398521652486</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
         <v>863.4267226475923</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.009963173775170324</v>
+        <v>0.009963173775170395</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         <v>860.5142178094807</v>
       </c>
       <c r="BG14" t="n">
-        <v>82.78316891326142</v>
+        <v>82.78316891326141</v>
       </c>
       <c r="BH14" t="n">
         <v>860.5142178094807</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.09620197691096111</v>
+        <v>0.09620197691096109</v>
       </c>
       <c r="BK14" t="n">
         <v>77.44627960285325</v>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>82.78316891326142</v>
+        <v>82.78316891326141</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.09620197691096111</v>
+        <v>0.09620197691096109</v>
       </c>
       <c r="BY14" t="n">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>824.123538232674</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.009478466783165988</v>
+        <v>0.009478466783166059</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -6689,22 +6689,22 @@
         <v>4.127687889806563</v>
       </c>
       <c r="CK14" t="n">
-        <v>4078.455604942696</v>
+        <v>4078.455604942694</v>
       </c>
       <c r="CL14" t="n">
-        <v>821.530919088081</v>
+        <v>821.5309190880805</v>
       </c>
       <c r="CN14" t="n">
         <v>81.47852154740329</v>
       </c>
       <c r="CO14" t="n">
-        <v>821.530919088081</v>
+        <v>821.5309190880805</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.09917888621629288</v>
+        <v>0.09917888621629294</v>
       </c>
       <c r="CR14" t="n">
-        <v>73.93778271792728</v>
+        <v>73.93778271792725</v>
       </c>
       <c r="CS14" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.09917888621629288</v>
+        <v>0.09917888621629294</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -6767,16 +6767,16 @@
         <v>785.6452102325906</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.008984120934631287</v>
+        <v>0.008984120934631358</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>3.935017938465924</v>
+        <v>3.935017938465923</v>
       </c>
       <c r="DR14" t="n">
-        <v>3888.66954405675</v>
+        <v>3888.669544056749</v>
       </c>
       <c r="DS14" t="n">
         <v>783.3019588805004</v>
@@ -6854,7 +6854,7 @@
         <v>748.9634353668308</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.008619120836680792</v>
+        <v>0.008619120836680859</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
@@ -6863,22 +6863,22 @@
         <v>3.751237482410462</v>
       </c>
       <c r="EY14" t="n">
-        <v>3707.422130191662</v>
+        <v>3707.422130191661</v>
       </c>
       <c r="EZ14" t="n">
-        <v>746.7929542674626</v>
+        <v>746.7929542674624</v>
       </c>
       <c r="FB14" t="n">
-        <v>78.01285209541652</v>
+        <v>78.01285209541651</v>
       </c>
       <c r="FC14" t="n">
-        <v>746.7929542674626</v>
+        <v>746.7929542674624</v>
       </c>
       <c r="FD14" t="n">
         <v>0.1044638298334512</v>
       </c>
       <c r="FF14" t="n">
-        <v>67.21136588407164</v>
+        <v>67.21136588407161</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>78.01285209541652</v>
+        <v>78.01285209541651</v>
       </c>
       <c r="FP14" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>851.3393862612265</v>
+        <v>851.3393862612263</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -8072,7 +8072,7 @@
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>296.6323901455492</v>
+        <v>296.632390145549</v>
       </c>
       <c r="BI17" t="n">
         <v>0</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="CO17" t="n">
-        <v>282.6136787537133</v>
+        <v>282.6136787537131</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -8246,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>266.6439376526817</v>
+        <v>266.6439376526816</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="FC17" t="n">
-        <v>251.2326487368789</v>
+        <v>251.2326487368788</v>
       </c>
       <c r="FD17" t="n">
         <v>0</v>
@@ -8463,7 +8463,7 @@
         <v>5.237607148392015</v>
       </c>
       <c r="W18" t="n">
-        <v>3303.504142879882</v>
+        <v>3303.504142879881</v>
       </c>
       <c r="X18" t="n">
         <v>2831.365952935264</v>
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0096954604144071</v>
+        <v>0.009695460414407102</v>
       </c>
       <c r="AV18" t="n">
         <v>3.502253215359765</v>
@@ -8550,7 +8550,7 @@
         <v>0.7543314617697956</v>
       </c>
       <c r="BD18" t="n">
-        <v>500.4503144277086</v>
+        <v>500.4503144277087</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -8962,10 +8962,10 @@
         <v>1741.650060051594</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5908038480959104</v>
+        <v>0.5908038480959105</v>
       </c>
       <c r="AD19" t="n">
-        <v>977.824700074986</v>
+        <v>977.8247000749859</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>16.8816946800873</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5811109166240237</v>
+        <v>0.5811109166240238</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.009692931471886608</v>
+        <v>0.00969293147188661</v>
       </c>
       <c r="AV19" t="n">
         <v>2.155232747913702</v>
@@ -9446,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>3940.181631695473</v>
+        <v>3940.181631695472</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="CO20" t="n">
-        <v>4000.688151897628</v>
+        <v>4000.688151897627</v>
       </c>
       <c r="CP20" t="n">
         <v>0</v>
@@ -9933,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3171.150246904993</v>
+        <v>3171.150246904992</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="CO21" t="n">
-        <v>3199.402600190578</v>
+        <v>3199.402600190577</v>
       </c>
       <c r="CP21" t="n">
         <v>0</v>
@@ -10411,7 +10411,7 @@
         <v>0.9981113886434008</v>
       </c>
       <c r="W22" t="n">
-        <v>2348.949587688861</v>
+        <v>2348.94958768886</v>
       </c>
       <c r="X22" t="n">
         <v>1957.457989740717</v>
@@ -10498,7 +10498,7 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="BD22" t="n">
-        <v>2371.618649759655</v>
+        <v>2371.618649759656</v>
       </c>
       <c r="BE22" t="n">
         <v>1976.348874799713</v>
@@ -10585,16 +10585,16 @@
         <v>0.9904994042258208</v>
       </c>
       <c r="CK22" t="n">
-        <v>2395.963136659473</v>
+        <v>2395.963136659472</v>
       </c>
       <c r="CL22" t="n">
-        <v>1996.635947216228</v>
+        <v>1996.635947216227</v>
       </c>
       <c r="CN22" t="n">
         <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>1996.635947216228</v>
+        <v>1996.635947216227</v>
       </c>
       <c r="CP22" t="n">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4024.80156753867</v>
+        <v>4024.801567538669</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>3832.547637235593</v>
+        <v>3832.547637235594</v>
       </c>
       <c r="BI23" t="n">
         <v>0</v>
@@ -11081,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="CO23" t="n">
-        <v>3655.894208151388</v>
+        <v>3655.894208151387</v>
       </c>
       <c r="CP23" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         <v>845.5385323864263</v>
       </c>
       <c r="T24" t="n">
-        <v>0.004189086744605323</v>
+        <v>0.004189086744605356</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -11385,22 +11385,22 @@
         <v>1.81201903763364</v>
       </c>
       <c r="W24" t="n">
-        <v>986.674476478006</v>
+        <v>986.6744764780059</v>
       </c>
       <c r="X24" t="n">
-        <v>843.2554920740035</v>
+        <v>843.2554920740034</v>
       </c>
       <c r="Z24" t="n">
-        <v>567.3244029729983</v>
+        <v>567.3244029729982</v>
       </c>
       <c r="AA24" t="n">
-        <v>843.2554920740035</v>
+        <v>843.2554920740034</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.6727787821193465</v>
+        <v>0.6727787821193464</v>
       </c>
       <c r="AD24" t="n">
-        <v>548.1160698481024</v>
+        <v>548.1160698481023</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>567.3244029729983</v>
+        <v>567.3244029729982</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
@@ -11436,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.6727787821193465</v>
+        <v>0.6727787821193464</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -11463,7 +11463,7 @@
         <v>838.6766035921892</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.00398526951006813</v>
+        <v>0.003985269510068158</v>
       </c>
       <c r="BB24" t="n">
         <v>0</v>
@@ -11472,22 +11472,22 @@
         <v>1.729803330183893</v>
       </c>
       <c r="BD24" t="n">
-        <v>978.0066501390913</v>
+        <v>978.0066501390914</v>
       </c>
       <c r="BE24" t="n">
-        <v>835.8475856784473</v>
+        <v>835.8475856784474</v>
       </c>
       <c r="BG24" t="n">
         <v>580.7402621115376</v>
       </c>
       <c r="BH24" t="n">
-        <v>835.8475856784473</v>
+        <v>835.8475856784474</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.6947920554680526</v>
+        <v>0.6947920554680524</v>
       </c>
       <c r="BK24" t="n">
-        <v>543.3009306909908</v>
+        <v>543.3009306909909</v>
       </c>
       <c r="BL24" t="n">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>0.6947920554680526</v>
+        <v>0.6947920554680524</v>
       </c>
       <c r="BY24" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
         <v>828.0212361299064</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.003791386713266395</v>
+        <v>0.003791386713266425</v>
       </c>
       <c r="CI24" t="n">
         <v>0</v>
@@ -11559,22 +11559,22 @@
         <v>1.651075155922625</v>
       </c>
       <c r="CK24" t="n">
-        <v>965.8012995752633</v>
+        <v>965.801299575263</v>
       </c>
       <c r="CL24" t="n">
-        <v>825.416355175379</v>
+        <v>825.4163551753786</v>
       </c>
       <c r="CN24" t="n">
         <v>591.2390955683774</v>
       </c>
       <c r="CO24" t="n">
-        <v>825.416355175379</v>
+        <v>825.4163551753786</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.7162919560065597</v>
+        <v>0.7162919560065599</v>
       </c>
       <c r="CR24" t="n">
-        <v>536.5206308639963</v>
+        <v>536.5206308639961</v>
       </c>
       <c r="CS24" t="n">
         <v>0</v>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.7162919560065597</v>
+        <v>0.7162919560065599</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -11637,7 +11637,7 @@
         <v>811.0794010948582</v>
       </c>
       <c r="DO24" t="n">
-        <v>0.003593648373852515</v>
+        <v>0.003593648373852544</v>
       </c>
       <c r="DP24" t="n">
         <v>0</v>
@@ -11724,7 +11724,7 @@
         <v>794.4842066552812</v>
       </c>
       <c r="EV24" t="n">
-        <v>0.003447648334672317</v>
+        <v>0.003447648334672344</v>
       </c>
       <c r="EW24" t="n">
         <v>0</v>
@@ -11739,13 +11739,13 @@
         <v>792.1818072685243</v>
       </c>
       <c r="FB24" t="n">
-        <v>597.6702731397303</v>
+        <v>597.6702731397304</v>
       </c>
       <c r="FC24" t="n">
         <v>792.1818072685243</v>
       </c>
       <c r="FD24" t="n">
-        <v>0.7544609932415921</v>
+        <v>0.7544609932415922</v>
       </c>
       <c r="FF24" t="n">
         <v>514.9181747245408</v>
@@ -11772,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="FO24" t="n">
-        <v>597.6702731397303</v>
+        <v>597.6702731397304</v>
       </c>
       <c r="FP24" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="FS24" t="n">
-        <v>0.7544609932415921</v>
+        <v>0.7544609932415922</v>
       </c>
       <c r="FT24" t="n">
         <v>0</v>
@@ -11881,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1070.115538583474</v>
+        <v>1070.115538583473</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -12055,7 +12055,7 @@
         <v>0</v>
       </c>
       <c r="CO25" t="n">
-        <v>1075.986172607015</v>
+        <v>1075.986172607014</v>
       </c>
       <c r="CP25" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>1.064062481716026</v>
       </c>
       <c r="W26" t="n">
-        <v>5133.874242024368</v>
+        <v>5133.874242024367</v>
       </c>
       <c r="X26" t="n">
-        <v>4339.617199912076</v>
+        <v>4339.617199912075</v>
       </c>
       <c r="Z26" t="n">
-        <v>1617.010545943947</v>
+        <v>1617.010545943946</v>
       </c>
       <c r="AA26" t="n">
-        <v>4339.617199912076</v>
+        <v>4339.617199912075</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.3726159408660996</v>
+        <v>0.3726159408660995</v>
       </c>
       <c r="AD26" t="n">
-        <v>1562.262191968348</v>
+        <v>1562.262191968347</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -12398,7 +12398,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1617.010545943947</v>
+        <v>1617.010545943946</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -12410,7 +12410,7 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.3726159408660996</v>
+        <v>0.3726159408660995</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -12446,22 +12446,22 @@
         <v>1.097378278018554</v>
       </c>
       <c r="BD26" t="n">
-        <v>5449.788698926401</v>
+        <v>5449.788698926402</v>
       </c>
       <c r="BE26" t="n">
-        <v>4606.656816825707</v>
+        <v>4606.656816825708</v>
       </c>
       <c r="BG26" t="n">
         <v>1772.677970915953</v>
       </c>
       <c r="BH26" t="n">
-        <v>4606.656816825707</v>
+        <v>4606.656816825708</v>
       </c>
       <c r="BI26" t="n">
         <v>0.3848079076438444</v>
       </c>
       <c r="BK26" t="n">
-        <v>1658.396454057254</v>
+        <v>1658.396454057255</v>
       </c>
       <c r="BL26" t="n">
         <v>0</v>
@@ -12533,22 +12533,22 @@
         <v>1.130442285535253</v>
       </c>
       <c r="CK26" t="n">
-        <v>5783.747316955467</v>
+        <v>5783.747316955465</v>
       </c>
       <c r="CL26" t="n">
-        <v>4888.948999013313</v>
+        <v>4888.948999013312</v>
       </c>
       <c r="CN26" t="n">
         <v>1939.522065961602</v>
       </c>
       <c r="CO26" t="n">
-        <v>4888.948999013313</v>
+        <v>4888.948999013312</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.3967155448651715</v>
+        <v>0.3967155448651717</v>
       </c>
       <c r="CR26" t="n">
-        <v>1760.021639644793</v>
+        <v>1760.021639644792</v>
       </c>
       <c r="CS26" t="n">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>0</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.3967155448651715</v>
+        <v>0.3967155448651717</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -12713,13 +12713,13 @@
         <v>5481.094671808413</v>
       </c>
       <c r="FB26" t="n">
-        <v>2290.30456438732</v>
+        <v>2290.304564387321</v>
       </c>
       <c r="FC26" t="n">
         <v>5481.094671808413</v>
       </c>
       <c r="FD26" t="n">
-        <v>0.4178553193338047</v>
+        <v>0.4178553193338048</v>
       </c>
       <c r="FF26" t="n">
         <v>1973.194081851029</v>
@@ -12746,7 +12746,7 @@
         <v>0</v>
       </c>
       <c r="FO26" t="n">
-        <v>2290.30456438732</v>
+        <v>2290.304564387321</v>
       </c>
       <c r="FP26" t="n">
         <v>0</v>
@@ -12758,7 +12758,7 @@
         <v>0</v>
       </c>
       <c r="FS26" t="n">
-        <v>0.4178553193338047</v>
+        <v>0.4178553193338048</v>
       </c>
       <c r="FT26" t="n">
         <v>0</v>
@@ -12846,22 +12846,22 @@
         <v>4.931725028513852</v>
       </c>
       <c r="W27" t="n">
-        <v>2854.487689098793</v>
+        <v>2854.487689098792</v>
       </c>
       <c r="X27" t="n">
-        <v>2421.534212808207</v>
+        <v>2421.534212808206</v>
       </c>
       <c r="Z27" t="n">
-        <v>926.1130028392221</v>
+        <v>926.1130028392217</v>
       </c>
       <c r="AA27" t="n">
-        <v>2421.534212808207</v>
+        <v>2421.534212808206</v>
       </c>
       <c r="AB27" t="n">
         <v>0.3824488615278438</v>
       </c>
       <c r="AD27" t="n">
-        <v>894.7568916326323</v>
+        <v>894.756891632632</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>926.1130028392221</v>
+        <v>926.1130028392217</v>
       </c>
       <c r="AN27" t="n">
         <v>0</v>
@@ -12933,7 +12933,7 @@
         <v>5.413110708547088</v>
       </c>
       <c r="BD27" t="n">
-        <v>3241.097471758819</v>
+        <v>3241.09747175882</v>
       </c>
       <c r="BE27" t="n">
         <v>2749.50508453166</v>
@@ -12945,7 +12945,7 @@
         <v>2749.50508453166</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.3949625607622237</v>
+        <v>0.3949625607622236</v>
       </c>
       <c r="BK27" t="n">
         <v>1015.942128734448</v>
@@ -12984,7 +12984,7 @@
         <v>0</v>
       </c>
       <c r="BX27" t="n">
-        <v>0.3949625607622237</v>
+        <v>0.3949625607622236</v>
       </c>
       <c r="BY27" t="n">
         <v>0</v>
@@ -13020,22 +13020,22 @@
         <v>5.90072372117301</v>
       </c>
       <c r="CK27" t="n">
-        <v>3653.649213254592</v>
+        <v>3653.649213254591</v>
       </c>
       <c r="CL27" t="n">
-        <v>3099.483177063222</v>
+        <v>3099.483177063221</v>
       </c>
       <c r="CN27" t="n">
         <v>1262.061282375725</v>
       </c>
       <c r="CO27" t="n">
-        <v>3099.483177063222</v>
+        <v>3099.483177063221</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.4071844272991135</v>
+        <v>0.4071844272991137</v>
       </c>
       <c r="CR27" t="n">
-        <v>1145.259033924861</v>
+        <v>1145.25903392486</v>
       </c>
       <c r="CS27" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>0</v>
       </c>
       <c r="DE27" t="n">
-        <v>0.4071844272991135</v>
+        <v>0.4071844272991137</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13206,7 +13206,7 @@
         <v>3868.572834902751</v>
       </c>
       <c r="FD27" t="n">
-        <v>0.4288820569273358</v>
+        <v>0.4288820569273359</v>
       </c>
       <c r="FF27" t="n">
         <v>1429.437662496567</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="FS27" t="n">
-        <v>0.4288820569273358</v>
+        <v>0.4288820569273359</v>
       </c>
       <c r="FT27" t="n">
         <v>0</v>
@@ -13333,16 +13333,16 @@
         <v>0.0714425083209866</v>
       </c>
       <c r="W28" t="n">
-        <v>57.68379292977682</v>
+        <v>57.68379292977681</v>
       </c>
       <c r="X28" t="n">
-        <v>48.0698274414807</v>
+        <v>48.06982744148068</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>48.0698274414807</v>
+        <v>48.06982744148068</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -13507,7 +13507,7 @@
         <v>0.01484365688036909</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.09531780175379</v>
+        <v>13.09531780175378</v>
       </c>
       <c r="CL28" t="n">
         <v>10.91276483479482</v>
@@ -13820,7 +13820,7 @@
         <v>0.9981113886434008</v>
       </c>
       <c r="W29" t="n">
-        <v>379.6890995669585</v>
+        <v>379.6890995669584</v>
       </c>
       <c r="X29" t="n">
         <v>316.4075829724654</v>
@@ -13910,13 +13910,13 @@
         <v>387.5675035892824</v>
       </c>
       <c r="BE29" t="n">
-        <v>322.9729196577353</v>
+        <v>322.9729196577354</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>322.9729196577353</v>
+        <v>322.9729196577354</v>
       </c>
       <c r="BI29" t="n">
         <v>0</v>
@@ -13994,16 +13994,16 @@
         <v>0.9904994042258208</v>
       </c>
       <c r="CK29" t="n">
-        <v>394.632161632877</v>
+        <v>394.6321616328769</v>
       </c>
       <c r="CL29" t="n">
-        <v>328.8601346940642</v>
+        <v>328.8601346940641</v>
       </c>
       <c r="CN29" t="n">
         <v>0</v>
       </c>
       <c r="CO29" t="n">
-        <v>328.8601346940642</v>
+        <v>328.8601346940641</v>
       </c>
       <c r="CP29" t="n">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>169602.966241225</v>
+        <v>169602.9662412249</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         <v>0</v>
       </c>
       <c r="CO30" t="n">
-        <v>115106.9731355889</v>
+        <v>115106.9731355888</v>
       </c>
       <c r="CP30" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="FC30" t="n">
-        <v>133525.1395656342</v>
+        <v>133525.1395656341</v>
       </c>
       <c r="FD30" t="n">
         <v>0</v>
@@ -14797,13 +14797,13 @@
         <v>404.9699914878825</v>
       </c>
       <c r="X31" t="n">
-        <v>337.4749929065688</v>
+        <v>337.4749929065687</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>337.4749929065688</v>
+        <v>337.4749929065687</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -14881,16 +14881,16 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="BD31" t="n">
-        <v>423.725589396146</v>
+        <v>423.7255893961461</v>
       </c>
       <c r="BE31" t="n">
-        <v>353.1046578301217</v>
+        <v>353.1046578301218</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>353.1046578301217</v>
+        <v>353.1046578301218</v>
       </c>
       <c r="BI31" t="n">
         <v>0</v>
@@ -14968,16 +14968,16 @@
         <v>0.9904994042258208</v>
       </c>
       <c r="CK31" t="n">
-        <v>442.8694717102466</v>
+        <v>442.8694717102464</v>
       </c>
       <c r="CL31" t="n">
-        <v>369.0578930918721</v>
+        <v>369.057893091872</v>
       </c>
       <c r="CN31" t="n">
         <v>0</v>
       </c>
       <c r="CO31" t="n">
-        <v>369.0578930918721</v>
+        <v>369.057893091872</v>
       </c>
       <c r="CP31" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>5073.98963060231</v>
+        <v>5073.989630602309</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -15377,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>5527.292942890055</v>
+        <v>5527.292942890056</v>
       </c>
       <c r="BI32" t="n">
         <v>0</v>
@@ -15464,7 +15464,7 @@
         <v>0</v>
       </c>
       <c r="CO32" t="n">
-        <v>5995.637336485222</v>
+        <v>5995.63733648522</v>
       </c>
       <c r="CP32" t="n">
         <v>0</v>
@@ -15768,13 +15768,13 @@
         <v>1.996222777286802</v>
       </c>
       <c r="W33" t="n">
-        <v>3703.164840447765</v>
+        <v>3703.164840447764</v>
       </c>
       <c r="X33" t="n">
         <v>3127.446052155705</v>
       </c>
       <c r="Z33" t="n">
-        <v>809.2612869666435</v>
+        <v>809.2612869666434</v>
       </c>
       <c r="AA33" t="n">
         <v>3127.446052155705</v>
@@ -15783,7 +15783,7 @@
         <v>0.2587610700459024</v>
       </c>
       <c r="AD33" t="n">
-        <v>781.8615130389263</v>
+        <v>781.8615130389262</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>809.2612869666435</v>
+        <v>809.2612869666434</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
@@ -15861,16 +15861,16 @@
         <v>3192.339365092542</v>
       </c>
       <c r="BG33" t="n">
-        <v>853.081549701625</v>
+        <v>853.0815497016249</v>
       </c>
       <c r="BH33" t="n">
         <v>3192.339365092542</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.2672277136415587</v>
+        <v>0.2672277136415586</v>
       </c>
       <c r="BK33" t="n">
-        <v>798.0848412731355</v>
+        <v>798.0848412731356</v>
       </c>
       <c r="BL33" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
         <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>853.081549701625</v>
+        <v>853.0815497016249</v>
       </c>
       <c r="BU33" t="n">
         <v>0</v>
@@ -15906,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="BX33" t="n">
-        <v>0.2672277136415587</v>
+        <v>0.2672277136415586</v>
       </c>
       <c r="BY33" t="n">
         <v>0</v>
@@ -15942,22 +15942,22 @@
         <v>1.980998808451642</v>
       </c>
       <c r="CK33" t="n">
-        <v>3848.906770132474</v>
+        <v>3848.906770132473</v>
       </c>
       <c r="CL33" t="n">
-        <v>3250.529966122356</v>
+        <v>3250.529966122355</v>
       </c>
       <c r="CN33" t="n">
-        <v>895.5109490352763</v>
+        <v>895.5109490352764</v>
       </c>
       <c r="CO33" t="n">
-        <v>3250.529966122356</v>
+        <v>3250.529966122355</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.2754969061563691</v>
+        <v>0.2754969061563692</v>
       </c>
       <c r="CR33" t="n">
-        <v>812.6324915305889</v>
+        <v>812.6324915305887</v>
       </c>
       <c r="CS33" t="n">
         <v>0</v>
@@ -15981,7 +15981,7 @@
         <v>0</v>
       </c>
       <c r="DA33" t="n">
-        <v>895.5109490352763</v>
+        <v>895.5109490352764</v>
       </c>
       <c r="DB33" t="n">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.2754969061563691</v>
+        <v>0.2754969061563692</v>
       </c>
       <c r="DF33" t="n">
         <v>0</v>
@@ -16122,13 +16122,13 @@
         <v>3338.272619409124</v>
       </c>
       <c r="FB33" t="n">
-        <v>968.6909523656225</v>
+        <v>968.6909523656227</v>
       </c>
       <c r="FC33" t="n">
         <v>3338.272619409124</v>
       </c>
       <c r="FD33" t="n">
-        <v>0.29017730509292</v>
+        <v>0.2901773050929201</v>
       </c>
       <c r="FF33" t="n">
         <v>834.5681548522809</v>
@@ -16155,7 +16155,7 @@
         <v>0</v>
       </c>
       <c r="FO33" t="n">
-        <v>968.6909523656225</v>
+        <v>968.6909523656227</v>
       </c>
       <c r="FP33" t="n">
         <v>0</v>
@@ -16167,7 +16167,7 @@
         <v>0</v>
       </c>
       <c r="FS33" t="n">
-        <v>0.29017730509292</v>
+        <v>0.2901773050929201</v>
       </c>
       <c r="FT33" t="n">
         <v>0</v>
@@ -16264,7 +16264,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>619.06001967216</v>
+        <v>619.0600196721599</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -16351,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>652.3759313174745</v>
+        <v>652.3759313174746</v>
       </c>
       <c r="BI34" t="n">
         <v>0</v>
@@ -16438,7 +16438,7 @@
         <v>0</v>
       </c>
       <c r="CO34" t="n">
-        <v>684.9404559320016</v>
+        <v>684.9404559320013</v>
       </c>
       <c r="CP34" t="n">
         <v>0</v>
@@ -17412,7 +17412,7 @@
         <v>0</v>
       </c>
       <c r="CO36" t="n">
-        <v>1097.053330209619</v>
+        <v>1097.053330209618</v>
       </c>
       <c r="CP36" t="n">
         <v>0</v>
@@ -17725,7 +17725,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>655.4118387480228</v>
+        <v>655.4118387480227</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -17899,7 +17899,7 @@
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>679.15217920339</v>
+        <v>679.1521792033898</v>
       </c>
       <c r="CP37" t="n">
         <v>0</v>
@@ -18212,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2622.622241557956</v>
+        <v>2622.622241557955</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -18386,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="CO38" t="n">
-        <v>2717.536175492132</v>
+        <v>2717.536175492131</v>
       </c>
       <c r="CP38" t="n">
         <v>0</v>
@@ -18873,7 +18873,7 @@
         <v>0</v>
       </c>
       <c r="CO39" t="n">
-        <v>2037.813750397149</v>
+        <v>2037.813750397148</v>
       </c>
       <c r="CP39" t="n">
         <v>0</v>
@@ -19186,7 +19186,7 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>319.3016625577396</v>
+        <v>319.3016625577395</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -19273,7 +19273,7 @@
         <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>325.7223464271788</v>
+        <v>325.7223464271789</v>
       </c>
       <c r="BI40" t="n">
         <v>0</v>
@@ -19360,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="CO40" t="n">
-        <v>330.8784321794282</v>
+        <v>330.878432179428</v>
       </c>
       <c r="CP40" t="n">
         <v>0</v>
@@ -19847,7 +19847,7 @@
         <v>0</v>
       </c>
       <c r="CO41" t="n">
-        <v>156.7350443115288</v>
+        <v>156.7350443115287</v>
       </c>
       <c r="CP41" t="n">
         <v>0</v>
@@ -20160,7 +20160,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>605.3222080845247</v>
+        <v>605.3222080845246</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -20247,7 +20247,7 @@
         <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>617.4802613318567</v>
+        <v>617.4802613318568</v>
       </c>
       <c r="BI42" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
         <v>0</v>
       </c>
       <c r="CO42" t="n">
-        <v>627.2422363788296</v>
+        <v>627.2422363788294</v>
       </c>
       <c r="CP42" t="n">
         <v>0</v>
@@ -20647,7 +20647,7 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>393.3471376909883</v>
+        <v>393.3471376909882</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
         <v>0</v>
       </c>
       <c r="BH43" t="n">
-        <v>401.2518103897</v>
+        <v>401.2518103897001</v>
       </c>
       <c r="BI43" t="n">
         <v>0</v>
@@ -20821,7 +20821,7 @@
         <v>0</v>
       </c>
       <c r="CO43" t="n">
-        <v>407.5992328589784</v>
+        <v>407.5992328589783</v>
       </c>
       <c r="CP43" t="n">
         <v>0</v>
@@ -21308,7 +21308,7 @@
         <v>0</v>
       </c>
       <c r="CO44" t="n">
-        <v>1796.815531277529</v>
+        <v>1796.815531277528</v>
       </c>
       <c r="CP44" t="n">
         <v>0</v>
@@ -23073,22 +23073,22 @@
         <v>2.553963433397899</v>
       </c>
       <c r="W48" t="n">
-        <v>2329.264628551853</v>
+        <v>2329.264628551852</v>
       </c>
       <c r="X48" t="n">
         <v>1977.995860083196</v>
       </c>
       <c r="Z48" t="n">
-        <v>1187.441714699464</v>
+        <v>1187.441714699463</v>
       </c>
       <c r="AA48" t="n">
         <v>1977.995860083196</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.6003256825064935</v>
+        <v>0.6003256825064934</v>
       </c>
       <c r="AD48" t="n">
-        <v>1147.237598848254</v>
+        <v>1147.237598848253</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -23112,7 +23112,7 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1187.441714699464</v>
+        <v>1187.441714699463</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
@@ -23124,7 +23124,7 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.6003256825064935</v>
+        <v>0.6003256825064934</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -23172,7 +23172,7 @@
         <v>1946.786295209895</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.619968295648416</v>
+        <v>0.6199682956484159</v>
       </c>
       <c r="BK48" t="n">
         <v>1129.136051221739</v>
@@ -23211,7 +23211,7 @@
         <v>0</v>
       </c>
       <c r="BX48" t="n">
-        <v>0.619968295648416</v>
+        <v>0.6199682956484159</v>
       </c>
       <c r="BY48" t="n">
         <v>0</v>
@@ -23253,13 +23253,13 @@
         <v>1935.910589403095</v>
       </c>
       <c r="CN48" t="n">
-        <v>1237.342716904101</v>
+        <v>1237.342716904102</v>
       </c>
       <c r="CO48" t="n">
         <v>1935.910589403095</v>
       </c>
       <c r="CP48" t="n">
-        <v>0.6391528222827763</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="CR48" t="n">
         <v>1122.828141853795</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="DA48" t="n">
-        <v>1237.342716904101</v>
+        <v>1237.342716904102</v>
       </c>
       <c r="DB48" t="n">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>0</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.6391528222827763</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="DF48" t="n">
         <v>0</v>
@@ -23560,22 +23560,22 @@
         <v>3.632416248756491</v>
       </c>
       <c r="W49" t="n">
-        <v>7634.940315337027</v>
+        <v>7634.940315337025</v>
       </c>
       <c r="X49" t="n">
-        <v>1399.815925726608</v>
+        <v>1399.815925726607</v>
       </c>
       <c r="Z49" t="n">
-        <v>507.1050135316376</v>
+        <v>507.1050135316374</v>
       </c>
       <c r="AA49" t="n">
-        <v>1399.815925726608</v>
+        <v>1399.815925726607</v>
       </c>
       <c r="AB49" t="n">
         <v>0.3622654980642634</v>
       </c>
       <c r="AD49" t="n">
-        <v>489.9355740043127</v>
+        <v>489.9355740043126</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -23599,7 +23599,7 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>507.1050135316376</v>
+        <v>507.1050135316374</v>
       </c>
       <c r="AN49" t="n">
         <v>0</v>
@@ -23659,10 +23659,10 @@
         <v>1335.379808821523</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.3741187990981822</v>
+        <v>0.3741187990981821</v>
       </c>
       <c r="BK49" t="n">
-        <v>467.382933087533</v>
+        <v>467.3829330875331</v>
       </c>
       <c r="BL49" t="n">
         <v>0</v>
@@ -23698,7 +23698,7 @@
         <v>0</v>
       </c>
       <c r="BX49" t="n">
-        <v>0.3741187990981822</v>
+        <v>0.3741187990981821</v>
       </c>
       <c r="BY49" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         <v>3.309733085271783</v>
       </c>
       <c r="CK49" t="n">
-        <v>6953.478295838579</v>
+        <v>6953.478295838577</v>
       </c>
       <c r="CL49" t="n">
         <v>1274.87436125157</v>
@@ -23746,10 +23746,10 @@
         <v>1274.87436125157</v>
       </c>
       <c r="CP49" t="n">
-        <v>0.3856956686189168</v>
+        <v>0.3856956686189169</v>
       </c>
       <c r="CR49" t="n">
-        <v>446.2060264380497</v>
+        <v>446.2060264380495</v>
       </c>
       <c r="CS49" t="n">
         <v>0</v>
@@ -23785,7 +23785,7 @@
         <v>0</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.3856956686189168</v>
+        <v>0.3856956686189169</v>
       </c>
       <c r="DF49" t="n">
         <v>0</v>
@@ -23914,13 +23914,13 @@
         <v>1158.8954967446</v>
       </c>
       <c r="FB49" t="n">
-        <v>470.7992409815363</v>
+        <v>470.7992409815364</v>
       </c>
       <c r="FC49" t="n">
         <v>1158.8954967446</v>
       </c>
       <c r="FD49" t="n">
-        <v>0.406248227130088</v>
+        <v>0.4062482271300881</v>
       </c>
       <c r="FF49" t="n">
         <v>405.6134238606099</v>
@@ -23947,7 +23947,7 @@
         <v>0</v>
       </c>
       <c r="FO49" t="n">
-        <v>470.7992409815363</v>
+        <v>470.7992409815364</v>
       </c>
       <c r="FP49" t="n">
         <v>0</v>
@@ -23959,7 +23959,7 @@
         <v>0</v>
       </c>
       <c r="FS49" t="n">
-        <v>0.406248227130088</v>
+        <v>0.4062482271300881</v>
       </c>
       <c r="FT49" t="n">
         <v>0</v>
@@ -24056,7 +24056,7 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>62.56619627665982</v>
+        <v>62.56619627665981</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
@@ -24230,7 +24230,7 @@
         <v>0</v>
       </c>
       <c r="CO50" t="n">
-        <v>67.64591025786717</v>
+        <v>67.64591025786716</v>
       </c>
       <c r="CP50" t="n">
         <v>0</v>
@@ -24543,7 +24543,7 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>20.85539875888661</v>
+        <v>20.8553987588866</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
@@ -24717,7 +24717,7 @@
         <v>0</v>
       </c>
       <c r="CO51" t="n">
-        <v>22.54863675262239</v>
+        <v>22.54863675262238</v>
       </c>
       <c r="CP51" t="n">
         <v>0</v>
@@ -25021,13 +25021,13 @@
         <v>4.896868646499627</v>
       </c>
       <c r="W52" t="n">
-        <v>12102.48456707236</v>
+        <v>12102.48456707235</v>
       </c>
       <c r="X52" t="n">
         <v>10209.08532157877</v>
       </c>
       <c r="Z52" t="n">
-        <v>5177.759130323213</v>
+        <v>5177.759130323212</v>
       </c>
       <c r="AA52" t="n">
         <v>10209.08532157877</v>
@@ -25036,7 +25036,7 @@
         <v>0.5071716972899687</v>
       </c>
       <c r="AD52" t="n">
-        <v>5002.451807573599</v>
+        <v>5002.451807573598</v>
       </c>
       <c r="AE52" t="n">
         <v>0</v>
@@ -25060,7 +25060,7 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>5177.759130323213</v>
+        <v>5177.759130323212</v>
       </c>
       <c r="AN52" t="n">
         <v>0</v>
@@ -25120,10 +25120,10 @@
         <v>10045.00161911344</v>
       </c>
       <c r="BI52" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BK52" t="n">
-        <v>4922.050793365584</v>
+        <v>4922.050793365585</v>
       </c>
       <c r="BL52" t="n">
         <v>0</v>
@@ -25159,7 +25159,7 @@
         <v>0</v>
       </c>
       <c r="BX52" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BY52" t="n">
         <v>0</v>
@@ -25195,22 +25195,22 @@
         <v>4.512954144614056</v>
       </c>
       <c r="CK52" t="n">
-        <v>11727.1720236714</v>
+        <v>11727.17202367139</v>
       </c>
       <c r="CL52" t="n">
-        <v>9892.489356791184</v>
+        <v>9892.48935679118</v>
       </c>
       <c r="CN52" t="n">
         <v>5341.686415482332</v>
       </c>
       <c r="CO52" t="n">
-        <v>9892.489356791184</v>
+        <v>9892.48935679118</v>
       </c>
       <c r="CP52" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="CR52" t="n">
-        <v>4847.31978482768</v>
+        <v>4847.319784827679</v>
       </c>
       <c r="CS52" t="n">
         <v>0</v>
@@ -25246,7 +25246,7 @@
         <v>0</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="DF52" t="n">
         <v>0</v>
@@ -25381,7 +25381,7 @@
         <v>9414.858410042913</v>
       </c>
       <c r="FD52" t="n">
-        <v>0.5687475179821232</v>
+        <v>0.5687475179821233</v>
       </c>
       <c r="FF52" t="n">
         <v>4613.280620921028</v>
@@ -25420,7 +25420,7 @@
         <v>0</v>
       </c>
       <c r="FS52" t="n">
-        <v>0.5687475179821232</v>
+        <v>0.5687475179821233</v>
       </c>
       <c r="FT52" t="n">
         <v>0</v>
@@ -25508,22 +25508,22 @@
         <v>2.110969997609437</v>
       </c>
       <c r="W53" t="n">
-        <v>7825.811859140788</v>
+        <v>7825.811859140787</v>
       </c>
       <c r="X53" t="n">
-        <v>6601.485879846746</v>
+        <v>6601.485879846744</v>
       </c>
       <c r="Z53" t="n">
-        <v>3348.086798317637</v>
+        <v>3348.086798317636</v>
       </c>
       <c r="AA53" t="n">
-        <v>6601.485879846746</v>
+        <v>6601.485879846744</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.5071716972899687</v>
+        <v>0.5071716972899688</v>
       </c>
       <c r="AD53" t="n">
-        <v>3234.728081124905</v>
+        <v>3234.728081124904</v>
       </c>
       <c r="AE53" t="n">
         <v>0</v>
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>3348.086798317637</v>
+        <v>3348.086798317636</v>
       </c>
       <c r="AN53" t="n">
         <v>0</v>
@@ -25559,7 +25559,7 @@
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.5071716972899687</v>
+        <v>0.5071716972899688</v>
       </c>
       <c r="AR53" t="n">
         <v>0</v>
@@ -25598,19 +25598,19 @@
         <v>7700.032894209347</v>
       </c>
       <c r="BE53" t="n">
-        <v>6495.384675789967</v>
+        <v>6495.384675789968</v>
       </c>
       <c r="BG53" t="n">
         <v>3402.063720422188</v>
       </c>
       <c r="BH53" t="n">
-        <v>6495.384675789967</v>
+        <v>6495.384675789968</v>
       </c>
       <c r="BI53" t="n">
-        <v>0.5237663187374548</v>
+        <v>0.5237663187374547</v>
       </c>
       <c r="BK53" t="n">
-        <v>3182.738491137083</v>
+        <v>3182.738491137084</v>
       </c>
       <c r="BL53" t="n">
         <v>0</v>
@@ -25646,7 +25646,7 @@
         <v>0</v>
       </c>
       <c r="BX53" t="n">
-        <v>0.5237663187374548</v>
+        <v>0.5237663187374547</v>
       </c>
       <c r="BY53" t="n">
         <v>0</v>
@@ -25682,22 +25682,22 @@
         <v>1.945469949796857</v>
       </c>
       <c r="CK53" t="n">
-        <v>7583.124059230455</v>
+        <v>7583.124059230452</v>
       </c>
       <c r="CL53" t="n">
-        <v>6396.765895114701</v>
+        <v>6396.7658951147</v>
       </c>
       <c r="CN53" t="n">
         <v>3454.086858480928</v>
       </c>
       <c r="CO53" t="n">
-        <v>6396.765895114701</v>
+        <v>6396.7658951147</v>
       </c>
       <c r="CP53" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="CR53" t="n">
-        <v>3134.415288606204</v>
+        <v>3134.415288606203</v>
       </c>
       <c r="CS53" t="n">
         <v>0</v>
@@ -25733,7 +25733,7 @@
         <v>0</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="DF53" t="n">
         <v>0</v>
@@ -25862,13 +25862,13 @@
         <v>5927.693696807593</v>
       </c>
       <c r="FB53" t="n">
-        <v>3371.361077417595</v>
+        <v>3371.361077417596</v>
       </c>
       <c r="FC53" t="n">
         <v>5927.693696807593</v>
       </c>
       <c r="FD53" t="n">
-        <v>0.5687475179821233</v>
+        <v>0.5687475179821234</v>
       </c>
       <c r="FF53" t="n">
         <v>2904.569911435721</v>
@@ -25895,7 +25895,7 @@
         <v>0</v>
       </c>
       <c r="FO53" t="n">
-        <v>3371.361077417595</v>
+        <v>3371.361077417596</v>
       </c>
       <c r="FP53" t="n">
         <v>0</v>
@@ -25907,7 +25907,7 @@
         <v>0</v>
       </c>
       <c r="FS53" t="n">
-        <v>0.5687475179821233</v>
+        <v>0.5687475179821234</v>
       </c>
       <c r="FT53" t="n">
         <v>0</v>
@@ -25995,22 +25995,22 @@
         <v>0.2238584692226681</v>
       </c>
       <c r="W54" t="n">
-        <v>837.0157895110051</v>
+        <v>837.0157895110049</v>
       </c>
       <c r="X54" t="n">
-        <v>706.0670528657887</v>
+        <v>706.0670528657885</v>
       </c>
       <c r="Z54" t="n">
-        <v>358.0972256024681</v>
+        <v>358.097225602468</v>
       </c>
       <c r="AA54" t="n">
-        <v>706.0670528657887</v>
+        <v>706.0670528657885</v>
       </c>
       <c r="AB54" t="n">
         <v>0.5071716972899687</v>
       </c>
       <c r="AD54" t="n">
-        <v>345.9728559042364</v>
+        <v>345.9728559042363</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -26034,7 +26034,7 @@
         <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>358.0972256024681</v>
+        <v>358.097225602468</v>
       </c>
       <c r="AN54" t="n">
         <v>0</v>
@@ -26085,16 +26085,16 @@
         <v>823.5630025630289</v>
       </c>
       <c r="BE54" t="n">
-        <v>694.7189161254553</v>
+        <v>694.7189161254554</v>
       </c>
       <c r="BG54" t="n">
-        <v>363.8703692563045</v>
+        <v>363.8703692563044</v>
       </c>
       <c r="BH54" t="n">
-        <v>694.7189161254553</v>
+        <v>694.7189161254554</v>
       </c>
       <c r="BI54" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BK54" t="n">
         <v>340.4122689014731</v>
@@ -26121,7 +26121,7 @@
         <v>0</v>
       </c>
       <c r="BT54" t="n">
-        <v>363.8703692563045</v>
+        <v>363.8703692563044</v>
       </c>
       <c r="BU54" t="n">
         <v>0</v>
@@ -26133,7 +26133,7 @@
         <v>0</v>
       </c>
       <c r="BX54" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BY54" t="n">
         <v>0</v>
@@ -26169,22 +26169,22 @@
         <v>0.2063079652356109</v>
       </c>
       <c r="CK54" t="n">
-        <v>811.058927257874</v>
+        <v>811.0589272578737</v>
       </c>
       <c r="CL54" t="n">
-        <v>684.1710677931313</v>
+        <v>684.1710677931311</v>
       </c>
       <c r="CN54" t="n">
         <v>369.4345444190661</v>
       </c>
       <c r="CO54" t="n">
-        <v>684.1710677931313</v>
+        <v>684.1710677931311</v>
       </c>
       <c r="CP54" t="n">
-        <v>0.5399739360664836</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="CR54" t="n">
-        <v>335.2438232186344</v>
+        <v>335.2438232186342</v>
       </c>
       <c r="CS54" t="n">
         <v>0</v>
@@ -26220,7 +26220,7 @@
         <v>0</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.5399739360664836</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="DF54" t="n">
         <v>0</v>
@@ -26349,13 +26349,13 @@
         <v>413.4917596897783</v>
       </c>
       <c r="FB54" t="n">
-        <v>235.172412029622</v>
+        <v>235.1724120296221</v>
       </c>
       <c r="FC54" t="n">
         <v>413.4917596897783</v>
       </c>
       <c r="FD54" t="n">
-        <v>0.5687475179821232</v>
+        <v>0.5687475179821234</v>
       </c>
       <c r="FF54" t="n">
         <v>202.6109622479914</v>
@@ -26382,7 +26382,7 @@
         <v>0</v>
       </c>
       <c r="FO54" t="n">
-        <v>235.172412029622</v>
+        <v>235.1724120296221</v>
       </c>
       <c r="FP54" t="n">
         <v>0</v>
@@ -26394,7 +26394,7 @@
         <v>0</v>
       </c>
       <c r="FS54" t="n">
-        <v>0.5687475179821232</v>
+        <v>0.5687475179821234</v>
       </c>
       <c r="FT54" t="n">
         <v>0</v>
@@ -26665,7 +26665,7 @@
         <v>0</v>
       </c>
       <c r="CO55" t="n">
-        <v>1828.821281345313</v>
+        <v>1828.821281345312</v>
       </c>
       <c r="CP55" t="n">
         <v>0</v>
@@ -26969,16 +26969,16 @@
         <v>1.103090034888927</v>
       </c>
       <c r="W56" t="n">
-        <v>706.1071331571625</v>
+        <v>706.1071331571623</v>
       </c>
       <c r="X56" t="n">
-        <v>484.8593484285775</v>
+        <v>484.8593484285774</v>
       </c>
       <c r="Z56" t="n">
-        <v>321.1845729821127</v>
+        <v>321.1845729821126</v>
       </c>
       <c r="AA56" t="n">
-        <v>484.8593484285775</v>
+        <v>484.8593484285774</v>
       </c>
       <c r="AB56" t="n">
         <v>0.6624283393175103</v>
@@ -27008,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>321.1845729821127</v>
+        <v>321.1845729821126</v>
       </c>
       <c r="AN56" t="n">
         <v>0</v>
@@ -27056,7 +27056,7 @@
         <v>1.153920423696608</v>
       </c>
       <c r="BD56" t="n">
-        <v>738.1401758119196</v>
+        <v>738.1401758119197</v>
       </c>
       <c r="BE56" t="n">
         <v>506.8553309933272</v>
@@ -27071,7 +27071,7 @@
         <v>0.6841029469223903</v>
       </c>
       <c r="BK56" t="n">
-        <v>324.3874118357294</v>
+        <v>324.3874118357295</v>
       </c>
       <c r="BL56" t="n">
         <v>0</v>
@@ -27143,7 +27143,7 @@
         <v>0.4900596709711953</v>
       </c>
       <c r="CK56" t="n">
-        <v>313.5506439453736</v>
+        <v>313.5506439453735</v>
       </c>
       <c r="CL56" t="n">
         <v>215.3043834056226</v>
@@ -27155,10 +27155,10 @@
         <v>215.3043834056226</v>
       </c>
       <c r="CP56" t="n">
-        <v>0.4342986656432767</v>
+        <v>0.4342986656432768</v>
       </c>
       <c r="CR56" t="n">
-        <v>84.8525013626987</v>
+        <v>84.85250136269867</v>
       </c>
       <c r="CS56" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>0</v>
       </c>
       <c r="DE56" t="n">
-        <v>0.4342986656432767</v>
+        <v>0.4342986656432768</v>
       </c>
       <c r="DF56" t="n">
         <v>0</v>
@@ -27447,7 +27447,7 @@
         <v>3340.489390610359</v>
       </c>
       <c r="T57" t="n">
-        <v>0.006725964771826922</v>
+        <v>0.006725964771826972</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -27462,7 +27462,7 @@
         <v>3336.027960689637</v>
       </c>
       <c r="Z57" t="n">
-        <v>2278.938195101305</v>
+        <v>2278.938195101304</v>
       </c>
       <c r="AA57" t="n">
         <v>3336.027960689637</v>
@@ -27471,7 +27471,7 @@
         <v>0.6831292249211823</v>
       </c>
       <c r="AD57" t="n">
-        <v>2201.778454055161</v>
+        <v>2201.77845405516</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -27495,7 +27495,7 @@
         <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>2278.938195101305</v>
+        <v>2278.938195101304</v>
       </c>
       <c r="AN57" t="n">
         <v>0</v>
@@ -27534,7 +27534,7 @@
         <v>3494.419141729683</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.007011764178208721</v>
+        <v>0.007011764178208772</v>
       </c>
       <c r="BB57" t="n">
         <v>0</v>
@@ -27543,19 +27543,19 @@
         <v>7.466673899251261</v>
       </c>
       <c r="BD57" t="n">
-        <v>4184.820593101648</v>
+        <v>4184.820593101649</v>
       </c>
       <c r="BE57" t="n">
         <v>3487.380467807774</v>
       </c>
       <c r="BG57" t="n">
-        <v>2460.281231787722</v>
+        <v>2460.281231787721</v>
       </c>
       <c r="BH57" t="n">
         <v>3487.380467807774</v>
       </c>
       <c r="BI57" t="n">
-        <v>0.7054811640137149</v>
+        <v>0.7054811640137146</v>
       </c>
       <c r="BK57" t="n">
         <v>2301.671108753131</v>
@@ -27582,7 +27582,7 @@
         <v>0</v>
       </c>
       <c r="BT57" t="n">
-        <v>2460.281231787722</v>
+        <v>2460.281231787721</v>
       </c>
       <c r="BU57" t="n">
         <v>0</v>
@@ -27594,7 +27594,7 @@
         <v>0</v>
       </c>
       <c r="BX57" t="n">
-        <v>0.7054811640137149</v>
+        <v>0.7054811640137146</v>
       </c>
       <c r="BY57" t="n">
         <v>0</v>
@@ -27621,7 +27621,7 @@
         <v>1903.499914600747</v>
       </c>
       <c r="CH57" t="n">
-        <v>0.002968068773353955</v>
+        <v>0.002968068773353977</v>
       </c>
       <c r="CI57" t="n">
         <v>0</v>
@@ -27630,22 +27630,22 @@
         <v>3.512904594930831</v>
       </c>
       <c r="CK57" t="n">
-        <v>2280.296498882032</v>
+        <v>2280.296498882031</v>
       </c>
       <c r="CL57" t="n">
         <v>1900.263414904891</v>
       </c>
       <c r="CN57" t="n">
-        <v>851.0719237596783</v>
+        <v>851.0719237596784</v>
       </c>
       <c r="CO57" t="n">
         <v>1900.263414904891</v>
       </c>
       <c r="CP57" t="n">
-        <v>0.447870498944629</v>
+        <v>0.4478704989446293</v>
       </c>
       <c r="CR57" t="n">
-        <v>772.3062444089834</v>
+        <v>772.3062444089832</v>
       </c>
       <c r="CS57" t="n">
         <v>0</v>
@@ -27669,7 +27669,7 @@
         <v>0</v>
       </c>
       <c r="DA57" t="n">
-        <v>851.0719237596783</v>
+        <v>851.0719237596784</v>
       </c>
       <c r="DB57" t="n">
         <v>0</v>
@@ -27681,7 +27681,7 @@
         <v>0</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.447870498944629</v>
+        <v>0.4478704989446293</v>
       </c>
       <c r="DF57" t="n">
         <v>0</v>
@@ -27943,22 +27943,22 @@
         <v>2.627892174416866</v>
       </c>
       <c r="W58" t="n">
-        <v>2034.423559062402</v>
+        <v>2034.423559062401</v>
       </c>
       <c r="X58" t="n">
         <v>1705.259232279679</v>
       </c>
       <c r="Z58" t="n">
-        <v>935.459971738729</v>
+        <v>935.4599717387288</v>
       </c>
       <c r="AA58" t="n">
         <v>1705.259232279679</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.5485734684973131</v>
+        <v>0.5485734684973133</v>
       </c>
       <c r="AD58" t="n">
-        <v>903.7873931082299</v>
+        <v>903.7873931082297</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -27982,7 +27982,7 @@
         <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>935.459971738729</v>
+        <v>935.4599717387288</v>
       </c>
       <c r="AN58" t="n">
         <v>0</v>
@@ -27994,7 +27994,7 @@
         <v>0</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.5485734684973131</v>
+        <v>0.5485734684973133</v>
       </c>
       <c r="AR58" t="n">
         <v>0</v>
@@ -28030,22 +28030,22 @@
         <v>2.386520278196677</v>
       </c>
       <c r="BD58" t="n">
-        <v>1895.018493719377</v>
+        <v>1895.018493719378</v>
       </c>
       <c r="BE58" t="n">
         <v>1588.409536136609</v>
       </c>
       <c r="BG58" t="n">
-        <v>899.8701431766581</v>
+        <v>899.870143176658</v>
       </c>
       <c r="BH58" t="n">
         <v>1588.409536136609</v>
       </c>
       <c r="BI58" t="n">
-        <v>0.5665227529201046</v>
+        <v>0.5665227529201043</v>
       </c>
       <c r="BK58" t="n">
-        <v>841.8570541524031</v>
+        <v>841.8570541524032</v>
       </c>
       <c r="BL58" t="n">
         <v>0</v>
@@ -28069,7 +28069,7 @@
         <v>0</v>
       </c>
       <c r="BT58" t="n">
-        <v>899.8701431766581</v>
+        <v>899.870143176658</v>
       </c>
       <c r="BU58" t="n">
         <v>0</v>
@@ -28081,7 +28081,7 @@
         <v>0</v>
       </c>
       <c r="BX58" t="n">
-        <v>0.5665227529201046</v>
+        <v>0.5665227529201043</v>
       </c>
       <c r="BY58" t="n">
         <v>0</v>
@@ -28117,22 +28117,22 @@
         <v>2.175289368373489</v>
       </c>
       <c r="CK58" t="n">
-        <v>1779.181784350023</v>
+        <v>1779.181784350022</v>
       </c>
       <c r="CL58" t="n">
-        <v>1491.314898587275</v>
+        <v>1491.314898587274</v>
       </c>
       <c r="CN58" t="n">
         <v>871.0075982112706</v>
       </c>
       <c r="CO58" t="n">
-        <v>1491.314898587275</v>
+        <v>1491.314898587274</v>
       </c>
       <c r="CP58" t="n">
-        <v>0.5840534410515026</v>
+        <v>0.5840534410515028</v>
       </c>
       <c r="CR58" t="n">
-        <v>790.3968962512558</v>
+        <v>790.3968962512555</v>
       </c>
       <c r="CS58" t="n">
         <v>0</v>
@@ -28168,7 +28168,7 @@
         <v>0</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.5840534410515026</v>
+        <v>0.5840534410515028</v>
       </c>
       <c r="DF58" t="n">
         <v>0</v>
@@ -28433,13 +28433,13 @@
         <v>1048.06059875957</v>
       </c>
       <c r="X59" t="n">
-        <v>878.4914472978986</v>
+        <v>878.4914472978985</v>
       </c>
       <c r="Z59" t="n">
-        <v>481.9171002894329</v>
+        <v>481.9171002894328</v>
       </c>
       <c r="AA59" t="n">
-        <v>878.4914472978986</v>
+        <v>878.4914472978985</v>
       </c>
       <c r="AB59" t="n">
         <v>0.5485734684973133</v>
@@ -28469,7 +28469,7 @@
         <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>481.9171002894329</v>
+        <v>481.9171002894328</v>
       </c>
       <c r="AN59" t="n">
         <v>0</v>
@@ -28517,19 +28517,19 @@
         <v>0.9207111070284328</v>
       </c>
       <c r="BD59" t="n">
-        <v>976.2565734105744</v>
+        <v>976.2565734105746</v>
       </c>
       <c r="BE59" t="n">
         <v>818.3048300113495</v>
       </c>
       <c r="BG59" t="n">
-        <v>463.5883050258478</v>
+        <v>463.5883050258477</v>
       </c>
       <c r="BH59" t="n">
         <v>818.3048300113495</v>
       </c>
       <c r="BI59" t="n">
-        <v>0.5665227529201043</v>
+        <v>0.5665227529201042</v>
       </c>
       <c r="BK59" t="n">
         <v>433.7015599060152</v>
@@ -28556,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="BT59" t="n">
-        <v>463.5883050258478</v>
+        <v>463.5883050258477</v>
       </c>
       <c r="BU59" t="n">
         <v>0</v>
@@ -28568,7 +28568,7 @@
         <v>0</v>
       </c>
       <c r="BX59" t="n">
-        <v>0.5665227529201043</v>
+        <v>0.5665227529201042</v>
       </c>
       <c r="BY59" t="n">
         <v>0</v>
@@ -28604,22 +28604,22 @@
         <v>0.8392189669453463</v>
       </c>
       <c r="CK59" t="n">
-        <v>916.5943328665625</v>
+        <v>916.5943328665622</v>
       </c>
       <c r="CL59" t="n">
-        <v>768.2955384621989</v>
+        <v>768.2955384621987</v>
       </c>
       <c r="CN59" t="n">
         <v>448.7256529833643</v>
       </c>
       <c r="CO59" t="n">
-        <v>768.2955384621989</v>
+        <v>768.2955384621987</v>
       </c>
       <c r="CP59" t="n">
-        <v>0.5840534410515026</v>
+        <v>0.5840534410515028</v>
       </c>
       <c r="CR59" t="n">
-        <v>407.1966353849655</v>
+        <v>407.1966353849653</v>
       </c>
       <c r="CS59" t="n">
         <v>0</v>
@@ -28655,7 +28655,7 @@
         <v>0</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.5840534410515026</v>
+        <v>0.5840534410515028</v>
       </c>
       <c r="DF59" t="n">
         <v>0</v>
@@ -28917,22 +28917,22 @@
         <v>0.4452704918698726</v>
       </c>
       <c r="W60" t="n">
-        <v>657.4403957072391</v>
+        <v>657.440395707239</v>
       </c>
       <c r="X60" t="n">
-        <v>547.8717053047988</v>
+        <v>547.8717053047986</v>
       </c>
       <c r="Z60" t="n">
         <v>374.2671734011136</v>
       </c>
       <c r="AA60" t="n">
-        <v>547.8717053047988</v>
+        <v>547.8717053047986</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.6831292249211823</v>
+        <v>0.6831292249211824</v>
       </c>
       <c r="AD60" t="n">
-        <v>361.5953255011672</v>
+        <v>361.5953255011671</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -28968,7 +28968,7 @@
         <v>0</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.6831292249211823</v>
+        <v>0.6831292249211824</v>
       </c>
       <c r="AR60" t="n">
         <v>0</v>
@@ -29004,7 +29004,7 @@
         <v>0.4657885561352362</v>
       </c>
       <c r="BD60" t="n">
-        <v>687.265637869129</v>
+        <v>687.2656378691291</v>
       </c>
       <c r="BE60" t="n">
         <v>572.7262873947617</v>
@@ -29016,7 +29016,7 @@
         <v>572.7262873947617</v>
       </c>
       <c r="BI60" t="n">
-        <v>0.705481164013715</v>
+        <v>0.7054811640137149</v>
       </c>
       <c r="BK60" t="n">
         <v>377.9993496805428</v>
@@ -29055,7 +29055,7 @@
         <v>0</v>
       </c>
       <c r="BX60" t="n">
-        <v>0.705481164013715</v>
+        <v>0.7054811640137149</v>
       </c>
       <c r="BY60" t="n">
         <v>0</v>
@@ -29091,19 +29091,19 @@
         <v>0.4872520928019479</v>
       </c>
       <c r="CK60" t="n">
-        <v>719.0933599280079</v>
+        <v>719.0933599280077</v>
       </c>
       <c r="CL60" t="n">
-        <v>599.2496170748717</v>
+        <v>599.2496170748716</v>
       </c>
       <c r="CN60" t="n">
         <v>268.3862249917007</v>
       </c>
       <c r="CO60" t="n">
-        <v>599.2496170748717</v>
+        <v>599.2496170748716</v>
       </c>
       <c r="CP60" t="n">
-        <v>0.447870498944629</v>
+        <v>0.4478704989446292</v>
       </c>
       <c r="CR60" t="n">
         <v>243.5474037949517</v>
@@ -29142,7 +29142,7 @@
         <v>0</v>
       </c>
       <c r="DE60" t="n">
-        <v>0.447870498944629</v>
+        <v>0.4478704989446292</v>
       </c>
       <c r="DF60" t="n">
         <v>0</v>
@@ -29410,7 +29410,7 @@
         <v>16397.31096257364</v>
       </c>
       <c r="Z61" t="n">
-        <v>9334.568607212115</v>
+        <v>9334.568607212113</v>
       </c>
       <c r="AA61" t="n">
         <v>16397.31096257364</v>
@@ -29419,7 +29419,7 @@
         <v>0.5692743541009854</v>
       </c>
       <c r="AD61" t="n">
-        <v>9018.521029415502</v>
+        <v>9018.5210294155</v>
       </c>
       <c r="AE61" t="n">
         <v>0</v>
@@ -29443,7 +29443,7 @@
         <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>9334.568607212115</v>
+        <v>9334.568607212113</v>
       </c>
       <c r="AN61" t="n">
         <v>0</v>
@@ -29506,7 +29506,7 @@
         <v>0.587900970011429</v>
       </c>
       <c r="BK61" t="n">
-        <v>9669.236122967195</v>
+        <v>9669.236122967199</v>
       </c>
       <c r="BL61" t="n">
         <v>0</v>
@@ -29578,22 +29578,22 @@
         <v>8.449651537743833</v>
       </c>
       <c r="CK61" t="n">
-        <v>22364.74206851176</v>
+        <v>22364.74206851175</v>
       </c>
       <c r="CL61" t="n">
-        <v>18865.95189858476</v>
+        <v>18865.95189858475</v>
       </c>
       <c r="CN61" t="n">
         <v>11434.52503546096</v>
       </c>
       <c r="CO61" t="n">
-        <v>18865.95189858476</v>
+        <v>18865.95189858475</v>
       </c>
       <c r="CP61" t="n">
-        <v>0.6060931935440123</v>
+        <v>0.6060931935440124</v>
       </c>
       <c r="CR61" t="n">
-        <v>10376.27354422162</v>
+        <v>10376.27354422161</v>
       </c>
       <c r="CS61" t="n">
         <v>0</v>
@@ -29629,7 +29629,7 @@
         <v>0</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.6060931935440123</v>
+        <v>0.6060931935440124</v>
       </c>
       <c r="DF61" t="n">
         <v>0</v>
@@ -29758,7 +29758,7 @@
         <v>13538.42703927306</v>
       </c>
       <c r="FB61" t="n">
-        <v>7349.47473983309</v>
+        <v>7349.474739833091</v>
       </c>
       <c r="FC61" t="n">
         <v>13538.42703927306</v>
@@ -29791,7 +29791,7 @@
         <v>0</v>
       </c>
       <c r="FO61" t="n">
-        <v>7349.47473983309</v>
+        <v>7349.474739833091</v>
       </c>
       <c r="FP61" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
         <v>0</v>
       </c>
       <c r="CO62" t="n">
-        <v>2255.585514820285</v>
+        <v>2255.585514820284</v>
       </c>
       <c r="CP62" t="n">
         <v>0</v>
@@ -30378,16 +30378,16 @@
         <v>0.1079109816739168</v>
       </c>
       <c r="W63" t="n">
-        <v>84.23802772828859</v>
+        <v>84.23802772828857</v>
       </c>
       <c r="X63" t="n">
-        <v>70.19835644024049</v>
+        <v>70.19835644024047</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>70.19835644024049</v>
+        <v>70.19835644024047</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
@@ -30465,7 +30465,7 @@
         <v>0.1128835197094509</v>
       </c>
       <c r="BD63" t="n">
-        <v>88.05954461809506</v>
+        <v>88.05954461809507</v>
       </c>
       <c r="BE63" t="n">
         <v>73.38295384841255</v>
@@ -30552,16 +30552,16 @@
         <v>0.1180851922976622</v>
       </c>
       <c r="CK63" t="n">
-        <v>92.13763983528951</v>
+        <v>92.13763983528948</v>
       </c>
       <c r="CL63" t="n">
-        <v>76.7813665294079</v>
+        <v>76.78136652940789</v>
       </c>
       <c r="CN63" t="n">
         <v>0</v>
       </c>
       <c r="CO63" t="n">
-        <v>76.7813665294079</v>
+        <v>76.78136652940789</v>
       </c>
       <c r="CP63" t="n">
         <v>0</v>
@@ -30874,7 +30874,7 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>8269.052260657694</v>
+        <v>8269.052260657692</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -31048,7 +31048,7 @@
         <v>0</v>
       </c>
       <c r="CO64" t="n">
-        <v>8273.029512375995</v>
+        <v>8273.029512375993</v>
       </c>
       <c r="CP64" t="n">
         <v>0</v>
@@ -31535,7 +31535,7 @@
         <v>0</v>
       </c>
       <c r="CO65" t="n">
-        <v>361.0239354840332</v>
+        <v>361.0239354840331</v>
       </c>
       <c r="CP65" t="n">
         <v>0</v>
@@ -32329,19 +32329,19 @@
         <v>10982.4171535269</v>
       </c>
       <c r="X67" t="n">
-        <v>9304.194815574057</v>
+        <v>9304.194815574056</v>
       </c>
       <c r="Z67" t="n">
-        <v>5585.547102832876</v>
+        <v>5585.547102832875</v>
       </c>
       <c r="AA67" t="n">
-        <v>9304.194815574057</v>
+        <v>9304.194815574056</v>
       </c>
       <c r="AB67" t="n">
         <v>0.6003256825064937</v>
       </c>
       <c r="AD67" t="n">
-        <v>5396.432993032953</v>
+        <v>5396.432993032952</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -32365,7 +32365,7 @@
         <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>5585.547102832876</v>
+        <v>5585.547102832875</v>
       </c>
       <c r="AN67" t="n">
         <v>0</v>
@@ -32419,7 +32419,7 @@
         <v>10007.89126526951</v>
       </c>
       <c r="BG67" t="n">
-        <v>6204.575290763808</v>
+        <v>6204.575290763807</v>
       </c>
       <c r="BH67" t="n">
         <v>10007.89126526951</v>
@@ -32452,7 +32452,7 @@
         <v>0</v>
       </c>
       <c r="BT67" t="n">
-        <v>6204.575290763808</v>
+        <v>6204.575290763807</v>
       </c>
       <c r="BU67" t="n">
         <v>0</v>
@@ -32500,22 +32500,22 @@
         <v>4.828372307282191</v>
       </c>
       <c r="CK67" t="n">
-        <v>12692.33830096214</v>
+        <v>12692.33830096213</v>
       </c>
       <c r="CL67" t="n">
         <v>10752.82304127373</v>
       </c>
       <c r="CN67" t="n">
-        <v>6872.697194337372</v>
+        <v>6872.697194337373</v>
       </c>
       <c r="CO67" t="n">
         <v>10752.82304127373</v>
       </c>
       <c r="CP67" t="n">
-        <v>0.6391528222827763</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="CR67" t="n">
-        <v>6236.637363938764</v>
+        <v>6236.637363938762</v>
       </c>
       <c r="CS67" t="n">
         <v>0</v>
@@ -32539,7 +32539,7 @@
         <v>0</v>
       </c>
       <c r="DA67" t="n">
-        <v>6872.697194337372</v>
+        <v>6872.697194337373</v>
       </c>
       <c r="DB67" t="n">
         <v>0</v>
@@ -32551,7 +32551,7 @@
         <v>0</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.6391528222827763</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="DF67" t="n">
         <v>0</v>
@@ -32680,13 +32680,13 @@
         <v>12347.29955001049</v>
       </c>
       <c r="FB67" t="n">
-        <v>8312.342171945196</v>
+        <v>8312.342171945198</v>
       </c>
       <c r="FC67" t="n">
         <v>12347.29955001049</v>
       </c>
       <c r="FD67" t="n">
-        <v>0.6732113478155745</v>
+        <v>0.6732113478155746</v>
       </c>
       <c r="FF67" t="n">
         <v>7161.433739006083</v>
@@ -32713,7 +32713,7 @@
         <v>0</v>
       </c>
       <c r="FO67" t="n">
-        <v>8312.342171945196</v>
+        <v>8312.342171945198</v>
       </c>
       <c r="FP67" t="n">
         <v>0</v>
@@ -32725,7 +32725,7 @@
         <v>0</v>
       </c>
       <c r="FS67" t="n">
-        <v>0.6732113478155745</v>
+        <v>0.6732113478155746</v>
       </c>
       <c r="FT67" t="n">
         <v>0</v>
@@ -34277,13 +34277,13 @@
         <v>1051.411676327869</v>
       </c>
       <c r="X71" t="n">
-        <v>876.176396939891</v>
+        <v>876.1763969398908</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>876.176396939891</v>
+        <v>876.1763969398908</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
@@ -34364,13 +34364,13 @@
         <v>392.5953943185531</v>
       </c>
       <c r="BE71" t="n">
-        <v>327.1628285987942</v>
+        <v>327.1628285987943</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
       </c>
       <c r="BH71" t="n">
-        <v>327.1628285987942</v>
+        <v>327.1628285987943</v>
       </c>
       <c r="BI71" t="n">
         <v>0</v>
@@ -34448,16 +34448,16 @@
         <v>0.09715831850449134</v>
       </c>
       <c r="CK71" t="n">
-        <v>232.3110666722967</v>
+        <v>232.3110666722966</v>
       </c>
       <c r="CL71" t="n">
-        <v>193.5925555602473</v>
+        <v>193.5925555602472</v>
       </c>
       <c r="CN71" t="n">
         <v>0</v>
       </c>
       <c r="CO71" t="n">
-        <v>193.5925555602473</v>
+        <v>193.5925555602472</v>
       </c>
       <c r="CP71" t="n">
         <v>0</v>
@@ -34767,7 +34767,7 @@
         <v>122.6276935343746</v>
       </c>
       <c r="Z72" t="n">
-        <v>64.38909956976102</v>
+        <v>64.389099569761</v>
       </c>
       <c r="AA72" t="n">
         <v>122.6276935343746</v>
@@ -34776,7 +34776,7 @@
         <v>0.5250779633371452</v>
       </c>
       <c r="AD72" t="n">
-        <v>62.20902892998823</v>
+        <v>62.20902892998821</v>
       </c>
       <c r="AE72" t="n">
         <v>0</v>
@@ -34800,7 +34800,7 @@
         <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>64.38909956976102</v>
+        <v>64.389099569761</v>
       </c>
       <c r="AN72" t="n">
         <v>0</v>
@@ -34860,10 +34860,10 @@
         <v>121.3527530652989</v>
       </c>
       <c r="BI72" t="n">
-        <v>0.5422584765214509</v>
+        <v>0.5422584765214508</v>
       </c>
       <c r="BK72" t="n">
-        <v>61.5622516300261</v>
+        <v>61.56225163002611</v>
       </c>
       <c r="BL72" t="n">
         <v>0</v>
@@ -34899,7 +34899,7 @@
         <v>0</v>
       </c>
       <c r="BX72" t="n">
-        <v>0.5422584765214509</v>
+        <v>0.5422584765214508</v>
       </c>
       <c r="BY72" t="n">
         <v>0</v>
@@ -34941,16 +34941,16 @@
         <v>119.9972214396463</v>
       </c>
       <c r="CN72" t="n">
-        <v>67.08304531498285</v>
+        <v>67.08304531498287</v>
       </c>
       <c r="CO72" t="n">
         <v>119.9972214396463</v>
       </c>
       <c r="CP72" t="n">
-        <v>0.5590383219725041</v>
+        <v>0.5590383219725044</v>
       </c>
       <c r="CR72" t="n">
-        <v>60.87459043633255</v>
+        <v>60.87459043633254</v>
       </c>
       <c r="CS72" t="n">
         <v>0</v>
@@ -34974,7 +34974,7 @@
         <v>0</v>
       </c>
       <c r="DA72" t="n">
-        <v>67.08304531498285</v>
+        <v>67.08304531498287</v>
       </c>
       <c r="DB72" t="n">
         <v>0</v>
@@ -34986,7 +34986,7 @@
         <v>0</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.5590383219725041</v>
+        <v>0.5590383219725044</v>
       </c>
       <c r="DF72" t="n">
         <v>0</v>
@@ -35115,13 +35115,13 @@
         <v>72.84043468462049</v>
       </c>
       <c r="FB72" t="n">
-        <v>35.09595793833271</v>
+        <v>35.09595793833272</v>
       </c>
       <c r="FC72" t="n">
         <v>72.84043468462049</v>
       </c>
       <c r="FD72" t="n">
-        <v>0.4818197212892644</v>
+        <v>0.4818197212892645</v>
       </c>
       <c r="FF72" t="n">
         <v>30.23664956076971</v>
@@ -35148,7 +35148,7 @@
         <v>0</v>
       </c>
       <c r="FO72" t="n">
-        <v>35.09595793833271</v>
+        <v>35.09595793833272</v>
       </c>
       <c r="FP72" t="n">
         <v>0</v>
@@ -35160,7 +35160,7 @@
         <v>0</v>
       </c>
       <c r="FS72" t="n">
-        <v>0.4818197212892644</v>
+        <v>0.4818197212892645</v>
       </c>
       <c r="FT72" t="n">
         <v>0</v>
@@ -35254,16 +35254,16 @@
         <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2667.95368371769</v>
+        <v>2667.953683717689</v>
       </c>
       <c r="AA73" t="n">
-        <v>3965.573461328948</v>
+        <v>3965.573461328947</v>
       </c>
       <c r="AB73" t="n">
         <v>0.6727787821193463</v>
       </c>
       <c r="AD73" t="n">
-        <v>2577.622749863816</v>
+        <v>2577.622749863815</v>
       </c>
       <c r="AE73" t="n">
         <v>0</v>
@@ -35287,7 +35287,7 @@
         <v>0</v>
       </c>
       <c r="AM73" t="n">
-        <v>2667.95368371769</v>
+        <v>2667.953683717689</v>
       </c>
       <c r="AN73" t="n">
         <v>0</v>
@@ -35344,10 +35344,10 @@
         <v>2956.297928111979</v>
       </c>
       <c r="BH73" t="n">
-        <v>4254.939164669124</v>
+        <v>4254.939164669125</v>
       </c>
       <c r="BI73" t="n">
-        <v>0.6947920554680526</v>
+        <v>0.6947920554680524</v>
       </c>
       <c r="BK73" t="n">
         <v>2765.710457034931</v>
@@ -35386,7 +35386,7 @@
         <v>0</v>
       </c>
       <c r="BX73" t="n">
-        <v>0.6947920554680526</v>
+        <v>0.6947920554680524</v>
       </c>
       <c r="BY73" t="n">
         <v>0</v>
@@ -35428,16 +35428,16 @@
         <v>0</v>
       </c>
       <c r="CN73" t="n">
-        <v>3270.843841995195</v>
+        <v>3270.843841995194</v>
       </c>
       <c r="CO73" t="n">
-        <v>4566.355680204289</v>
+        <v>4566.355680204287</v>
       </c>
       <c r="CP73" t="n">
-        <v>0.7162919560065598</v>
+        <v>0.71629195600656</v>
       </c>
       <c r="CR73" t="n">
-        <v>2968.131192132788</v>
+        <v>2968.131192132787</v>
       </c>
       <c r="CS73" t="n">
         <v>0</v>
@@ -35461,7 +35461,7 @@
         <v>0</v>
       </c>
       <c r="DA73" t="n">
-        <v>3270.843841995195</v>
+        <v>3270.843841995194</v>
       </c>
       <c r="DB73" t="n">
         <v>0</v>
@@ -35473,7 +35473,7 @@
         <v>0</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.7162919560065598</v>
+        <v>0.71629195600656</v>
       </c>
       <c r="DF73" t="n">
         <v>0</v>
@@ -35738,13 +35738,13 @@
         <v>1064.376073554377</v>
       </c>
       <c r="X74" t="n">
-        <v>886.9800612953143</v>
+        <v>886.980061295314</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>886.9800612953143</v>
+        <v>886.980061295314</v>
       </c>
       <c r="AB74" t="n">
         <v>0</v>
@@ -35825,13 +35825,13 @@
         <v>1081.01494781839</v>
       </c>
       <c r="BE74" t="n">
-        <v>900.8457898486585</v>
+        <v>900.8457898486586</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
       </c>
       <c r="BH74" t="n">
-        <v>900.8457898486585</v>
+        <v>900.8457898486586</v>
       </c>
       <c r="BI74" t="n">
         <v>0</v>
@@ -35912,13 +35912,13 @@
         <v>1095.579912407896</v>
       </c>
       <c r="CL74" t="n">
-        <v>912.9832603399135</v>
+        <v>912.9832603399132</v>
       </c>
       <c r="CN74" t="n">
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>912.9832603399135</v>
+        <v>912.9832603399132</v>
       </c>
       <c r="CP74" t="n">
         <v>0</v>
@@ -36225,25 +36225,25 @@
         <v>2302.689559696661</v>
       </c>
       <c r="X75" t="n">
-        <v>1918.918608868032</v>
+        <v>1918.918608868031</v>
       </c>
       <c r="Z75" t="n">
-        <v>940.2236108561707</v>
+        <v>940.2236108561706</v>
       </c>
       <c r="AA75" t="n">
-        <v>1918.918608868032</v>
+        <v>1918.918608868031</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.4899757636989135</v>
+        <v>0.4899757636989136</v>
       </c>
       <c r="AD75" t="n">
-        <v>863.5133739906144</v>
+        <v>863.5133739906142</v>
       </c>
       <c r="AE75" t="n">
         <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>48.13596403585754</v>
+        <v>48.13596403585753</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -36261,7 +36261,7 @@
         <v>0</v>
       </c>
       <c r="AM75" t="n">
-        <v>893.7745786110356</v>
+        <v>893.7745786110355</v>
       </c>
       <c r="AN75" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.4657699260826244</v>
+        <v>0.4657699260826245</v>
       </c>
       <c r="AR75" t="n">
         <v>0</v>
@@ -36312,25 +36312,25 @@
         <v>2438.608949947725</v>
       </c>
       <c r="BE75" t="n">
-        <v>2032.185395595948</v>
+        <v>2032.185395595949</v>
       </c>
       <c r="BG75" t="n">
-        <v>985.2093378774024</v>
+        <v>985.2093378774023</v>
       </c>
       <c r="BH75" t="n">
-        <v>2032.185395595948</v>
+        <v>2032.185395595949</v>
       </c>
       <c r="BI75" t="n">
-        <v>0.484802882656523</v>
+        <v>0.4848028826565229</v>
       </c>
       <c r="BK75" t="n">
-        <v>914.4834280181769</v>
+        <v>914.4834280181771</v>
       </c>
       <c r="BL75" t="n">
         <v>0</v>
       </c>
       <c r="BM75" t="n">
-        <v>8.307996273535609</v>
+        <v>8.307996273535611</v>
       </c>
       <c r="BN75" t="n">
         <v>0</v>
@@ -36348,25 +36348,25 @@
         <v>0</v>
       </c>
       <c r="BT75" t="n">
-        <v>977.5012625295693</v>
+        <v>977.5012625295692</v>
       </c>
       <c r="BU75" t="n">
         <v>0</v>
       </c>
       <c r="BV75" t="n">
-        <v>7.708075347833099</v>
+        <v>7.708075347833102</v>
       </c>
       <c r="BW75" t="n">
         <v>0</v>
       </c>
       <c r="BX75" t="n">
-        <v>0.4810098845548057</v>
+        <v>0.4810098845548056</v>
       </c>
       <c r="BY75" t="n">
         <v>0</v>
       </c>
       <c r="BZ75" t="n">
-        <v>0.003792998101717323</v>
+        <v>0.003792998101717324</v>
       </c>
       <c r="CA75" t="n">
         <v>0</v>
@@ -36396,7 +36396,7 @@
         <v>0.7871660247011885</v>
       </c>
       <c r="CK75" t="n">
-        <v>1608.123807721882</v>
+        <v>1608.123807721881</v>
       </c>
       <c r="CL75" t="n">
         <v>1340.110605446851</v>
@@ -36408,10 +36408,10 @@
         <v>1340.110605446851</v>
       </c>
       <c r="CP75" t="n">
-        <v>0.3978188290844993</v>
+        <v>0.3978188290844994</v>
       </c>
       <c r="CR75" t="n">
-        <v>483.7815053356641</v>
+        <v>483.781505335664</v>
       </c>
       <c r="CS75" t="n">
         <v>0</v>
@@ -36447,7 +36447,7 @@
         <v>0</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.3978188290844993</v>
+        <v>0.3978188290844994</v>
       </c>
       <c r="DF75" t="n">
         <v>0</v>
@@ -36709,16 +36709,16 @@
         <v>3.379890274386407</v>
       </c>
       <c r="W76" t="n">
-        <v>5372.942305958876</v>
+        <v>5372.942305958875</v>
       </c>
       <c r="X76" t="n">
-        <v>4477.476754025407</v>
+        <v>4477.476754025406</v>
       </c>
       <c r="Z76" t="n">
-        <v>2193.855091997732</v>
+        <v>2193.855091997731</v>
       </c>
       <c r="AA76" t="n">
-        <v>4477.476754025407</v>
+        <v>4477.476754025406</v>
       </c>
       <c r="AB76" t="n">
         <v>0.4899757636989136</v>
@@ -36766,7 +36766,7 @@
         <v>0</v>
       </c>
       <c r="AS76" t="n">
-        <v>0.02420583761628917</v>
+        <v>0.02420583761628916</v>
       </c>
       <c r="AT76" t="n">
         <v>0</v>
@@ -36802,7 +36802,7 @@
         <v>4741.765923057214</v>
       </c>
       <c r="BG76" t="n">
-        <v>2298.821788380606</v>
+        <v>2298.821788380605</v>
       </c>
       <c r="BH76" t="n">
         <v>4741.765923057214</v>
@@ -36835,7 +36835,7 @@
         <v>0</v>
       </c>
       <c r="BT76" t="n">
-        <v>2280.836279235662</v>
+        <v>2280.836279235661</v>
       </c>
       <c r="BU76" t="n">
         <v>0</v>
@@ -36847,13 +36847,13 @@
         <v>0</v>
       </c>
       <c r="BX76" t="n">
-        <v>0.4810098845548056</v>
+        <v>0.4810098845548055</v>
       </c>
       <c r="BY76" t="n">
         <v>0</v>
       </c>
       <c r="BZ76" t="n">
-        <v>0.003792998101717323</v>
+        <v>0.003792998101717324</v>
       </c>
       <c r="CA76" t="n">
         <v>0</v>
@@ -36883,19 +36883,19 @@
         <v>2.361498074103565</v>
       </c>
       <c r="CK76" t="n">
-        <v>3752.288884684391</v>
+        <v>3752.28888468439</v>
       </c>
       <c r="CL76" t="n">
-        <v>3126.924746042653</v>
+        <v>3126.924746042651</v>
       </c>
       <c r="CN76" t="n">
         <v>1243.949541106034</v>
       </c>
       <c r="CO76" t="n">
-        <v>3126.924746042653</v>
+        <v>3126.924746042651</v>
       </c>
       <c r="CP76" t="n">
-        <v>0.3978188290844993</v>
+        <v>0.3978188290844996</v>
       </c>
       <c r="CR76" t="n">
         <v>1128.823512449883</v>
@@ -36934,7 +36934,7 @@
         <v>0</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.3978188290844993</v>
+        <v>0.3978188290844996</v>
       </c>
       <c r="DF76" t="n">
         <v>0</v>
@@ -37205,7 +37205,7 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>4770.526105663749</v>
+        <v>4770.526105663748</v>
       </c>
       <c r="AB77" t="n">
         <v>0</v>
@@ -37292,7 +37292,7 @@
         <v>0</v>
       </c>
       <c r="BH77" t="n">
-        <v>5095.126755761101</v>
+        <v>5095.126755761102</v>
       </c>
       <c r="BI77" t="n">
         <v>0</v>
@@ -37379,7 +37379,7 @@
         <v>0</v>
       </c>
       <c r="CO77" t="n">
-        <v>5432.935697386409</v>
+        <v>5432.935697386407</v>
       </c>
       <c r="CP77" t="n">
         <v>0</v>
@@ -37683,31 +37683,31 @@
         <v>4.522238241588476</v>
       </c>
       <c r="W78" t="n">
-        <v>5456.955254452701</v>
+        <v>5456.9552544527</v>
       </c>
       <c r="X78" t="n">
-        <v>4627.435179817339</v>
+        <v>4627.435179817338</v>
       </c>
       <c r="Z78" t="n">
-        <v>1944.632677091361</v>
+        <v>1944.63267709136</v>
       </c>
       <c r="AA78" t="n">
-        <v>4627.435179817339</v>
+        <v>4627.435179817338</v>
       </c>
       <c r="AB78" t="n">
         <v>0.4202398524290343</v>
       </c>
       <c r="AD78" t="n">
-        <v>1795.199410865547</v>
+        <v>1795.199410865546</v>
       </c>
       <c r="AE78" t="n">
         <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>26.60986228059256</v>
+        <v>26.60986228059255</v>
       </c>
       <c r="AG78" t="n">
-        <v>63.0542236060035</v>
+        <v>63.05422360600348</v>
       </c>
       <c r="AH78" t="n">
         <v>0.3879469600558315</v>
@@ -37728,19 +37728,19 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>25.67731582542154</v>
+        <v>25.67731582542153</v>
       </c>
       <c r="AP78" t="n">
-        <v>60.84447926056866</v>
+        <v>60.84447926056865</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.4015422820204078</v>
+        <v>0.4015422820204077</v>
       </c>
       <c r="AR78" t="n">
         <v>0</v>
       </c>
       <c r="AS78" t="n">
-        <v>0.005548930417742797</v>
+        <v>0.005548930417742796</v>
       </c>
       <c r="AT78" t="n">
         <v>0.01314863999088376</v>
@@ -37770,7 +37770,7 @@
         <v>0.7987194484834893</v>
       </c>
       <c r="BD78" t="n">
-        <v>995.2753884847856</v>
+        <v>995.2753884847857</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37857,7 +37857,7 @@
         <v>0.2280489318242397</v>
       </c>
       <c r="CK78" t="n">
-        <v>293.2858085529205</v>
+        <v>293.2858085529203</v>
       </c>
       <c r="CL78" t="n">
         <v>0</v>
@@ -38161,7 +38161,7 @@
         <v>1785.310313556582</v>
       </c>
       <c r="T79" t="n">
-        <v>0.02401046072011333</v>
+        <v>0.02401046072011351</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -38170,22 +38170,22 @@
         <v>3.152425719430006</v>
       </c>
       <c r="W79" t="n">
-        <v>2087.843802400395</v>
+        <v>2087.843802400394</v>
       </c>
       <c r="X79" t="n">
-        <v>1771.116277048731</v>
+        <v>1771.11627704873</v>
       </c>
       <c r="Z79" t="n">
-        <v>898.2600483286955</v>
+        <v>898.260048328695</v>
       </c>
       <c r="AA79" t="n">
-        <v>1771.116277048731</v>
+        <v>1771.11627704873</v>
       </c>
       <c r="AB79" t="n">
         <v>0.5071716972899687</v>
       </c>
       <c r="AD79" t="n">
-        <v>867.8469757538782</v>
+        <v>867.8469757538778</v>
       </c>
       <c r="AE79" t="n">
         <v>0</v>
@@ -38209,7 +38209,7 @@
         <v>0</v>
       </c>
       <c r="AM79" t="n">
-        <v>898.2600483286955</v>
+        <v>898.260048328695</v>
       </c>
       <c r="AN79" t="n">
         <v>0</v>
@@ -38248,31 +38248,31 @@
         <v>1894.160151494478</v>
       </c>
       <c r="BA79" t="n">
-        <v>0.02452726485504424</v>
+        <v>0.02452726485504441</v>
       </c>
       <c r="BB79" t="n">
         <v>0</v>
       </c>
       <c r="BC79" t="n">
-        <v>3.231446877246035</v>
+        <v>3.231446877246034</v>
       </c>
       <c r="BD79" t="n">
-        <v>2213.6842674375</v>
+        <v>2213.684267437501</v>
       </c>
       <c r="BE79" t="n">
         <v>1877.866645865764</v>
       </c>
       <c r="BG79" t="n">
-        <v>983.5633001849632</v>
+        <v>983.5633001849628</v>
       </c>
       <c r="BH79" t="n">
         <v>1877.866645865764</v>
       </c>
       <c r="BI79" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BK79" t="n">
-        <v>920.1546564742242</v>
+        <v>920.1546564742241</v>
       </c>
       <c r="BL79" t="n">
         <v>0</v>
@@ -38296,7 +38296,7 @@
         <v>0</v>
       </c>
       <c r="BT79" t="n">
-        <v>983.5633001849632</v>
+        <v>983.5633001849628</v>
       </c>
       <c r="BU79" t="n">
         <v>0</v>
@@ -38308,7 +38308,7 @@
         <v>0</v>
       </c>
       <c r="BX79" t="n">
-        <v>0.5237663187374549</v>
+        <v>0.5237663187374548</v>
       </c>
       <c r="BY79" t="n">
         <v>0</v>
@@ -38335,7 +38335,7 @@
         <v>2007.159354933222</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.02505898570883447</v>
+        <v>0.02505898570883466</v>
       </c>
       <c r="CI79" t="n">
         <v>0</v>
@@ -38344,7 +38344,7 @@
         <v>3.312444748910455</v>
       </c>
       <c r="CK79" t="n">
-        <v>2346.320822823734</v>
+        <v>2346.320822823733</v>
       </c>
       <c r="CL79" t="n">
         <v>1990.382132851022</v>
@@ -38356,10 +38356,10 @@
         <v>1990.382132851022</v>
       </c>
       <c r="CP79" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="CR79" t="n">
-        <v>975.2872450970009</v>
+        <v>975.2872450970006</v>
       </c>
       <c r="CS79" t="n">
         <v>0</v>
@@ -38395,7 +38395,7 @@
         <v>0</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.5399739360664835</v>
+        <v>0.5399739360664837</v>
       </c>
       <c r="DF79" t="n">
         <v>0</v>
@@ -38422,7 +38422,7 @@
         <v>2124.866979970051</v>
       </c>
       <c r="DO79" t="n">
-        <v>0.02553922120585154</v>
+        <v>0.02553922120585175</v>
       </c>
       <c r="DP79" t="n">
         <v>0</v>
@@ -38509,7 +38509,7 @@
         <v>1558.944101184794</v>
       </c>
       <c r="EV79" t="n">
-        <v>0.01825789040242592</v>
+        <v>0.01825789040242606</v>
       </c>
       <c r="EW79" t="n">
         <v>0</v>
@@ -38518,7 +38518,7 @@
         <v>2.41199958754975</v>
       </c>
       <c r="EY79" t="n">
-        <v>1822.815584614194</v>
+        <v>1822.815584614193</v>
       </c>
       <c r="EZ79" t="n">
         <v>1546.293045608383</v>
@@ -38530,10 +38530,10 @@
         <v>1546.293045608383</v>
       </c>
       <c r="FD79" t="n">
-        <v>0.4431638969883433</v>
+        <v>0.4431638969883434</v>
       </c>
       <c r="FF79" t="n">
-        <v>590.3815011983382</v>
+        <v>590.3815011983381</v>
       </c>
       <c r="FG79" t="n">
         <v>0</v>
@@ -38569,7 +38569,7 @@
         <v>0</v>
       </c>
       <c r="FS79" t="n">
-        <v>0.4431638969883433</v>
+        <v>0.4431638969883434</v>
       </c>
       <c r="FT79" t="n">
         <v>0</v>
@@ -40109,7 +40109,7 @@
         <v>6816.831951971585</v>
       </c>
       <c r="T83" t="n">
-        <v>0.0157820858784628</v>
+        <v>0.01578208587846291</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -40118,22 +40118,22 @@
         <v>4.396578053677243</v>
       </c>
       <c r="W83" t="n">
-        <v>8005.402372034606</v>
+        <v>8005.402372034604</v>
       </c>
       <c r="X83" t="n">
-        <v>6789.769882645438</v>
+        <v>6789.769882645436</v>
       </c>
       <c r="Z83" t="n">
-        <v>4286.904613285011</v>
+        <v>4286.90461328501</v>
       </c>
       <c r="AA83" t="n">
-        <v>6789.769882645438</v>
+        <v>6789.769882645436</v>
       </c>
       <c r="AB83" t="n">
         <v>0.6313770109120019</v>
       </c>
       <c r="AD83" t="n">
-        <v>4141.759628413717</v>
+        <v>4141.759628413716</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -40157,7 +40157,7 @@
         <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>4286.904613285011</v>
+        <v>4286.90461328501</v>
       </c>
       <c r="AN83" t="n">
         <v>0</v>
@@ -40196,7 +40196,7 @@
         <v>7374.944207180017</v>
       </c>
       <c r="BA83" t="n">
-        <v>0.01645269759418638</v>
+        <v>0.0164526975941865</v>
       </c>
       <c r="BB83" t="n">
         <v>0</v>
@@ -40205,19 +40205,19 @@
         <v>4.599228997192246</v>
       </c>
       <c r="BD83" t="n">
-        <v>8655.018692583359</v>
+        <v>8655.01869258336</v>
       </c>
       <c r="BE83" t="n">
-        <v>7340.740979856613</v>
+        <v>7340.740979856614</v>
       </c>
       <c r="BG83" t="n">
-        <v>4786.424605496026</v>
+        <v>4786.424605496025</v>
       </c>
       <c r="BH83" t="n">
-        <v>7340.740979856613</v>
+        <v>7340.740979856614</v>
       </c>
       <c r="BI83" t="n">
-        <v>0.6520356212854032</v>
+        <v>0.6520356212854029</v>
       </c>
       <c r="BK83" t="n">
         <v>4477.851997712534</v>
@@ -40244,7 +40244,7 @@
         <v>0</v>
       </c>
       <c r="BT83" t="n">
-        <v>4786.424605496026</v>
+        <v>4786.424605496025</v>
       </c>
       <c r="BU83" t="n">
         <v>0</v>
@@ -40256,7 +40256,7 @@
         <v>0</v>
       </c>
       <c r="BX83" t="n">
-        <v>0.6520356212854032</v>
+        <v>0.6520356212854029</v>
       </c>
       <c r="BY83" t="n">
         <v>0</v>
@@ -40283,7 +40283,7 @@
         <v>7968.019343456677</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.01715440142794974</v>
+        <v>0.01715440142794987</v>
       </c>
       <c r="CI83" t="n">
         <v>0</v>
@@ -40292,19 +40292,19 @@
         <v>4.811217905854241</v>
       </c>
       <c r="CK83" t="n">
-        <v>9353.205886285437</v>
+        <v>9353.205886285434</v>
       </c>
       <c r="CL83" t="n">
-        <v>7932.907389481108</v>
+        <v>7932.907389481105</v>
       </c>
       <c r="CN83" t="n">
-        <v>5332.599120009987</v>
+        <v>5332.599120009988</v>
       </c>
       <c r="CO83" t="n">
-        <v>7932.907389481108</v>
+        <v>7932.907389481105</v>
       </c>
       <c r="CP83" t="n">
-        <v>0.6722124510215406</v>
+        <v>0.6722124510215409</v>
       </c>
       <c r="CR83" t="n">
         <v>4839.073507583475</v>
@@ -40331,7 +40331,7 @@
         <v>0</v>
       </c>
       <c r="DA83" t="n">
-        <v>5332.599120009987</v>
+        <v>5332.599120009988</v>
       </c>
       <c r="DB83" t="n">
         <v>0</v>
@@ -40343,7 +40343,7 @@
         <v>0</v>
       </c>
       <c r="DE83" t="n">
-        <v>0.6722124510215406</v>
+        <v>0.6722124510215409</v>
       </c>
       <c r="DF83" t="n">
         <v>0</v>
@@ -40370,7 +40370,7 @@
         <v>8598.660893983686</v>
       </c>
       <c r="DO83" t="n">
-        <v>0.01784201153379754</v>
+        <v>0.01784201153379768</v>
       </c>
       <c r="DP83" t="n">
         <v>0</v>
@@ -40457,7 +40457,7 @@
         <v>2374.62859166879</v>
       </c>
       <c r="EV83" t="n">
-        <v>0.004806692883870512</v>
+        <v>0.00480669288387055</v>
       </c>
       <c r="EW83" t="n">
         <v>0</v>
@@ -40605,22 +40605,22 @@
         <v>3.17643618015012</v>
       </c>
       <c r="W84" t="n">
-        <v>6311.237614486221</v>
+        <v>6311.237614486219</v>
       </c>
       <c r="X84" t="n">
-        <v>5353.817969757827</v>
+        <v>5353.817969757826</v>
       </c>
       <c r="Z84" t="n">
         <v>2715.304946703611</v>
       </c>
       <c r="AA84" t="n">
-        <v>5353.817969757827</v>
+        <v>5353.817969757826</v>
       </c>
       <c r="AB84" t="n">
         <v>0.5071716972899687</v>
       </c>
       <c r="AD84" t="n">
-        <v>2623.370805181335</v>
+        <v>2623.370805181334</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -40692,22 +40692,22 @@
         <v>3.255974142101079</v>
       </c>
       <c r="BD84" t="n">
-        <v>6691.459591341157</v>
+        <v>6691.459591341158</v>
       </c>
       <c r="BE84" t="n">
-        <v>5676.359977605923</v>
+        <v>5676.359977605924</v>
       </c>
       <c r="BG84" t="n">
         <v>2973.086169299277</v>
       </c>
       <c r="BH84" t="n">
-        <v>5676.359977605923</v>
+        <v>5676.359977605924</v>
       </c>
       <c r="BI84" t="n">
-        <v>0.523766318737455</v>
+        <v>0.5237663187374549</v>
       </c>
       <c r="BK84" t="n">
-        <v>2781.416389026902</v>
+        <v>2781.416389026903</v>
       </c>
       <c r="BL84" t="n">
         <v>0</v>
@@ -40743,7 +40743,7 @@
         <v>0</v>
       </c>
       <c r="BX84" t="n">
-        <v>0.523766318737455</v>
+        <v>0.5237663187374549</v>
       </c>
       <c r="BY84" t="n">
         <v>0</v>
@@ -40779,22 +40779,22 @@
         <v>3.337503734619289</v>
       </c>
       <c r="CK84" t="n">
-        <v>7092.212944561546</v>
+        <v>7092.212944561544</v>
       </c>
       <c r="CL84" t="n">
-        <v>6016.318736088936</v>
+        <v>6016.318736088933</v>
       </c>
       <c r="CN84" t="n">
         <v>3248.655308556473</v>
       </c>
       <c r="CO84" t="n">
-        <v>6016.318736088936</v>
+        <v>6016.318736088933</v>
       </c>
       <c r="CP84" t="n">
-        <v>0.5399739360664834</v>
+        <v>0.5399739360664836</v>
       </c>
       <c r="CR84" t="n">
-        <v>2947.996180683578</v>
+        <v>2947.996180683577</v>
       </c>
       <c r="CS84" t="n">
         <v>0</v>
@@ -40830,7 +40830,7 @@
         <v>0</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.5399739360664834</v>
+        <v>0.5399739360664836</v>
       </c>
       <c r="DF84" t="n">
         <v>0</v>
@@ -40965,7 +40965,7 @@
         <v>4673.993631581882</v>
       </c>
       <c r="FD84" t="n">
-        <v>0.4431638969883432</v>
+        <v>0.4431638969883434</v>
       </c>
       <c r="FF84" t="n">
         <v>1784.551372485215</v>
@@ -41004,7 +41004,7 @@
         <v>0</v>
       </c>
       <c r="FS84" t="n">
-        <v>0.4431638969883432</v>
+        <v>0.4431638969883434</v>
       </c>
       <c r="FT84" t="n">
         <v>0</v>
@@ -41188,7 +41188,7 @@
         <v>0</v>
       </c>
       <c r="BH85" t="n">
-        <v>16.88182699549793</v>
+        <v>16.88182699549794</v>
       </c>
       <c r="BI85" t="n">
         <v>0</v>
@@ -41275,7 +41275,7 @@
         <v>0</v>
       </c>
       <c r="CO85" t="n">
-        <v>16.44797671825915</v>
+        <v>16.44797671825914</v>
       </c>
       <c r="CP85" t="n">
         <v>0</v>
@@ -41588,7 +41588,7 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>39.55722141811316</v>
+        <v>39.55722141811315</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -41675,7 +41675,7 @@
         <v>0</v>
       </c>
       <c r="BH86" t="n">
-        <v>38.42961227012716</v>
+        <v>38.42961227012717</v>
       </c>
       <c r="BI86" t="n">
         <v>0</v>
@@ -41762,7 +41762,7 @@
         <v>0</v>
       </c>
       <c r="CO86" t="n">
-        <v>37.44278459058842</v>
+        <v>37.44278459058841</v>
       </c>
       <c r="CP86" t="n">
         <v>0</v>
@@ -42069,13 +42069,13 @@
         <v>144.7728732029396</v>
       </c>
       <c r="X87" t="n">
-        <v>120.6440610024497</v>
+        <v>120.6440610024496</v>
       </c>
       <c r="Z87" t="n">
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>120.6440610024497</v>
+        <v>120.6440610024496</v>
       </c>
       <c r="AB87" t="n">
         <v>0</v>
@@ -42556,13 +42556,13 @@
         <v>293.9007877402116</v>
       </c>
       <c r="X88" t="n">
-        <v>244.917323116843</v>
+        <v>244.9173231168429</v>
       </c>
       <c r="Z88" t="n">
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>244.917323116843</v>
+        <v>244.9173231168429</v>
       </c>
       <c r="AB88" t="n">
         <v>0</v>
@@ -42727,7 +42727,7 @@
         <v>2.86871108822917</v>
       </c>
       <c r="CK88" t="n">
-        <v>276.5558380470797</v>
+        <v>276.5558380470796</v>
       </c>
       <c r="CL88" t="n">
         <v>230.4631983725664</v>
@@ -43127,22 +43127,22 @@
         <v>2.743368122170749</v>
       </c>
       <c r="BD89" t="n">
-        <v>6251.786083387837</v>
+        <v>6251.786083387838</v>
       </c>
       <c r="BE89" t="n">
-        <v>5372.789890308738</v>
+        <v>5372.789890308739</v>
       </c>
       <c r="BG89" t="n">
         <v>2014.80053014736</v>
       </c>
       <c r="BH89" t="n">
-        <v>5372.789890308738</v>
+        <v>5372.789890308739</v>
       </c>
       <c r="BI89" t="n">
-        <v>0.3750008042900749</v>
+        <v>0.3750008042900748</v>
       </c>
       <c r="BK89" t="n">
-        <v>1880.476461608058</v>
+        <v>1880.476461608059</v>
       </c>
       <c r="BL89" t="n">
         <v>0</v>
@@ -43151,7 +43151,7 @@
         <v>0</v>
       </c>
       <c r="BN89" t="n">
-        <v>5.107652480289732</v>
+        <v>5.107652480289733</v>
       </c>
       <c r="BO89" t="n">
         <v>0.35</v>
@@ -43175,7 +43175,7 @@
         <v>0</v>
       </c>
       <c r="BW89" t="n">
-        <v>4.73882857820123</v>
+        <v>4.738828578201232</v>
       </c>
       <c r="BX89" t="n">
         <v>0.3741187990981821</v>
@@ -43187,7 +43187,7 @@
         <v>0</v>
       </c>
       <c r="CA89" t="n">
-        <v>0.0008820051918927582</v>
+        <v>0.0008820051918927584</v>
       </c>
       <c r="CC89" t="n">
         <v>345.6643833935144</v>
@@ -43214,22 +43214,22 @@
         <v>3.840715371039049</v>
       </c>
       <c r="CK89" t="n">
-        <v>9317.226465502752</v>
+        <v>9317.226465502748</v>
       </c>
       <c r="CL89" t="n">
-        <v>8007.231772147105</v>
+        <v>8007.231772147103</v>
       </c>
       <c r="CN89" t="n">
         <v>3113.984667684119</v>
       </c>
       <c r="CO89" t="n">
-        <v>8007.231772147105</v>
+        <v>8007.231772147103</v>
       </c>
       <c r="CP89" t="n">
-        <v>0.3888965320719219</v>
+        <v>0.388896532071922</v>
       </c>
       <c r="CR89" t="n">
-        <v>2802.531120251486</v>
+        <v>2802.531120251485</v>
       </c>
       <c r="CS89" t="n">
         <v>0</v>
@@ -43238,7 +43238,7 @@
         <v>0</v>
       </c>
       <c r="CU89" t="n">
-        <v>28.54621592461996</v>
+        <v>28.54621592461995</v>
       </c>
       <c r="CV89" t="n">
         <v>0.3499999999999999</v>
@@ -43262,10 +43262,10 @@
         <v>0</v>
       </c>
       <c r="DD89" t="n">
-        <v>25.63005553920749</v>
+        <v>25.63005553920747</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.3856956686189167</v>
+        <v>0.3856956686189169</v>
       </c>
       <c r="DF89" t="n">
         <v>0</v>
@@ -43274,7 +43274,7 @@
         <v>0</v>
       </c>
       <c r="DH89" t="n">
-        <v>0.00320086345300517</v>
+        <v>0.003200863453005169</v>
       </c>
       <c r="DJ89" t="n">
         <v>483.9301367509202</v>
@@ -43349,7 +43349,7 @@
         <v>0</v>
       </c>
       <c r="EK89" t="n">
-        <v>65.4384964676801</v>
+        <v>65.43849646768012</v>
       </c>
       <c r="EL89" t="n">
         <v>0.3962085148184847</v>
@@ -43361,7 +43361,7 @@
         <v>0</v>
       </c>
       <c r="EO89" t="n">
-        <v>0.005482696861935666</v>
+        <v>0.005482696861935668</v>
       </c>
       <c r="EQ89" t="n">
         <v>677.5021914512882</v>
@@ -43394,13 +43394,13 @@
         <v>17789.89884475349</v>
       </c>
       <c r="FB89" t="n">
-        <v>7363.282061334416</v>
+        <v>7363.282061334417</v>
       </c>
       <c r="FC89" t="n">
         <v>17789.89884475349</v>
       </c>
       <c r="FD89" t="n">
-        <v>0.4139024131385636</v>
+        <v>0.4139024131385637</v>
       </c>
       <c r="FF89" t="n">
         <v>6226.464595663722</v>
@@ -43427,7 +43427,7 @@
         <v>0.009070679838954241</v>
       </c>
       <c r="FO89" t="n">
-        <v>7227.114866504707</v>
+        <v>7227.114866504709</v>
       </c>
       <c r="FP89" t="n">
         <v>0</v>
@@ -43439,7 +43439,7 @@
         <v>136.167194829709</v>
       </c>
       <c r="FS89" t="n">
-        <v>0.406248227130088</v>
+        <v>0.4062482271300881</v>
       </c>
       <c r="FT89" t="n">
         <v>0</v>
@@ -43448,7 +43448,7 @@
         <v>0</v>
       </c>
       <c r="FV89" t="n">
-        <v>0.007654186008475633</v>
+        <v>0.007654186008475631</v>
       </c>
     </row>
     <row r="90">
@@ -43614,22 +43614,22 @@
         <v>2.743368122170749</v>
       </c>
       <c r="BD90" t="n">
-        <v>6251.786083387837</v>
+        <v>6251.786083387838</v>
       </c>
       <c r="BE90" t="n">
-        <v>5372.789890308738</v>
+        <v>5372.789890308739</v>
       </c>
       <c r="BG90" t="n">
         <v>2014.80053014736</v>
       </c>
       <c r="BH90" t="n">
-        <v>5372.789890308738</v>
+        <v>5372.789890308739</v>
       </c>
       <c r="BI90" t="n">
-        <v>0.3750008042900749</v>
+        <v>0.3750008042900748</v>
       </c>
       <c r="BK90" t="n">
-        <v>1880.476461608058</v>
+        <v>1880.476461608059</v>
       </c>
       <c r="BL90" t="n">
         <v>0</v>
@@ -43638,7 +43638,7 @@
         <v>0</v>
       </c>
       <c r="BN90" t="n">
-        <v>5.107652480289732</v>
+        <v>5.107652480289733</v>
       </c>
       <c r="BO90" t="n">
         <v>0.35</v>
@@ -43662,7 +43662,7 @@
         <v>0</v>
       </c>
       <c r="BW90" t="n">
-        <v>4.73882857820123</v>
+        <v>4.738828578201232</v>
       </c>
       <c r="BX90" t="n">
         <v>0.3741187990981821</v>
@@ -43674,7 +43674,7 @@
         <v>0</v>
       </c>
       <c r="CA90" t="n">
-        <v>0.0008820051918927582</v>
+        <v>0.0008820051918927584</v>
       </c>
       <c r="CC90" t="n">
         <v>345.6643833935144</v>
@@ -43701,22 +43701,22 @@
         <v>3.840715371039049</v>
       </c>
       <c r="CK90" t="n">
-        <v>9317.226465502752</v>
+        <v>9317.226465502748</v>
       </c>
       <c r="CL90" t="n">
-        <v>8007.231772147105</v>
+        <v>8007.231772147103</v>
       </c>
       <c r="CN90" t="n">
         <v>3113.984667684119</v>
       </c>
       <c r="CO90" t="n">
-        <v>8007.231772147105</v>
+        <v>8007.231772147103</v>
       </c>
       <c r="CP90" t="n">
-        <v>0.3888965320719219</v>
+        <v>0.388896532071922</v>
       </c>
       <c r="CR90" t="n">
-        <v>2802.531120251486</v>
+        <v>2802.531120251485</v>
       </c>
       <c r="CS90" t="n">
         <v>0</v>
@@ -43725,7 +43725,7 @@
         <v>0</v>
       </c>
       <c r="CU90" t="n">
-        <v>28.54621592461996</v>
+        <v>28.54621592461995</v>
       </c>
       <c r="CV90" t="n">
         <v>0.3499999999999999</v>
@@ -43749,10 +43749,10 @@
         <v>0</v>
       </c>
       <c r="DD90" t="n">
-        <v>25.63005553920749</v>
+        <v>25.63005553920747</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.3856956686189167</v>
+        <v>0.3856956686189169</v>
       </c>
       <c r="DF90" t="n">
         <v>0</v>
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.00320086345300517</v>
+        <v>0.003200863453005169</v>
       </c>
       <c r="DJ90" t="n">
         <v>483.9301367509202</v>
@@ -43836,7 +43836,7 @@
         <v>0</v>
       </c>
       <c r="EK90" t="n">
-        <v>65.4384964676801</v>
+        <v>65.43849646768012</v>
       </c>
       <c r="EL90" t="n">
         <v>0.3962085148184847</v>
@@ -43848,7 +43848,7 @@
         <v>0</v>
       </c>
       <c r="EO90" t="n">
-        <v>0.005482696861935666</v>
+        <v>0.005482696861935668</v>
       </c>
       <c r="EQ90" t="n">
         <v>677.5021914512882</v>
@@ -43881,13 +43881,13 @@
         <v>17789.89884475349</v>
       </c>
       <c r="FB90" t="n">
-        <v>7363.282061334416</v>
+        <v>7363.282061334417</v>
       </c>
       <c r="FC90" t="n">
         <v>17789.89884475349</v>
       </c>
       <c r="FD90" t="n">
-        <v>0.4139024131385636</v>
+        <v>0.4139024131385637</v>
       </c>
       <c r="FF90" t="n">
         <v>6226.464595663722</v>
@@ -43914,7 +43914,7 @@
         <v>0.009070679838954241</v>
       </c>
       <c r="FO90" t="n">
-        <v>7227.114866504707</v>
+        <v>7227.114866504709</v>
       </c>
       <c r="FP90" t="n">
         <v>0</v>
@@ -43926,7 +43926,7 @@
         <v>136.167194829709</v>
       </c>
       <c r="FS90" t="n">
-        <v>0.406248227130088</v>
+        <v>0.4062482271300881</v>
       </c>
       <c r="FT90" t="n">
         <v>0</v>
@@ -43935,7 +43935,7 @@
         <v>0</v>
       </c>
       <c r="FV90" t="n">
-        <v>0.007654186008475633</v>
+        <v>0.007654186008475631</v>
       </c>
     </row>
     <row r="91">
@@ -44023,7 +44023,7 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>7006.660737007776</v>
+        <v>7006.660737007775</v>
       </c>
       <c r="AB91" t="n">
         <v>0</v>
@@ -44110,7 +44110,7 @@
         <v>0</v>
       </c>
       <c r="BH91" t="n">
-        <v>7364.854767298409</v>
+        <v>7364.85476729841</v>
       </c>
       <c r="BI91" t="n">
         <v>0</v>
@@ -44197,7 +44197,7 @@
         <v>0</v>
       </c>
       <c r="CO91" t="n">
-        <v>7742.947424702473</v>
+        <v>7742.947424702471</v>
       </c>
       <c r="CP91" t="n">
         <v>0</v>
@@ -44510,7 +44510,7 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>340.5790355226707</v>
+        <v>340.5790355226706</v>
       </c>
       <c r="AB92" t="n">
         <v>0</v>
@@ -44684,7 +44684,7 @@
         <v>0</v>
       </c>
       <c r="CO92" t="n">
-        <v>376.3683821708904</v>
+        <v>376.3683821708902</v>
       </c>
       <c r="CP92" t="n">
         <v>0</v>
@@ -44997,7 +44997,7 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>6053.400860246243</v>
+        <v>6053.400860246242</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -45084,7 +45084,7 @@
         <v>0</v>
       </c>
       <c r="BH93" t="n">
-        <v>5790.826930142768</v>
+        <v>5790.826930142769</v>
       </c>
       <c r="BI93" t="n">
         <v>0</v>
@@ -45171,7 +45171,7 @@
         <v>0</v>
       </c>
       <c r="CO93" t="n">
-        <v>5470.319113369159</v>
+        <v>5470.319113369157</v>
       </c>
       <c r="CP93" t="n">
         <v>0</v>
@@ -45466,7 +45466,7 @@
         <v>2866.777187793799</v>
       </c>
       <c r="T94" t="n">
-        <v>0.005706544289548924</v>
+        <v>0.005706544289548967</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -45475,7 +45475,7 @@
         <v>3.929496099204925</v>
       </c>
       <c r="W94" t="n">
-        <v>3320.566866465501</v>
+        <v>3320.5668664655</v>
       </c>
       <c r="X94" t="n">
         <v>2861.490662688719</v>
@@ -45553,7 +45553,7 @@
         <v>3013.805535586104</v>
       </c>
       <c r="BA94" t="n">
-        <v>0.005623788658484214</v>
+        <v>0.005623788658484254</v>
       </c>
       <c r="BB94" t="n">
         <v>0</v>
@@ -45562,7 +45562,7 @@
         <v>3.885858753466767</v>
       </c>
       <c r="BD94" t="n">
-        <v>3488.502398303446</v>
+        <v>3488.502398303447</v>
       </c>
       <c r="BE94" t="n">
         <v>3006.208711025884</v>
@@ -45574,7 +45574,7 @@
         <v>3006.208711025884</v>
       </c>
       <c r="BI94" t="n">
-        <v>0.6632142166771363</v>
+        <v>0.6632142166771362</v>
       </c>
       <c r="BK94" t="n">
         <v>1803.72522661553</v>
@@ -45586,7 +45586,7 @@
         <v>0</v>
       </c>
       <c r="BN94" t="n">
-        <v>70.85535138033606</v>
+        <v>70.85535138033607</v>
       </c>
       <c r="BO94" t="n">
         <v>0.6</v>
@@ -45610,10 +45610,10 @@
         <v>0</v>
       </c>
       <c r="BW94" t="n">
-        <v>65.73888206673368</v>
+        <v>65.73888206673371</v>
       </c>
       <c r="BX94" t="n">
-        <v>0.6413465127397407</v>
+        <v>0.6413465127397406</v>
       </c>
       <c r="BY94" t="n">
         <v>0</v>
@@ -45622,7 +45622,7 @@
         <v>0</v>
       </c>
       <c r="CA94" t="n">
-        <v>0.0218677039373956</v>
+        <v>0.02186770393739561</v>
       </c>
       <c r="CC94" t="n">
         <v>9.739744553651121</v>
@@ -45640,31 +45640,31 @@
         <v>1278.854437707636</v>
       </c>
       <c r="CH94" t="n">
-        <v>0.002244682956084806</v>
+        <v>0.002244682956084824</v>
       </c>
       <c r="CI94" t="n">
         <v>0</v>
       </c>
       <c r="CJ94" t="n">
-        <v>1.556114445628095</v>
+        <v>1.556114445628094</v>
       </c>
       <c r="CK94" t="n">
         <v>1480.616976740361</v>
       </c>
       <c r="CL94" t="n">
-        <v>1275.918186363968</v>
+        <v>1275.918186363967</v>
       </c>
       <c r="CN94" t="n">
-        <v>541.0421284582569</v>
+        <v>541.0421284582568</v>
       </c>
       <c r="CO94" t="n">
-        <v>1275.918186363968</v>
+        <v>1275.918186363967</v>
       </c>
       <c r="CP94" t="n">
-        <v>0.4240413956321801</v>
+        <v>0.4240413956321802</v>
       </c>
       <c r="CR94" t="n">
-        <v>471.4176968379534</v>
+        <v>471.4176968379532</v>
       </c>
       <c r="CS94" t="n">
         <v>0</v>
@@ -45673,7 +45673,7 @@
         <v>0</v>
       </c>
       <c r="CU94" t="n">
-        <v>23.99710278867148</v>
+        <v>23.99710278867147</v>
       </c>
       <c r="CV94" t="n">
         <v>0.3694732952912681</v>
@@ -45688,7 +45688,7 @@
         <v>0.01880771278686523</v>
       </c>
       <c r="DA94" t="n">
-        <v>519.4964679448693</v>
+        <v>519.4964679448692</v>
       </c>
       <c r="DB94" t="n">
         <v>0</v>
@@ -45697,10 +45697,10 @@
         <v>0</v>
       </c>
       <c r="DD94" t="n">
-        <v>21.54566051338762</v>
+        <v>21.54566051338759</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.4071549990405718</v>
+        <v>0.4071549990405719</v>
       </c>
       <c r="DF94" t="n">
         <v>0</v>
@@ -45709,7 +45709,7 @@
         <v>0</v>
       </c>
       <c r="DH94" t="n">
-        <v>0.01688639659160835</v>
+        <v>0.01688639659160834</v>
       </c>
       <c r="DJ94" t="n">
         <v>1.685458808587339</v>
@@ -45962,16 +45962,16 @@
         <v>0.9838006608736186</v>
       </c>
       <c r="W95" t="n">
-        <v>665.0511128474008</v>
+        <v>665.0511128474006</v>
       </c>
       <c r="X95" t="n">
-        <v>573.1020267793756</v>
+        <v>573.1020267793755</v>
       </c>
       <c r="Z95" t="n">
-        <v>364.3206999926177</v>
+        <v>364.3206999926176</v>
       </c>
       <c r="AA95" t="n">
-        <v>573.1020267793756</v>
+        <v>573.1020267793755</v>
       </c>
       <c r="AB95" t="n">
         <v>0.6356995490662756</v>
@@ -45986,7 +45986,7 @@
         <v>0</v>
       </c>
       <c r="AG95" t="n">
-        <v>8.7145166143943</v>
+        <v>8.714516614394299</v>
       </c>
       <c r="AH95" t="n">
         <v>0.6</v>
@@ -46001,7 +46001,7 @@
         <v>0.01520587296360948</v>
       </c>
       <c r="AM95" t="n">
-        <v>355.911584867776</v>
+        <v>355.9115848677759</v>
       </c>
       <c r="AN95" t="n">
         <v>0</v>
@@ -46010,7 +46010,7 @@
         <v>0</v>
       </c>
       <c r="AP95" t="n">
-        <v>8.409115124841708</v>
+        <v>8.409115124841707</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.6210265681101658</v>
@@ -46049,22 +46049,22 @@
         <v>0.9728706355313128</v>
       </c>
       <c r="BD95" t="n">
-        <v>698.6769068465958</v>
+        <v>698.6769068465959</v>
       </c>
       <c r="BE95" t="n">
-        <v>602.0787630342719</v>
+        <v>602.078763034272</v>
       </c>
       <c r="BG95" t="n">
         <v>399.303740856024</v>
       </c>
       <c r="BH95" t="n">
-        <v>602.0787630342719</v>
+        <v>602.078763034272</v>
       </c>
       <c r="BI95" t="n">
         <v>0.6632084793087023</v>
       </c>
       <c r="BK95" t="n">
-        <v>361.2472578205631</v>
+        <v>361.2472578205632</v>
       </c>
       <c r="BL95" t="n">
         <v>0</v>
@@ -46088,7 +46088,7 @@
         <v>0.02356348745840324</v>
       </c>
       <c r="BT95" t="n">
-        <v>386.141115066687</v>
+        <v>386.1411150666871</v>
       </c>
       <c r="BU95" t="n">
         <v>0</v>
@@ -46109,7 +46109,7 @@
         <v>0</v>
       </c>
       <c r="CA95" t="n">
-        <v>0.02186196656896152</v>
+        <v>0.02186196656896153</v>
       </c>
       <c r="CC95" t="n">
         <v>1.947948910730224</v>
@@ -46136,22 +46136,22 @@
         <v>0.3895897821460448</v>
       </c>
       <c r="CK95" t="n">
-        <v>296.5333324561649</v>
+        <v>296.5333324561648</v>
       </c>
       <c r="CL95" t="n">
-        <v>255.5350266397719</v>
+        <v>255.5350266397718</v>
       </c>
       <c r="CN95" t="n">
         <v>108.356029970377</v>
       </c>
       <c r="CO95" t="n">
-        <v>255.5350266397719</v>
+        <v>255.5350266397718</v>
       </c>
       <c r="CP95" t="n">
-        <v>0.4240359194402208</v>
+        <v>0.424035919440221</v>
       </c>
       <c r="CR95" t="n">
-        <v>94.41336835493851</v>
+        <v>94.41336835493848</v>
       </c>
       <c r="CS95" t="n">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>0</v>
       </c>
       <c r="CU95" t="n">
-        <v>4.804470811608065</v>
+        <v>4.804470811608063</v>
       </c>
       <c r="CV95" t="n">
         <v>0.3694732952912681</v>
@@ -46184,10 +46184,10 @@
         <v>0</v>
       </c>
       <c r="DD95" t="n">
-        <v>4.313666444028179</v>
+        <v>4.313666444028176</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.4071549990405718</v>
+        <v>0.407154999040572</v>
       </c>
       <c r="DF95" t="n">
         <v>0</v>
@@ -46196,7 +46196,7 @@
         <v>0</v>
       </c>
       <c r="DH95" t="n">
-        <v>0.01688092039964901</v>
+        <v>0.016880920399649</v>
       </c>
       <c r="DJ95" t="n">
         <v>0.3370917617174677</v>
@@ -46449,16 +46449,16 @@
         <v>4.256605722329833</v>
       </c>
       <c r="W96" t="n">
-        <v>4048.006395189134</v>
+        <v>4048.006395189133</v>
       </c>
       <c r="X96" t="n">
-        <v>3333.026459658039</v>
+        <v>3333.026459658038</v>
       </c>
       <c r="Z96" t="n">
         <v>2000.901384206414</v>
       </c>
       <c r="AA96" t="n">
-        <v>3333.026459658039</v>
+        <v>3333.026459658038</v>
       </c>
       <c r="AB96" t="n">
         <v>0.6003256825064937</v>
@@ -46536,19 +46536,19 @@
         <v>4.001422209276159</v>
       </c>
       <c r="BD96" t="n">
-        <v>3992.866491248631</v>
+        <v>3992.866491248632</v>
       </c>
       <c r="BE96" t="n">
-        <v>3287.625652229692</v>
+        <v>3287.625652229693</v>
       </c>
       <c r="BG96" t="n">
-        <v>2038.223672342855</v>
+        <v>2038.223672342854</v>
       </c>
       <c r="BH96" t="n">
-        <v>3287.625652229692</v>
+        <v>3287.625652229693</v>
       </c>
       <c r="BI96" t="n">
-        <v>0.619968295648416</v>
+        <v>0.6199682956484159</v>
       </c>
       <c r="BK96" t="n">
         <v>1906.822878293221</v>
@@ -46575,7 +46575,7 @@
         <v>0</v>
       </c>
       <c r="BT96" t="n">
-        <v>2038.223672342855</v>
+        <v>2038.223672342854</v>
       </c>
       <c r="BU96" t="n">
         <v>0</v>
@@ -46587,7 +46587,7 @@
         <v>0</v>
       </c>
       <c r="BX96" t="n">
-        <v>0.619968295648416</v>
+        <v>0.6199682956484159</v>
       </c>
       <c r="BY96" t="n">
         <v>0</v>
@@ -46623,19 +46623,19 @@
         <v>3.792227856175201</v>
       </c>
       <c r="CK96" t="n">
-        <v>3974.201500630857</v>
+        <v>3974.201500630856</v>
       </c>
       <c r="CL96" t="n">
-        <v>3272.257369296086</v>
+        <v>3272.257369296085</v>
       </c>
       <c r="CN96" t="n">
         <v>2091.472532821207</v>
       </c>
       <c r="CO96" t="n">
-        <v>3272.257369296086</v>
+        <v>3272.257369296085</v>
       </c>
       <c r="CP96" t="n">
-        <v>0.6391528222827764</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="CR96" t="n">
         <v>1897.90927419173</v>
@@ -46674,7 +46674,7 @@
         <v>0</v>
       </c>
       <c r="DE96" t="n">
-        <v>0.6391528222827764</v>
+        <v>0.6391528222827766</v>
       </c>
       <c r="DF96" t="n">
         <v>0</v>
@@ -47032,7 +47032,7 @@
         <v>0</v>
       </c>
       <c r="BH97" t="n">
-        <v>17.64257244786237</v>
+        <v>17.64257244786238</v>
       </c>
       <c r="BI97" t="n">
         <v>0</v>
@@ -47119,7 +47119,7 @@
         <v>0</v>
       </c>
       <c r="CO97" t="n">
-        <v>17.6090540716272</v>
+        <v>17.60905407162719</v>
       </c>
       <c r="CP97" t="n">
         <v>0</v>
@@ -47432,7 +47432,7 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>657.8625451005828</v>
+        <v>657.8625451005827</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
@@ -47606,7 +47606,7 @@
         <v>0</v>
       </c>
       <c r="CO98" t="n">
-        <v>680.3445620672948</v>
+        <v>680.3445620672945</v>
       </c>
       <c r="CP98" t="n">
         <v>0</v>
@@ -47910,16 +47910,16 @@
         <v>1.21370812127122</v>
       </c>
       <c r="W99" t="n">
-        <v>39.37851135013746</v>
+        <v>39.37851135013744</v>
       </c>
       <c r="X99" t="n">
-        <v>32.81542612511455</v>
+        <v>32.81542612511454</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>32.81542612511455</v>
+        <v>32.81542612511454</v>
       </c>
       <c r="AB99" t="n">
         <v>0</v>
@@ -47997,16 +47997,16 @@
         <v>1.312115575743891</v>
       </c>
       <c r="BD99" t="n">
-        <v>44.66936435324928</v>
+        <v>44.66936435324929</v>
       </c>
       <c r="BE99" t="n">
-        <v>37.2244702943744</v>
+        <v>37.22447029437441</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
       </c>
       <c r="BH99" t="n">
-        <v>37.2244702943744</v>
+        <v>37.22447029437441</v>
       </c>
       <c r="BI99" t="n">
         <v>0</v>
@@ -48084,16 +48084,16 @@
         <v>1.40351754675021</v>
       </c>
       <c r="CK99" t="n">
-        <v>50.1811461354701</v>
+        <v>50.18114613547009</v>
       </c>
       <c r="CL99" t="n">
-        <v>41.81762177955843</v>
+        <v>41.81762177955842</v>
       </c>
       <c r="CN99" t="n">
         <v>0</v>
       </c>
       <c r="CO99" t="n">
-        <v>41.81762177955843</v>
+        <v>41.81762177955842</v>
       </c>
       <c r="CP99" t="n">
         <v>0</v>
@@ -48406,7 +48406,7 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>4036.81935165459</v>
+        <v>4036.819351654589</v>
       </c>
       <c r="AB100" t="n">
         <v>0</v>
@@ -48580,7 +48580,7 @@
         <v>0</v>
       </c>
       <c r="CO100" t="n">
-        <v>4387.416224273983</v>
+        <v>4387.416224273981</v>
       </c>
       <c r="CP100" t="n">
         <v>0</v>
@@ -48893,7 +48893,7 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>4285.3405495293</v>
+        <v>4285.340549529298</v>
       </c>
       <c r="AB101" t="n">
         <v>0</v>
@@ -48980,7 +48980,7 @@
         <v>0</v>
       </c>
       <c r="BH101" t="n">
-        <v>3430.387548802655</v>
+        <v>3430.387548802653</v>
       </c>
       <c r="BI101" t="n">
         <v>0</v>
@@ -49067,7 +49067,7 @@
         <v>0</v>
       </c>
       <c r="CO101" t="n">
-        <v>491.4275754348321</v>
+        <v>491.4275754348319</v>
       </c>
       <c r="CP101" t="n">
         <v>0</v>
@@ -49241,7 +49241,7 @@
         <v>0</v>
       </c>
       <c r="FC101" t="n">
-        <v>53.91632660474394</v>
+        <v>53.91632660474392</v>
       </c>
       <c r="FD101" t="n">
         <v>0</v>
@@ -49554,7 +49554,7 @@
         <v>0</v>
       </c>
       <c r="CO102" t="n">
-        <v>1160.589604797387</v>
+        <v>1160.589604797386</v>
       </c>
       <c r="CP102" t="n">
         <v>0</v>
@@ -51815,7 +51815,7 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>242967.513342648</v>
+        <v>242967.5133426479</v>
       </c>
       <c r="AB107" t="n">
         <v>0</v>
@@ -51902,7 +51902,7 @@
         <v>0</v>
       </c>
       <c r="BH107" t="n">
-        <v>258952.1503084711</v>
+        <v>258952.150308471</v>
       </c>
       <c r="BI107" t="n">
         <v>0</v>
@@ -51989,7 +51989,7 @@
         <v>0</v>
       </c>
       <c r="CO107" t="n">
-        <v>178371.9226501163</v>
+        <v>178371.9226501162</v>
       </c>
       <c r="CP107" t="n">
         <v>0</v>
@@ -52163,7 +52163,7 @@
         <v>0</v>
       </c>
       <c r="FC107" t="n">
-        <v>131086.2067667197</v>
+        <v>131086.2067667196</v>
       </c>
       <c r="FD107" t="n">
         <v>0</v>
@@ -52302,7 +52302,7 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>20247.292778554</v>
+        <v>20247.29277855399</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
@@ -52389,7 +52389,7 @@
         <v>0</v>
       </c>
       <c r="BH108" t="n">
-        <v>21579.34585903926</v>
+        <v>21579.34585903925</v>
       </c>
       <c r="BI108" t="n">
         <v>0</v>
@@ -52780,16 +52780,16 @@
         <v>0.9981113886434008</v>
       </c>
       <c r="W109" t="n">
-        <v>613.7908932264191</v>
+        <v>613.7908932264189</v>
       </c>
       <c r="X109" t="n">
-        <v>511.4924110220159</v>
+        <v>511.4924110220158</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>511.4924110220159</v>
+        <v>511.4924110220158</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -52867,16 +52867,16 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="BD109" t="n">
-        <v>642.2177283872487</v>
+        <v>642.2177283872488</v>
       </c>
       <c r="BE109" t="n">
-        <v>535.1814403227073</v>
+        <v>535.1814403227074</v>
       </c>
       <c r="BG109" t="n">
         <v>0</v>
       </c>
       <c r="BH109" t="n">
-        <v>535.1814403227073</v>
+        <v>535.1814403227074</v>
       </c>
       <c r="BI109" t="n">
         <v>0</v>
@@ -52954,16 +52954,16 @@
         <v>0.9904994042258208</v>
       </c>
       <c r="CK109" t="n">
-        <v>671.2330650106408</v>
+        <v>671.2330650106406</v>
       </c>
       <c r="CL109" t="n">
-        <v>559.3608875088673</v>
+        <v>559.3608875088671</v>
       </c>
       <c r="CN109" t="n">
         <v>0</v>
       </c>
       <c r="CO109" t="n">
-        <v>559.3608875088673</v>
+        <v>559.3608875088671</v>
       </c>
       <c r="CP109" t="n">
         <v>0</v>
@@ -53267,16 +53267,16 @@
         <v>0.05278624599262982</v>
       </c>
       <c r="W110" t="n">
-        <v>22.71474003074618</v>
+        <v>22.71474003074617</v>
       </c>
       <c r="X110" t="n">
-        <v>18.92895002562182</v>
+        <v>18.92895002562181</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>18.92895002562182</v>
+        <v>18.92895002562181</v>
       </c>
       <c r="AB110" t="n">
         <v>0</v>
@@ -53354,7 +53354,7 @@
         <v>0.05409428916832715</v>
       </c>
       <c r="BD110" t="n">
-        <v>25.19357875867747</v>
+        <v>25.19357875867748</v>
       </c>
       <c r="BE110" t="n">
         <v>20.99464896556456</v>
@@ -53444,13 +53444,13 @@
         <v>27.74393801061093</v>
       </c>
       <c r="CL110" t="n">
-        <v>23.11994834217578</v>
+        <v>23.11994834217577</v>
       </c>
       <c r="CN110" t="n">
         <v>0</v>
       </c>
       <c r="CO110" t="n">
-        <v>23.11994834217578</v>
+        <v>23.11994834217577</v>
       </c>
       <c r="CP110" t="n">
         <v>0</v>
@@ -53754,16 +53754,16 @@
         <v>0.2111449839705193</v>
       </c>
       <c r="W111" t="n">
-        <v>75.08252104376521</v>
+        <v>75.0825210437652</v>
       </c>
       <c r="X111" t="n">
-        <v>62.56876753647101</v>
+        <v>62.568767536471</v>
       </c>
       <c r="Z111" t="n">
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>62.56876753647101</v>
+        <v>62.568767536471</v>
       </c>
       <c r="AB111" t="n">
         <v>0</v>
@@ -53841,7 +53841,7 @@
         <v>0.2163771566733086</v>
       </c>
       <c r="BD111" t="n">
-        <v>84.48008261179825</v>
+        <v>84.48008261179827</v>
       </c>
       <c r="BE111" t="n">
         <v>70.40006884316522</v>
@@ -53928,16 +53928,16 @@
         <v>0.2217389826156735</v>
       </c>
       <c r="CK111" t="n">
-        <v>94.22373308320088</v>
+        <v>94.22373308320086</v>
       </c>
       <c r="CL111" t="n">
-        <v>78.51977756933408</v>
+        <v>78.51977756933405</v>
       </c>
       <c r="CN111" t="n">
         <v>0</v>
       </c>
       <c r="CO111" t="n">
-        <v>78.51977756933408</v>
+        <v>78.51977756933405</v>
       </c>
       <c r="CP111" t="n">
         <v>0</v>
@@ -54241,7 +54241,7 @@
         <v>1.085372767898625</v>
       </c>
       <c r="W112" t="n">
-        <v>2655.596526238001</v>
+        <v>2655.596526238</v>
       </c>
       <c r="X112" t="n">
         <v>2286.263479778516</v>
@@ -54280,7 +54280,7 @@
         <v>0.04552894664608176</v>
       </c>
       <c r="AM112" t="n">
-        <v>356.6923122419544</v>
+        <v>356.6923122419543</v>
       </c>
       <c r="AN112" t="n">
         <v>0</v>
@@ -54289,7 +54289,7 @@
         <v>0</v>
       </c>
       <c r="AP112" t="n">
-        <v>103.3545208665763</v>
+        <v>103.3545208665762</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.1560154004106776</v>
@@ -54328,22 +54328,22 @@
         <v>1.113570752408632</v>
       </c>
       <c r="BD112" t="n">
-        <v>2918.647770100829</v>
+        <v>2918.647770100828</v>
       </c>
       <c r="BE112" t="n">
-        <v>2512.730281573088</v>
+        <v>2512.730281573087</v>
       </c>
       <c r="BG112" t="n">
-        <v>560.2546647851856</v>
+        <v>560.2546647851854</v>
       </c>
       <c r="BH112" t="n">
-        <v>2512.730281573088</v>
+        <v>2512.730281573087</v>
       </c>
       <c r="BI112" t="n">
         <v>0.2229664954069163</v>
       </c>
       <c r="BK112" t="n">
-        <v>376.9095422359632</v>
+        <v>376.9095422359631</v>
       </c>
       <c r="BL112" t="n">
         <v>0</v>
@@ -54352,7 +54352,7 @@
         <v>0</v>
       </c>
       <c r="BN112" t="n">
-        <v>154.4538787504516</v>
+        <v>154.4538787504515</v>
       </c>
       <c r="BO112" t="n">
         <v>0.15</v>
@@ -54367,7 +54367,7 @@
         <v>0.06146854673704021</v>
       </c>
       <c r="BT112" t="n">
-        <v>408.0529508182531</v>
+        <v>408.052950818253</v>
       </c>
       <c r="BU112" t="n">
         <v>0</v>
@@ -54376,7 +54376,7 @@
         <v>0</v>
       </c>
       <c r="BW112" t="n">
-        <v>152.2017139669325</v>
+        <v>152.2017139669324</v>
       </c>
       <c r="BX112" t="n">
         <v>0.162394250513347</v>
@@ -54415,22 +54415,22 @@
         <v>1.14741216757433</v>
       </c>
       <c r="CK112" t="n">
-        <v>3213.880941078058</v>
+        <v>3213.880941078057</v>
       </c>
       <c r="CL112" t="n">
-        <v>2766.903236747361</v>
+        <v>2766.90323674736</v>
       </c>
       <c r="CN112" t="n">
-        <v>671.6988663054449</v>
+        <v>671.6988663054447</v>
       </c>
       <c r="CO112" t="n">
-        <v>2766.903236747361</v>
+        <v>2766.90323674736</v>
       </c>
       <c r="CP112" t="n">
         <v>0.2427619648510231</v>
       </c>
       <c r="CR112" t="n">
-        <v>415.0354855121041</v>
+        <v>415.0354855121039</v>
       </c>
       <c r="CS112" t="n">
         <v>0</v>
@@ -54454,7 +54454,7 @@
         <v>0.0752495132522663</v>
       </c>
       <c r="DA112" t="n">
-        <v>468.1970786504062</v>
+        <v>468.197078650406</v>
       </c>
       <c r="DB112" t="n">
         <v>0</v>
@@ -54463,7 +54463,7 @@
         <v>0</v>
       </c>
       <c r="DD112" t="n">
-        <v>203.5017876550388</v>
+        <v>203.5017876550387</v>
       </c>
       <c r="DE112" t="n">
         <v>0.1692133907800825</v>
@@ -54475,7 +54475,7 @@
         <v>0</v>
       </c>
       <c r="DH112" t="n">
-        <v>0.07354857407094066</v>
+        <v>0.07354857407094068</v>
       </c>
       <c r="DJ112" t="n">
         <v>1.170681686332737</v>
@@ -54505,19 +54505,19 @@
         <v>3496.919089752774</v>
       </c>
       <c r="DS112" t="n">
-        <v>3010.577219713375</v>
+        <v>3010.577219713374</v>
       </c>
       <c r="DU112" t="n">
-        <v>778.8712443416856</v>
+        <v>778.8712443416855</v>
       </c>
       <c r="DV112" t="n">
-        <v>3010.577219713375</v>
+        <v>3010.577219713374</v>
       </c>
       <c r="DW112" t="n">
-        <v>0.2587115983079946</v>
+        <v>0.2587115983079945</v>
       </c>
       <c r="DY112" t="n">
-        <v>451.5865829570062</v>
+        <v>451.5865829570061</v>
       </c>
       <c r="DZ112" t="n">
         <v>0</v>
@@ -54541,7 +54541,7 @@
         <v>0.08719289309748272</v>
       </c>
       <c r="EH112" t="n">
-        <v>523.7754294563839</v>
+        <v>523.7754294563838</v>
       </c>
       <c r="EI112" t="n">
         <v>0</v>
@@ -54562,7 +54562,7 @@
         <v>0</v>
       </c>
       <c r="EO112" t="n">
-        <v>0.08473319110200016</v>
+        <v>0.08473319110200017</v>
       </c>
       <c r="EQ112" t="n">
         <v>1.194423110931565</v>
@@ -54589,22 +54589,22 @@
         <v>1.194423110931565</v>
       </c>
       <c r="EY112" t="n">
-        <v>3804.88367318781</v>
+        <v>3804.883673187809</v>
       </c>
       <c r="EZ112" t="n">
-        <v>3275.710937586609</v>
+        <v>3275.710937586608</v>
       </c>
       <c r="FB112" t="n">
-        <v>897.8191132628685</v>
+        <v>897.8191132628683</v>
       </c>
       <c r="FC112" t="n">
-        <v>3275.710937586609</v>
+        <v>3275.710937586608</v>
       </c>
       <c r="FD112" t="n">
         <v>0.2740837425430279</v>
       </c>
       <c r="FF112" t="n">
-        <v>491.3566406379914</v>
+        <v>491.3566406379913</v>
       </c>
       <c r="FG112" t="n">
         <v>0</v>
@@ -54613,7 +54613,7 @@
         <v>0</v>
       </c>
       <c r="FI112" t="n">
-        <v>324.1386612664957</v>
+        <v>324.1386612664956</v>
       </c>
       <c r="FJ112" t="n">
         <v>0.15</v>
@@ -54628,7 +54628,7 @@
         <v>0.09895215647608575</v>
       </c>
       <c r="FO112" t="n">
-        <v>584.5267898608433</v>
+        <v>584.5267898608432</v>
       </c>
       <c r="FP112" t="n">
         <v>0</v>
@@ -54637,7 +54637,7 @@
         <v>0</v>
       </c>
       <c r="FR112" t="n">
-        <v>313.2923234020253</v>
+        <v>313.2923234020251</v>
       </c>
       <c r="FS112" t="n">
         <v>0.1784427261739693</v>
@@ -54728,22 +54728,22 @@
         <v>3.256118303695876</v>
       </c>
       <c r="W113" t="n">
-        <v>8029.727873575058</v>
+        <v>8029.727873575055</v>
       </c>
       <c r="X113" t="n">
-        <v>6611.463838122345</v>
+        <v>6611.463838122343</v>
       </c>
       <c r="Z113" t="n">
         <v>1132.813898112387</v>
       </c>
       <c r="AA113" t="n">
-        <v>6611.463838122345</v>
+        <v>6611.463838122343</v>
       </c>
       <c r="AB113" t="n">
         <v>0.1713408597322233</v>
       </c>
       <c r="AD113" t="n">
-        <v>991.7195757183517</v>
+        <v>991.7195757183514</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -54815,16 +54815,16 @@
         <v>3.340712257225895</v>
       </c>
       <c r="BD113" t="n">
-        <v>8650.257213917066</v>
+        <v>8650.257213917062</v>
       </c>
       <c r="BE113" t="n">
-        <v>7122.391152068602</v>
+        <v>7122.3911520686</v>
       </c>
       <c r="BG113" t="n">
-        <v>1264.964301704895</v>
+        <v>1264.964301704894</v>
       </c>
       <c r="BH113" t="n">
-        <v>7122.391152068602</v>
+        <v>7122.3911520686</v>
       </c>
       <c r="BI113" t="n">
         <v>0.1776038797500616</v>
@@ -54854,7 +54854,7 @@
         <v>0.01543468972023027</v>
       </c>
       <c r="BT113" t="n">
-        <v>1156.635373003075</v>
+        <v>1156.635373003074</v>
       </c>
       <c r="BU113" t="n">
         <v>0</v>
@@ -54902,22 +54902,22 @@
         <v>3.442236502722989</v>
       </c>
       <c r="CK113" t="n">
-        <v>9358.795457180408</v>
+        <v>9358.795457180402</v>
       </c>
       <c r="CL113" t="n">
-        <v>7705.782650138966</v>
+        <v>7705.782650138964</v>
       </c>
       <c r="CN113" t="n">
         <v>1420.169538813218</v>
       </c>
       <c r="CO113" t="n">
-        <v>7705.782650138966</v>
+        <v>7705.782650138964</v>
       </c>
       <c r="CP113" t="n">
         <v>0.184299194941296</v>
       </c>
       <c r="CR113" t="n">
-        <v>1155.867397520845</v>
+        <v>1155.867397520844</v>
       </c>
       <c r="CS113" t="n">
         <v>0</v>
@@ -54926,7 +54926,7 @@
         <v>0</v>
       </c>
       <c r="CU113" t="n">
-        <v>118.9363642564281</v>
+        <v>118.936364256428</v>
       </c>
       <c r="CV113" t="n">
         <v>0.15</v>
@@ -54992,16 +54992,16 @@
         <v>10026.02142050462</v>
       </c>
       <c r="DS113" t="n">
-        <v>8255.15871839797</v>
+        <v>8255.158718397968</v>
       </c>
       <c r="DU113" t="n">
-        <v>1560.040792282903</v>
+        <v>1560.040792282902</v>
       </c>
       <c r="DV113" t="n">
-        <v>8255.15871839797</v>
+        <v>8255.158718397968</v>
       </c>
       <c r="DW113" t="n">
-        <v>0.1889776860142127</v>
+        <v>0.1889776860142128</v>
       </c>
       <c r="DY113" t="n">
         <v>1238.273807759695</v>
@@ -55040,7 +55040,7 @@
         <v>123.8214272233462</v>
       </c>
       <c r="EL113" t="n">
-        <v>0.1739784072059943</v>
+        <v>0.1739784072059944</v>
       </c>
       <c r="EM113" t="n">
         <v>0</v>
@@ -55079,13 +55079,13 @@
         <v>10740.81659165808</v>
       </c>
       <c r="EZ113" t="n">
-        <v>8843.702004067442</v>
+        <v>8843.702004067438</v>
       </c>
       <c r="FB113" t="n">
-        <v>1710.026531096219</v>
+        <v>1710.026531096218</v>
       </c>
       <c r="FC113" t="n">
-        <v>8843.702004067442</v>
+        <v>8843.702004067438</v>
       </c>
       <c r="FD113" t="n">
         <v>0.193360939831502</v>
@@ -55124,7 +55124,7 @@
         <v>0</v>
       </c>
       <c r="FR113" t="n">
-        <v>131.9322360202294</v>
+        <v>131.9322360202293</v>
       </c>
       <c r="FS113" t="n">
         <v>0.1784427261739692</v>
@@ -55215,19 +55215,19 @@
         <v>1.21370812127122</v>
       </c>
       <c r="W114" t="n">
-        <v>285.1022995201959</v>
+        <v>285.1022995201958</v>
       </c>
       <c r="X114" t="n">
-        <v>231.5160736801713</v>
+        <v>231.5160736801712</v>
       </c>
       <c r="Z114" t="n">
         <v>148.5702204566016</v>
       </c>
       <c r="AA114" t="n">
-        <v>231.5160736801713</v>
+        <v>231.5160736801712</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.641727453713838</v>
+        <v>0.6417274537138381</v>
       </c>
       <c r="AD114" t="n">
         <v>143.5399656817062</v>
@@ -55266,7 +55266,7 @@
         <v>0</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.641727453713838</v>
+        <v>0.6417274537138381</v>
       </c>
       <c r="AR114" t="n">
         <v>0</v>
@@ -55314,7 +55314,7 @@
         <v>256.2058274656652</v>
       </c>
       <c r="BI114" t="n">
-        <v>0.6627247298310656</v>
+        <v>0.6627247298310653</v>
       </c>
       <c r="BK114" t="n">
         <v>158.8476130287124</v>
@@ -55353,7 +55353,7 @@
         <v>0</v>
       </c>
       <c r="BX114" t="n">
-        <v>0.6627247298310656</v>
+        <v>0.6627247298310653</v>
       </c>
       <c r="BY114" t="n">
         <v>0</v>
@@ -55401,10 +55401,10 @@
         <v>113.8366434244752</v>
       </c>
       <c r="CP114" t="n">
-        <v>0.4207268323419242</v>
+        <v>0.4207268323419244</v>
       </c>
       <c r="CR114" t="n">
-        <v>43.46158642996919</v>
+        <v>43.46158642996917</v>
       </c>
       <c r="CS114" t="n">
         <v>0</v>
@@ -55440,7 +55440,7 @@
         <v>0</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.4207268323419242</v>
+        <v>0.4207268323419244</v>
       </c>
       <c r="DF114" t="n">
         <v>0</v>
@@ -55885,7 +55885,7 @@
         <v>0</v>
       </c>
       <c r="CO115" t="n">
-        <v>1480.157280926399</v>
+        <v>1480.157280926398</v>
       </c>
       <c r="CP115" t="n">
         <v>0</v>
@@ -56372,7 +56372,7 @@
         <v>0</v>
       </c>
       <c r="CO116" t="n">
-        <v>1637.117611983247</v>
+        <v>1637.117611983246</v>
       </c>
       <c r="CP116" t="n">
         <v>0</v>
@@ -56685,7 +56685,7 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>7428.72023606592</v>
+        <v>7428.720236065918</v>
       </c>
       <c r="AB117" t="n">
         <v>0</v>
@@ -56772,7 +56772,7 @@
         <v>0</v>
       </c>
       <c r="BH117" t="n">
-        <v>7828.511175809695</v>
+        <v>7828.511175809696</v>
       </c>
       <c r="BI117" t="n">
         <v>0</v>
@@ -56859,7 +56859,7 @@
         <v>0</v>
       </c>
       <c r="CO117" t="n">
-        <v>8219.285471184019</v>
+        <v>8219.285471184015</v>
       </c>
       <c r="CP117" t="n">
         <v>0</v>
@@ -57172,7 +57172,7 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>4952.48015737728</v>
+        <v>4952.480157377279</v>
       </c>
       <c r="AB118" t="n">
         <v>0</v>
@@ -57259,7 +57259,7 @@
         <v>0</v>
       </c>
       <c r="BH118" t="n">
-        <v>5219.007450539796</v>
+        <v>5219.007450539797</v>
       </c>
       <c r="BI118" t="n">
         <v>0</v>
@@ -57346,7 +57346,7 @@
         <v>0</v>
       </c>
       <c r="CO118" t="n">
-        <v>5479.523647456012</v>
+        <v>5479.523647456011</v>
       </c>
       <c r="CP118" t="n">
         <v>0</v>
@@ -58140,13 +58140,13 @@
         <v>3766.039352466853</v>
       </c>
       <c r="X120" t="n">
-        <v>3138.366127055711</v>
+        <v>3138.36612705571</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>3138.366127055711</v>
+        <v>3138.36612705571</v>
       </c>
       <c r="AB120" t="n">
         <v>0</v>
@@ -58224,7 +58224,7 @@
         <v>3.385108307766891</v>
       </c>
       <c r="BD120" t="n">
-        <v>4106.822096285046</v>
+        <v>4106.822096285047</v>
       </c>
       <c r="BE120" t="n">
         <v>3422.351746904206</v>
@@ -58311,16 +58311,16 @@
         <v>3.509815697825024</v>
       </c>
       <c r="CK120" t="n">
-        <v>4472.009131265238</v>
+        <v>4472.009131265237</v>
       </c>
       <c r="CL120" t="n">
-        <v>3726.674276054365</v>
+        <v>3726.674276054364</v>
       </c>
       <c r="CN120" t="n">
         <v>0</v>
       </c>
       <c r="CO120" t="n">
-        <v>3726.674276054365</v>
+        <v>3726.674276054364</v>
       </c>
       <c r="CP120" t="n">
         <v>0</v>
@@ -58711,16 +58711,16 @@
         <v>0.9952867334135399</v>
       </c>
       <c r="BD121" t="n">
-        <v>307.0505645122963</v>
+        <v>307.0505645122964</v>
       </c>
       <c r="BE121" t="n">
-        <v>255.8754704269136</v>
+        <v>255.8754704269137</v>
       </c>
       <c r="BG121" t="n">
         <v>0</v>
       </c>
       <c r="BH121" t="n">
-        <v>255.8754704269136</v>
+        <v>255.8754704269137</v>
       </c>
       <c r="BI121" t="n">
         <v>0</v>
@@ -58798,7 +58798,7 @@
         <v>0.9904994042258208</v>
       </c>
       <c r="CK121" t="n">
-        <v>327.4784689495373</v>
+        <v>327.4784689495372</v>
       </c>
       <c r="CL121" t="n">
         <v>272.8987241246144</v>
@@ -59114,13 +59114,13 @@
         <v>118.5234187313462</v>
       </c>
       <c r="X122" t="n">
-        <v>98.76951560945518</v>
+        <v>98.76951560945515</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>98.76951560945518</v>
+        <v>98.76951560945515</v>
       </c>
       <c r="AB122" t="n">
         <v>0</v>
@@ -59288,13 +59288,13 @@
         <v>125.1254177316974</v>
       </c>
       <c r="CL122" t="n">
-        <v>104.2711814430812</v>
+        <v>104.2711814430811</v>
       </c>
       <c r="CN122" t="n">
         <v>0</v>
       </c>
       <c r="CO122" t="n">
-        <v>104.2711814430812</v>
+        <v>104.2711814430811</v>
       </c>
       <c r="CP122" t="n">
         <v>0</v>
@@ -59772,7 +59772,7 @@
         <v>1.980998808451642</v>
       </c>
       <c r="CK123" t="n">
-        <v>126.705576024011</v>
+        <v>126.7055760240109</v>
       </c>
       <c r="CL123" t="n">
         <v>105.5879800200091</v>
@@ -60085,7 +60085,7 @@
         <v>4.990556943217004</v>
       </c>
       <c r="W124" t="n">
-        <v>1895.650632939567</v>
+        <v>1895.650632939566</v>
       </c>
       <c r="X124" t="n">
         <v>1579.708860782972</v>
@@ -60262,13 +60262,13 @@
         <v>1970.255948434851</v>
       </c>
       <c r="CL124" t="n">
-        <v>1641.879957029043</v>
+        <v>1641.879957029042</v>
       </c>
       <c r="CN124" t="n">
         <v>0</v>
       </c>
       <c r="CO124" t="n">
-        <v>1641.879957029043</v>
+        <v>1641.879957029042</v>
       </c>
       <c r="CP124" t="n">
         <v>0</v>
@@ -61068,7 +61068,7 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>7988.509832829463</v>
+        <v>7988.509832829461</v>
       </c>
       <c r="AB126" t="n">
         <v>0</v>
@@ -61155,7 +61155,7 @@
         <v>0</v>
       </c>
       <c r="BH126" t="n">
-        <v>8533.876289603424</v>
+        <v>8533.876289603426</v>
       </c>
       <c r="BI126" t="n">
         <v>0</v>
@@ -61242,7 +61242,7 @@
         <v>0</v>
       </c>
       <c r="CO126" t="n">
-        <v>6873.833000881652</v>
+        <v>6873.833000881649</v>
       </c>
       <c r="CP126" t="n">
         <v>0</v>
@@ -61555,7 +61555,7 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>4909.238051776442</v>
+        <v>4909.23805177644</v>
       </c>
       <c r="AB127" t="n">
         <v>0</v>
@@ -61642,7 +61642,7 @@
         <v>0</v>
       </c>
       <c r="BH127" t="n">
-        <v>4997.458540673324</v>
+        <v>4997.458540673325</v>
       </c>
       <c r="BI127" t="n">
         <v>0</v>
@@ -61729,7 +61729,7 @@
         <v>0</v>
       </c>
       <c r="CO127" t="n">
-        <v>5060.084660832046</v>
+        <v>5060.084660832044</v>
       </c>
       <c r="CP127" t="n">
         <v>0</v>
@@ -62216,7 +62216,7 @@
         <v>0</v>
       </c>
       <c r="CO128" t="n">
-        <v>1890.353320720159</v>
+        <v>1890.353320720158</v>
       </c>
       <c r="CP128" t="n">
         <v>0</v>
@@ -62529,7 +62529,7 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>8290.717350099087</v>
+        <v>8290.717350099085</v>
       </c>
       <c r="AB129" t="n">
         <v>0</v>
@@ -62616,7 +62616,7 @@
         <v>0</v>
       </c>
       <c r="BH129" t="n">
-        <v>8660.686703747151</v>
+        <v>8660.686703747147</v>
       </c>
       <c r="BI129" t="n">
         <v>0</v>
@@ -62703,7 +62703,7 @@
         <v>0</v>
       </c>
       <c r="CO129" t="n">
-        <v>9046.67391576051</v>
+        <v>9046.673915760506</v>
       </c>
       <c r="CP129" t="n">
         <v>0</v>
@@ -62790,7 +62790,7 @@
         <v>0</v>
       </c>
       <c r="DV129" t="n">
-        <v>9443.49467879881</v>
+        <v>9443.494678798808</v>
       </c>
       <c r="DW129" t="n">
         <v>0</v>
@@ -62877,7 +62877,7 @@
         <v>0</v>
       </c>
       <c r="FC129" t="n">
-        <v>9844.244018088732</v>
+        <v>9844.244018088728</v>
       </c>
       <c r="FD129" t="n">
         <v>0</v>
@@ -63097,13 +63097,13 @@
         <v>51.29941359750353</v>
       </c>
       <c r="BE130" t="n">
-        <v>42.74951133125294</v>
+        <v>42.74951133125295</v>
       </c>
       <c r="BG130" t="n">
         <v>0</v>
       </c>
       <c r="BH130" t="n">
-        <v>42.74951133125294</v>
+        <v>42.74951133125295</v>
       </c>
       <c r="BI130" t="n">
         <v>0</v>
@@ -63181,16 +63181,16 @@
         <v>0.03484188184547284</v>
       </c>
       <c r="CK130" t="n">
-        <v>41.46020597483334</v>
+        <v>41.46020597483333</v>
       </c>
       <c r="CL130" t="n">
-        <v>34.55017164569445</v>
+        <v>34.55017164569444</v>
       </c>
       <c r="CN130" t="n">
         <v>0</v>
       </c>
       <c r="CO130" t="n">
-        <v>34.55017164569445</v>
+        <v>34.55017164569444</v>
       </c>
       <c r="CP130" t="n">
         <v>0</v>
@@ -63494,16 +63494,16 @@
         <v>0.3106181476608478</v>
       </c>
       <c r="W131" t="n">
-        <v>351.2039441239848</v>
+        <v>351.2039441239847</v>
       </c>
       <c r="X131" t="n">
-        <v>292.669953436654</v>
+        <v>292.6699534366539</v>
       </c>
       <c r="Z131" t="n">
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>292.669953436654</v>
+        <v>292.6699534366539</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
@@ -63584,13 +63584,13 @@
         <v>111.5204724267195</v>
       </c>
       <c r="BE131" t="n">
-        <v>92.93372702226621</v>
+        <v>92.93372702226623</v>
       </c>
       <c r="BG131" t="n">
         <v>0</v>
       </c>
       <c r="BH131" t="n">
-        <v>92.93372702226621</v>
+        <v>92.93372702226623</v>
       </c>
       <c r="BI131" t="n">
         <v>0</v>
@@ -63668,16 +63668,16 @@
         <v>0.06968376369094569</v>
       </c>
       <c r="CK131" t="n">
-        <v>90.131312257715</v>
+        <v>90.13131225771497</v>
       </c>
       <c r="CL131" t="n">
-        <v>75.10942688142917</v>
+        <v>75.10942688142914</v>
       </c>
       <c r="CN131" t="n">
         <v>0</v>
       </c>
       <c r="CO131" t="n">
-        <v>75.10942688142917</v>
+        <v>75.10942688142914</v>
       </c>
       <c r="CP131" t="n">
         <v>0</v>
@@ -63981,16 +63981,16 @@
         <v>0.4046359675316866</v>
       </c>
       <c r="W132" t="n">
-        <v>557.5674048798105</v>
+        <v>557.5674048798104</v>
       </c>
       <c r="X132" t="n">
-        <v>464.6395040665088</v>
+        <v>464.6395040665087</v>
       </c>
       <c r="Z132" t="n">
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>464.6395040665088</v>
+        <v>464.6395040665087</v>
       </c>
       <c r="AB132" t="n">
         <v>0</v>
@@ -64068,16 +64068,16 @@
         <v>0.3674701539139007</v>
       </c>
       <c r="BD132" t="n">
-        <v>518.3283778574039</v>
+        <v>518.328377857404</v>
       </c>
       <c r="BE132" t="n">
-        <v>431.9403148811699</v>
+        <v>431.94031488117</v>
       </c>
       <c r="BG132" t="n">
         <v>0</v>
       </c>
       <c r="BH132" t="n">
-        <v>431.9403148811699</v>
+        <v>431.94031488117</v>
       </c>
       <c r="BI132" t="n">
         <v>0</v>
@@ -64155,16 +64155,16 @@
         <v>0.3349453705909817</v>
       </c>
       <c r="CK132" t="n">
-        <v>483.3881640382707</v>
+        <v>483.3881640382706</v>
       </c>
       <c r="CL132" t="n">
-        <v>402.8234700318924</v>
+        <v>402.8234700318922</v>
       </c>
       <c r="CN132" t="n">
         <v>0</v>
       </c>
       <c r="CO132" t="n">
-        <v>402.8234700318924</v>
+        <v>402.8234700318922</v>
       </c>
       <c r="CP132" t="n">
         <v>0</v>
@@ -64459,7 +64459,7 @@
         <v>3652.477700362169</v>
       </c>
       <c r="T133" t="n">
-        <v>0.01066425519290875</v>
+        <v>0.01066425519290883</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -64468,16 +64468,16 @@
         <v>1.139532478168885</v>
       </c>
       <c r="W133" t="n">
-        <v>4288.031846889131</v>
+        <v>4288.03184688913</v>
       </c>
       <c r="X133" t="n">
-        <v>3617.185517827284</v>
+        <v>3617.185517827283</v>
       </c>
       <c r="Z133" t="n">
         <v>748.7894361180236</v>
       </c>
       <c r="AA133" t="n">
-        <v>3617.185517827284</v>
+        <v>3617.185517827283</v>
       </c>
       <c r="AB133" t="n">
         <v>0.2070088560367219</v>
@@ -64546,7 +64546,7 @@
         <v>4027.027874541495</v>
       </c>
       <c r="BA133" t="n">
-        <v>0.01142475268318756</v>
+        <v>0.01142475268318764</v>
       </c>
       <c r="BB133" t="n">
         <v>0</v>
@@ -64558,19 +64558,19 @@
         <v>4724.679478908309</v>
       </c>
       <c r="BE133" t="n">
-        <v>3985.5212828891</v>
+        <v>3985.521282889101</v>
       </c>
       <c r="BG133" t="n">
-        <v>852.0333920769809</v>
+        <v>852.0333920769808</v>
       </c>
       <c r="BH133" t="n">
-        <v>3985.5212828891</v>
+        <v>3985.521282889101</v>
       </c>
       <c r="BI133" t="n">
-        <v>0.213782170913247</v>
+        <v>0.2137821709132469</v>
       </c>
       <c r="BK133" t="n">
-        <v>797.1042565778201</v>
+        <v>797.1042565778203</v>
       </c>
       <c r="BL133" t="n">
         <v>0</v>
@@ -64594,7 +64594,7 @@
         <v>0</v>
       </c>
       <c r="BT133" t="n">
-        <v>852.0333920769809</v>
+        <v>852.0333920769808</v>
       </c>
       <c r="BU133" t="n">
         <v>0</v>
@@ -64606,7 +64606,7 @@
         <v>0</v>
       </c>
       <c r="BX133" t="n">
-        <v>0.213782170913247</v>
+        <v>0.2137821709132469</v>
       </c>
       <c r="BY133" t="n">
         <v>0</v>
@@ -64633,7 +64633,7 @@
         <v>4439.986998613617</v>
       </c>
       <c r="CH133" t="n">
-        <v>0.01224133621532588</v>
+        <v>0.01224133621532597</v>
       </c>
       <c r="CI133" t="n">
         <v>0</v>
@@ -64642,22 +64642,22 @@
         <v>1.316954763775897</v>
       </c>
       <c r="CK133" t="n">
-        <v>5210.488531095075</v>
+        <v>5210.488531095073</v>
       </c>
       <c r="CL133" t="n">
-        <v>4395.327350275056</v>
+        <v>4395.327350275054</v>
       </c>
       <c r="CN133" t="n">
-        <v>968.7192692362</v>
+        <v>968.7192692361999</v>
       </c>
       <c r="CO133" t="n">
-        <v>4395.327350275056</v>
+        <v>4395.327350275054</v>
       </c>
       <c r="CP133" t="n">
-        <v>0.2203975249250953</v>
+        <v>0.2203975249250954</v>
       </c>
       <c r="CR133" t="n">
-        <v>879.0654700550115</v>
+        <v>879.065470055011</v>
       </c>
       <c r="CS133" t="n">
         <v>0</v>
@@ -64681,7 +64681,7 @@
         <v>0</v>
       </c>
       <c r="DA133" t="n">
-        <v>968.7192692362</v>
+        <v>968.7192692361999</v>
       </c>
       <c r="DB133" t="n">
         <v>0</v>
@@ -64693,7 +64693,7 @@
         <v>0</v>
       </c>
       <c r="DE133" t="n">
-        <v>0.2203975249250953</v>
+        <v>0.2203975249250954</v>
       </c>
       <c r="DF133" t="n">
         <v>0</v>
@@ -64720,7 +64720,7 @@
         <v>1987.407690657162</v>
       </c>
       <c r="DO133" t="n">
-        <v>0.005311887195504962</v>
+        <v>0.005311887195505006</v>
       </c>
       <c r="DP133" t="n">
         <v>0</v>
@@ -64964,7 +64964,7 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>44105.85114788332</v>
+        <v>44105.85114788331</v>
       </c>
       <c r="AB134" t="n">
         <v>0</v>
@@ -65051,7 +65051,7 @@
         <v>0</v>
       </c>
       <c r="BH134" t="n">
-        <v>48644.37436595823</v>
+        <v>48644.3743659582</v>
       </c>
       <c r="BI134" t="n">
         <v>0</v>
@@ -65138,7 +65138,7 @@
         <v>0</v>
       </c>
       <c r="CO134" t="n">
-        <v>53682.72970598954</v>
+        <v>53682.72970598952</v>
       </c>
       <c r="CP134" t="n">
         <v>0</v>
@@ -65225,7 +65225,7 @@
         <v>0</v>
       </c>
       <c r="DV134" t="n">
-        <v>59138.3468595415</v>
+        <v>59138.34685954148</v>
       </c>
       <c r="DW134" t="n">
         <v>0</v>
@@ -65312,7 +65312,7 @@
         <v>0</v>
       </c>
       <c r="FC134" t="n">
-        <v>65059.33148688285</v>
+        <v>65059.33148688282</v>
       </c>
       <c r="FD134" t="n">
         <v>0</v>
@@ -65538,7 +65538,7 @@
         <v>0</v>
       </c>
       <c r="BH135" t="n">
-        <v>5534.287943728713</v>
+        <v>5534.287943728714</v>
       </c>
       <c r="BI135" t="n">
         <v>0</v>
@@ -65625,7 +65625,7 @@
         <v>0</v>
       </c>
       <c r="CO135" t="n">
-        <v>5476.333635195652</v>
+        <v>5476.33363519565</v>
       </c>
       <c r="CP135" t="n">
         <v>0</v>
@@ -65920,7 +65920,7 @@
         <v>1179.685358943432</v>
       </c>
       <c r="T136" t="n">
-        <v>0.01323698547573715</v>
+        <v>0.01323698547573725</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -65929,22 +65929,22 @@
         <v>1.234637796747237</v>
       </c>
       <c r="W136" t="n">
-        <v>1361.266892169666</v>
+        <v>1361.266892169665</v>
       </c>
       <c r="X136" t="n">
         <v>1166.711239701591</v>
       </c>
       <c r="Z136" t="n">
-        <v>314.3940536580223</v>
+        <v>314.3940536580221</v>
       </c>
       <c r="AA136" t="n">
         <v>1166.711239701591</v>
       </c>
       <c r="AB136" t="n">
-        <v>0.269470322183949</v>
+        <v>0.2694703221839489</v>
       </c>
       <c r="AD136" t="n">
-        <v>295.7130914207325</v>
+        <v>295.7130914207323</v>
       </c>
       <c r="AE136" t="n">
         <v>0</v>
@@ -65953,7 +65953,7 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>8.619998910593532</v>
+        <v>8.619998910593527</v>
       </c>
       <c r="AH136" t="n">
         <v>0.2534586805698099</v>
@@ -65968,7 +65968,7 @@
         <v>0.007388288221855359</v>
       </c>
       <c r="AM136" t="n">
-        <v>306.0761438504421</v>
+        <v>306.0761438504418</v>
       </c>
       <c r="AN136" t="n">
         <v>0</v>
@@ -65977,10 +65977,10 @@
         <v>0</v>
       </c>
       <c r="AP136" t="n">
-        <v>8.317909807580218</v>
+        <v>8.317909807580214</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.2623409575866664</v>
+        <v>0.2623409575866663</v>
       </c>
       <c r="AR136" t="n">
         <v>0</v>
@@ -65989,7 +65989,7 @@
         <v>0</v>
       </c>
       <c r="AT136" t="n">
-        <v>0.0071293645972826</v>
+        <v>0.007129364597282601</v>
       </c>
       <c r="AV136" t="n">
         <v>11.13261205799925</v>
@@ -66103,7 +66103,7 @@
         <v>0.06435853514025321</v>
       </c>
       <c r="CK136" t="n">
-        <v>78.36539080275537</v>
+        <v>78.36539080275534</v>
       </c>
       <c r="CL136" t="n">
         <v>0</v>
@@ -66407,7 +66407,7 @@
         <v>4954.678507562416</v>
       </c>
       <c r="T137" t="n">
-        <v>0.07332349543395415</v>
+        <v>0.07332349543395471</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -66416,16 +66416,16 @@
         <v>6.166050415680915</v>
       </c>
       <c r="W137" t="n">
-        <v>5710.709536902687</v>
+        <v>5710.709536902686</v>
       </c>
       <c r="X137" t="n">
-        <v>4894.520715739996</v>
+        <v>4894.520715739995</v>
       </c>
       <c r="Z137" t="n">
         <v>1318.928074206469</v>
       </c>
       <c r="AA137" t="n">
-        <v>4894.520715739996</v>
+        <v>4894.520715739995</v>
       </c>
       <c r="AB137" t="n">
         <v>0.269470322183949</v>
@@ -66440,7 +66440,7 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>36.16212975572888</v>
+        <v>36.16212975572887</v>
       </c>
       <c r="AH137" t="n">
         <v>0.2534586805698099</v>
@@ -66464,7 +66464,7 @@
         <v>0</v>
       </c>
       <c r="AP137" t="n">
-        <v>34.89482271146302</v>
+        <v>34.89482271146301</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.2623409575866664</v>
@@ -66476,7 +66476,7 @@
         <v>0</v>
       </c>
       <c r="AT137" t="n">
-        <v>0.0071293645972826</v>
+        <v>0.007129364597282599</v>
       </c>
       <c r="AV137" t="n">
         <v>46.75697064359685</v>
@@ -66590,7 +66590,7 @@
         <v>0.321792675701266</v>
       </c>
       <c r="CK137" t="n">
-        <v>329.1346413715726</v>
+        <v>329.1346413715725</v>
       </c>
       <c r="CL137" t="n">
         <v>0</v>
@@ -66894,31 +66894,31 @@
         <v>3912.354832482289</v>
       </c>
       <c r="T138" t="n">
-        <v>0.1461146841468762</v>
+        <v>0.1461146841468773</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>6.70950756792204</v>
+        <v>6.709507567922038</v>
       </c>
       <c r="W138" t="n">
-        <v>4486.774537388616</v>
+        <v>4486.774537388614</v>
       </c>
       <c r="X138" t="n">
-        <v>3827.459784399331</v>
+        <v>3827.459784399328</v>
       </c>
       <c r="Z138" t="n">
-        <v>2561.676628446051</v>
+        <v>2561.676628446049</v>
       </c>
       <c r="AA138" t="n">
-        <v>3827.459784399331</v>
+        <v>3827.459784399328</v>
       </c>
       <c r="AB138" t="n">
-        <v>0.6692889730383077</v>
+        <v>0.6692889730383076</v>
       </c>
       <c r="AD138" t="n">
-        <v>2373.025066327586</v>
+        <v>2373.025066327584</v>
       </c>
       <c r="AE138" t="n">
         <v>0</v>
@@ -66927,7 +66927,7 @@
         <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>109.3218052163806</v>
+        <v>109.3218052163805</v>
       </c>
       <c r="AH138" t="n">
         <v>0.6200000000000001</v>
@@ -66942,7 +66942,7 @@
         <v>0.02856249611347313</v>
       </c>
       <c r="AM138" t="n">
-        <v>2456.186021634699</v>
+        <v>2456.186021634697</v>
       </c>
       <c r="AN138" t="n">
         <v>0</v>
@@ -66951,10 +66951,10 @@
         <v>0</v>
       </c>
       <c r="AP138" t="n">
-        <v>105.4906068113522</v>
+        <v>105.4906068113521</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.6417274537138382</v>
+        <v>0.6417274537138381</v>
       </c>
       <c r="AR138" t="n">
         <v>0</v>
@@ -66981,28 +66981,28 @@
         <v>4050.771502485696</v>
       </c>
       <c r="BA138" t="n">
-        <v>0.144174850880909</v>
+        <v>0.14417485088091</v>
       </c>
       <c r="BB138" t="n">
         <v>0</v>
       </c>
       <c r="BC138" t="n">
-        <v>6.643713853337565</v>
+        <v>6.643713853337564</v>
       </c>
       <c r="BD138" t="n">
-        <v>4642.688450905223</v>
+        <v>4642.688450905224</v>
       </c>
       <c r="BE138" t="n">
         <v>3960.46273091254</v>
       </c>
       <c r="BG138" t="n">
-        <v>2749.050365923859</v>
+        <v>2749.050365923858</v>
       </c>
       <c r="BH138" t="n">
         <v>3960.46273091254</v>
       </c>
       <c r="BI138" t="n">
-        <v>0.6941235286641476</v>
+        <v>0.6941235286641475</v>
       </c>
       <c r="BK138" t="n">
         <v>2455.486893165775</v>
@@ -67041,7 +67041,7 @@
         <v>124.3537725738417</v>
       </c>
       <c r="BX138" t="n">
-        <v>0.6627247298310656</v>
+        <v>0.6627247298310655</v>
       </c>
       <c r="BY138" t="n">
         <v>0</v>
@@ -67050,7 +67050,7 @@
         <v>0</v>
       </c>
       <c r="CA138" t="n">
-        <v>0.03139879883308206</v>
+        <v>0.03139879883308207</v>
       </c>
       <c r="CC138" t="n">
         <v>26.40323857215313</v>
@@ -67068,7 +67068,7 @@
         <v>4186.693455778783</v>
       </c>
       <c r="CH138" t="n">
-        <v>0.1422823070825398</v>
+        <v>0.1422823070825409</v>
       </c>
       <c r="CI138" t="n">
         <v>0</v>
@@ -67077,22 +67077,22 @@
         <v>6.578542056738256</v>
       </c>
       <c r="CK138" t="n">
-        <v>4799.871504790494</v>
+        <v>4799.871504790492</v>
       </c>
       <c r="CL138" t="n">
-        <v>4094.548322359509</v>
+        <v>4094.548322359507</v>
       </c>
       <c r="CN138" t="n">
         <v>2938.848414525093</v>
       </c>
       <c r="CO138" t="n">
-        <v>4094.548322359509</v>
+        <v>4094.548322359507</v>
       </c>
       <c r="CP138" t="n">
-        <v>0.7177466678013372</v>
+        <v>0.7177466678013376</v>
       </c>
       <c r="CR138" t="n">
-        <v>2538.619959862895</v>
+        <v>2538.619959862894</v>
       </c>
       <c r="CS138" t="n">
         <v>0</v>
@@ -67101,7 +67101,7 @@
         <v>0</v>
       </c>
       <c r="CU138" t="n">
-        <v>157.3999462788687</v>
+        <v>157.3999462788686</v>
       </c>
       <c r="CV138" t="n">
         <v>0.62</v>
@@ -67125,10 +67125,10 @@
         <v>0</v>
       </c>
       <c r="DD138" t="n">
-        <v>141.3206351289584</v>
+        <v>141.3206351289582</v>
       </c>
       <c r="DE138" t="n">
-        <v>0.6832323272677954</v>
+        <v>0.6832323272677958</v>
       </c>
       <c r="DF138" t="n">
         <v>0</v>
@@ -67137,7 +67137,7 @@
         <v>0</v>
       </c>
       <c r="DH138" t="n">
-        <v>0.03451434053354181</v>
+        <v>0.03451434053354178</v>
       </c>
       <c r="DJ138" t="n">
         <v>26.14237457506025</v>
@@ -67155,25 +67155,25 @@
         <v>4320.556123400509</v>
       </c>
       <c r="DO138" t="n">
-        <v>0.1400690167080312</v>
+        <v>0.1400690167080324</v>
       </c>
       <c r="DP138" t="n">
         <v>0</v>
       </c>
       <c r="DQ138" t="n">
-        <v>6.514353602398216</v>
+        <v>6.514353602398214</v>
       </c>
       <c r="DR138" t="n">
-        <v>4954.700102383527</v>
+        <v>4954.700102383526</v>
       </c>
       <c r="DS138" t="n">
-        <v>4226.625436068724</v>
+        <v>4226.625436068723</v>
       </c>
       <c r="DU138" t="n">
-        <v>3122.082252303619</v>
+        <v>3122.082252303618</v>
       </c>
       <c r="DV138" t="n">
-        <v>4226.625436068724</v>
+        <v>4226.625436068723</v>
       </c>
       <c r="DW138" t="n">
         <v>0.7386701990814535</v>
@@ -67188,7 +67188,7 @@
         <v>0</v>
       </c>
       <c r="EB138" t="n">
-        <v>179.4736236044278</v>
+        <v>179.4736236044277</v>
       </c>
       <c r="EC138" t="n">
         <v>0.6199999999999999</v>
@@ -67224,7 +67224,7 @@
         <v>0</v>
       </c>
       <c r="EO138" t="n">
-        <v>0.03681511568870904</v>
+        <v>0.03681511568870905</v>
       </c>
       <c r="EQ138" t="n">
         <v>25.88408791425866</v>
@@ -67242,28 +67242,28 @@
         <v>4458.698830621999</v>
       </c>
       <c r="EV138" t="n">
-        <v>0.1395671288787239</v>
+        <v>0.139567128878725</v>
       </c>
       <c r="EW138" t="n">
         <v>0</v>
       </c>
       <c r="EX138" t="n">
-        <v>6.449109794750752</v>
+        <v>6.449109794750751</v>
       </c>
       <c r="EY138" t="n">
         <v>5112.927393970689</v>
       </c>
       <c r="EZ138" t="n">
-        <v>4361.601818389186</v>
+        <v>4361.601818389185</v>
       </c>
       <c r="FB138" t="n">
         <v>3309.691037834486</v>
       </c>
       <c r="FC138" t="n">
-        <v>4361.601818389186</v>
+        <v>4361.601818389185</v>
       </c>
       <c r="FD138" t="n">
-        <v>0.7588246648009724</v>
+        <v>0.7588246648009725</v>
       </c>
       <c r="FF138" t="n">
         <v>2704.193127401295</v>
@@ -67275,7 +67275,7 @@
         <v>0</v>
       </c>
       <c r="FI138" t="n">
-        <v>202.5378138975754</v>
+        <v>202.5378138975753</v>
       </c>
       <c r="FJ138" t="n">
         <v>0.62</v>
@@ -67299,10 +67299,10 @@
         <v>0</v>
       </c>
       <c r="FR138" t="n">
-        <v>170.9091411940732</v>
+        <v>170.9091411940731</v>
       </c>
       <c r="FS138" t="n">
-        <v>0.7196397166304417</v>
+        <v>0.7196397166304418</v>
       </c>
       <c r="FT138" t="n">
         <v>0</v>
@@ -67311,7 +67311,7 @@
         <v>0</v>
       </c>
       <c r="FV138" t="n">
-        <v>0.03918494817053081</v>
+        <v>0.0391849481705308</v>
       </c>
     </row>
     <row r="139">
@@ -67399,7 +67399,7 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>574.7417825675874</v>
+        <v>574.7417825675873</v>
       </c>
       <c r="AB139" t="n">
         <v>0</v>
@@ -67573,7 +67573,7 @@
         <v>0</v>
       </c>
       <c r="CO139" t="n">
-        <v>576.3173667160008</v>
+        <v>576.3173667160007</v>
       </c>
       <c r="CP139" t="n">
         <v>0</v>
@@ -67886,7 +67886,7 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1698.824191382487</v>
+        <v>1698.824191382486</v>
       </c>
       <c r="AB140" t="n">
         <v>0</v>
@@ -68060,7 +68060,7 @@
         <v>0</v>
       </c>
       <c r="CO140" t="n">
-        <v>1607.549791389094</v>
+        <v>1607.549791389093</v>
       </c>
       <c r="CP140" t="n">
         <v>0</v>
@@ -68355,31 +68355,31 @@
         <v>4275.375951001142</v>
       </c>
       <c r="T141" t="n">
-        <v>0.5170209640436843</v>
+        <v>0.5170209640436881</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>5.558783636726803</v>
+        <v>5.558783636726799</v>
       </c>
       <c r="W141" t="n">
-        <v>4618.988692547426</v>
+        <v>4618.988692547422</v>
       </c>
       <c r="X141" t="n">
-        <v>3910.019420560499</v>
+        <v>3910.019420560496</v>
       </c>
       <c r="Z141" t="n">
-        <v>2721.636576652489</v>
+        <v>2721.636576652487</v>
       </c>
       <c r="AA141" t="n">
-        <v>3910.019420560499</v>
+        <v>3910.019420560496</v>
       </c>
       <c r="AB141" t="n">
         <v>0.6960672784234775</v>
       </c>
       <c r="AD141" t="n">
-        <v>2629.488060326936</v>
+        <v>2629.488060326933</v>
       </c>
       <c r="AE141" t="n">
         <v>0</v>
@@ -68403,7 +68403,7 @@
         <v>0</v>
       </c>
       <c r="AM141" t="n">
-        <v>2721.636576652489</v>
+        <v>2721.636576652487</v>
       </c>
       <c r="AN141" t="n">
         <v>0</v>
@@ -68442,31 +68442,31 @@
         <v>4396.870339338809</v>
       </c>
       <c r="BA141" t="n">
-        <v>0.5168448553313855</v>
+        <v>0.5168448553313892</v>
       </c>
       <c r="BB141" t="n">
         <v>0</v>
       </c>
       <c r="BC141" t="n">
-        <v>5.577794739701494</v>
+        <v>5.577794739701489</v>
       </c>
       <c r="BD141" t="n">
-        <v>4748.518361117589</v>
+        <v>4748.518361117585</v>
       </c>
       <c r="BE141" t="n">
-        <v>4019.667560740029</v>
+        <v>4019.667560740026</v>
       </c>
       <c r="BG141" t="n">
-        <v>2889.508078291831</v>
+        <v>2889.508078291828</v>
       </c>
       <c r="BH141" t="n">
-        <v>4019.667560740029</v>
+        <v>4019.667560740026</v>
       </c>
       <c r="BI141" t="n">
-        <v>0.7188425496957928</v>
+        <v>0.7188425496957925</v>
       </c>
       <c r="BK141" t="n">
-        <v>2703.22643459767</v>
+        <v>2703.226434597667</v>
       </c>
       <c r="BL141" t="n">
         <v>0</v>
@@ -68490,7 +68490,7 @@
         <v>0</v>
       </c>
       <c r="BT141" t="n">
-        <v>2889.508078291831</v>
+        <v>2889.508078291828</v>
       </c>
       <c r="BU141" t="n">
         <v>0</v>
@@ -68502,7 +68502,7 @@
         <v>0</v>
       </c>
       <c r="BX141" t="n">
-        <v>0.7188425496957928</v>
+        <v>0.7188425496957925</v>
       </c>
       <c r="BY141" t="n">
         <v>0</v>
@@ -68529,31 +68529,31 @@
         <v>4498.771717391343</v>
       </c>
       <c r="CH141" t="n">
-        <v>0.5153973289965154</v>
+        <v>0.5153973289965194</v>
       </c>
       <c r="CI141" t="n">
         <v>0</v>
       </c>
       <c r="CJ141" t="n">
-        <v>5.582167693041978</v>
+        <v>5.582167693041974</v>
       </c>
       <c r="CK141" t="n">
-        <v>4861.117373576977</v>
+        <v>4861.117373576973</v>
       </c>
       <c r="CL141" t="n">
-        <v>4114.983733772125</v>
+        <v>4114.98373377212</v>
       </c>
       <c r="CN141" t="n">
-        <v>3049.559623477232</v>
+        <v>3049.55962347723</v>
       </c>
       <c r="CO141" t="n">
-        <v>4114.983733772125</v>
+        <v>4114.98373377212</v>
       </c>
       <c r="CP141" t="n">
-        <v>0.7410866775606331</v>
+        <v>0.7410866775606333</v>
       </c>
       <c r="CR141" t="n">
-        <v>2767.326560961754</v>
+        <v>2767.326560961751</v>
       </c>
       <c r="CS141" t="n">
         <v>0</v>
@@ -68577,7 +68577,7 @@
         <v>0</v>
       </c>
       <c r="DA141" t="n">
-        <v>3049.559623477232</v>
+        <v>3049.55962347723</v>
       </c>
       <c r="DB141" t="n">
         <v>0</v>
@@ -68589,7 +68589,7 @@
         <v>0</v>
       </c>
       <c r="DE141" t="n">
-        <v>0.7410866775606331</v>
+        <v>0.7410866775606333</v>
       </c>
       <c r="DF141" t="n">
         <v>0</v>
@@ -68616,31 +68616,31 @@
         <v>4569.751673092784</v>
       </c>
       <c r="DO141" t="n">
-        <v>0.510792870796784</v>
+        <v>0.5107928707967881</v>
       </c>
       <c r="DP141" t="n">
         <v>0</v>
       </c>
       <c r="DQ141" t="n">
-        <v>5.567137991870746</v>
+        <v>5.567137991870743</v>
       </c>
       <c r="DR141" t="n">
-        <v>4941.172068537249</v>
+        <v>4941.172068537246</v>
       </c>
       <c r="DS141" t="n">
-        <v>4182.750821512942</v>
+        <v>4182.75082151294</v>
       </c>
       <c r="DU141" t="n">
-        <v>3184.271150271152</v>
+        <v>3184.271150271151</v>
       </c>
       <c r="DV141" t="n">
-        <v>4182.750821512942</v>
+        <v>4182.75082151294</v>
       </c>
       <c r="DW141" t="n">
         <v>0.7612863606155171</v>
       </c>
       <c r="DY141" t="n">
-        <v>2812.899927467453</v>
+        <v>2812.899927467452</v>
       </c>
       <c r="DZ141" t="n">
         <v>0</v>
@@ -68664,7 +68664,7 @@
         <v>0</v>
       </c>
       <c r="EH141" t="n">
-        <v>3184.271150271152</v>
+        <v>3184.271150271151</v>
       </c>
       <c r="EI141" t="n">
         <v>0</v>
@@ -68703,31 +68703,31 @@
         <v>4641.851524274116</v>
       </c>
       <c r="EV141" t="n">
-        <v>0.5123861404431139</v>
+        <v>0.5123861404431179</v>
       </c>
       <c r="EW141" t="n">
         <v>0</v>
       </c>
       <c r="EX141" t="n">
-        <v>5.545973784846625</v>
+        <v>5.545973784846622</v>
       </c>
       <c r="EY141" t="n">
-        <v>5016.701830481367</v>
+        <v>5016.701830481365</v>
       </c>
       <c r="EZ141" t="n">
-        <v>4246.68750888962</v>
+        <v>4246.687508889618</v>
       </c>
       <c r="FB141" t="n">
-        <v>3314.866386264648</v>
+        <v>3314.866386264646</v>
       </c>
       <c r="FC141" t="n">
-        <v>4246.68750888962</v>
+        <v>4246.687508889618</v>
       </c>
       <c r="FD141" t="n">
-        <v>0.7805769506999549</v>
+        <v>0.780576950699955</v>
       </c>
       <c r="FF141" t="n">
-        <v>2855.89734972827</v>
+        <v>2855.897349728268</v>
       </c>
       <c r="FG141" t="n">
         <v>0</v>
@@ -68751,7 +68751,7 @@
         <v>0</v>
       </c>
       <c r="FO141" t="n">
-        <v>3314.866386264648</v>
+        <v>3314.866386264646</v>
       </c>
       <c r="FP141" t="n">
         <v>0</v>
@@ -68763,7 +68763,7 @@
         <v>0</v>
       </c>
       <c r="FS141" t="n">
-        <v>0.7805769506999549</v>
+        <v>0.780576950699955</v>
       </c>
       <c r="FT141" t="n">
         <v>0</v>
@@ -68851,19 +68851,19 @@
         <v>3.037902300385244</v>
       </c>
       <c r="W142" t="n">
-        <v>4439.631229236336</v>
+        <v>4439.631229236335</v>
       </c>
       <c r="X142" t="n">
-        <v>3762.481442083357</v>
+        <v>3762.481442083356</v>
       </c>
       <c r="Z142" t="n">
         <v>2618.940217509803</v>
       </c>
       <c r="AA142" t="n">
-        <v>3762.481442083357</v>
+        <v>3762.481442083356</v>
       </c>
       <c r="AB142" t="n">
-        <v>0.6960672784234774</v>
+        <v>0.6960672784234775</v>
       </c>
       <c r="AD142" t="n">
         <v>2530.268769801057</v>
@@ -68902,7 +68902,7 @@
         <v>0</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6960672784234774</v>
+        <v>0.6960672784234775</v>
       </c>
       <c r="AR142" t="n">
         <v>0</v>
@@ -68938,19 +68938,19 @@
         <v>3.047319797516439</v>
       </c>
       <c r="BD142" t="n">
-        <v>4586.120065825891</v>
+        <v>4586.120065825892</v>
       </c>
       <c r="BE142" t="n">
-        <v>3886.627232731692</v>
+        <v>3886.627232731693</v>
       </c>
       <c r="BG142" t="n">
         <v>2793.873029693953</v>
       </c>
       <c r="BH142" t="n">
-        <v>3886.627232731692</v>
+        <v>3886.627232731693</v>
       </c>
       <c r="BI142" t="n">
-        <v>0.7188425496957928</v>
+        <v>0.7188425496957926</v>
       </c>
       <c r="BK142" t="n">
         <v>2613.756814012063</v>
@@ -68989,7 +68989,7 @@
         <v>0</v>
       </c>
       <c r="BX142" t="n">
-        <v>0.7188425496957928</v>
+        <v>0.7188425496957926</v>
       </c>
       <c r="BY142" t="n">
         <v>0</v>
@@ -69025,19 +69025,19 @@
         <v>3.048782511019247</v>
       </c>
       <c r="CK142" t="n">
-        <v>4720.748658389733</v>
+        <v>4720.748658389732</v>
       </c>
       <c r="CL142" t="n">
-        <v>4000.721749807693</v>
+        <v>4000.721749807692</v>
       </c>
       <c r="CN142" t="n">
         <v>2964.881589409545</v>
       </c>
       <c r="CO142" t="n">
-        <v>4000.721749807693</v>
+        <v>4000.721749807692</v>
       </c>
       <c r="CP142" t="n">
-        <v>0.7410866775606328</v>
+        <v>0.7410866775606332</v>
       </c>
       <c r="CR142" t="n">
         <v>2690.485376745673</v>
@@ -69076,7 +69076,7 @@
         <v>0</v>
       </c>
       <c r="DE142" t="n">
-        <v>0.7410866775606328</v>
+        <v>0.7410866775606332</v>
       </c>
       <c r="DF142" t="n">
         <v>0</v>
@@ -69205,13 +69205,13 @@
         <v>4188.883856978593</v>
       </c>
       <c r="FB142" t="n">
-        <v>3269.746187916617</v>
+        <v>3269.746187916618</v>
       </c>
       <c r="FC142" t="n">
         <v>4188.883856978593</v>
       </c>
       <c r="FD142" t="n">
-        <v>0.780576950699955</v>
+        <v>0.7805769506999553</v>
       </c>
       <c r="FF142" t="n">
         <v>2817.024393818105</v>
@@ -69238,7 +69238,7 @@
         <v>0</v>
       </c>
       <c r="FO142" t="n">
-        <v>3269.746187916617</v>
+        <v>3269.746187916618</v>
       </c>
       <c r="FP142" t="n">
         <v>0</v>
@@ -69250,7 +69250,7 @@
         <v>0</v>
       </c>
       <c r="FS142" t="n">
-        <v>0.780576950699955</v>
+        <v>0.7805769506999553</v>
       </c>
       <c r="FT142" t="n">
         <v>0</v>
@@ -69347,7 +69347,7 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>337.4515584748557</v>
+        <v>337.4515584748556</v>
       </c>
       <c r="AB143" t="n">
         <v>0</v>
@@ -69434,7 +69434,7 @@
         <v>0</v>
       </c>
       <c r="BH143" t="n">
-        <v>360.8181621088822</v>
+        <v>360.8181621088823</v>
       </c>
       <c r="BI143" t="n">
         <v>0</v>
@@ -69521,7 +69521,7 @@
         <v>0</v>
       </c>
       <c r="CO143" t="n">
-        <v>386.3506888816566</v>
+        <v>386.3506888816565</v>
       </c>
       <c r="CP143" t="n">
         <v>0</v>
@@ -69834,7 +69834,7 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>3615.658201697222</v>
+        <v>3615.658201697221</v>
       </c>
       <c r="AB144" t="n">
         <v>0</v>
@@ -70008,7 +70008,7 @@
         <v>0</v>
       </c>
       <c r="CO144" t="n">
-        <v>4139.556715141661</v>
+        <v>4139.556715141659</v>
       </c>
       <c r="CP144" t="n">
         <v>0</v>
@@ -70303,7 +70303,7 @@
         <v>1158.764451014064</v>
       </c>
       <c r="T145" t="n">
-        <v>0.0005541993444951023</v>
+        <v>0.0005541993444951064</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -70327,7 +70327,7 @@
         <v>0.2898123984514108</v>
       </c>
       <c r="AD145" t="n">
-        <v>324.163102323521</v>
+        <v>324.1631023235209</v>
       </c>
       <c r="AE145" t="n">
         <v>0</v>
@@ -70390,7 +70390,7 @@
         <v>1234.319819670348</v>
       </c>
       <c r="BA145" t="n">
-        <v>0.0005777483592531532</v>
+        <v>0.0005777483592531573</v>
       </c>
       <c r="BB145" t="n">
         <v>0</v>
@@ -70405,13 +70405,13 @@
         <v>1232.373023137166</v>
       </c>
       <c r="BG145" t="n">
-        <v>368.8431323656582</v>
+        <v>368.8431323656581</v>
       </c>
       <c r="BH145" t="n">
         <v>1232.373023137166</v>
       </c>
       <c r="BI145" t="n">
-        <v>0.2992950392785458</v>
+        <v>0.2992950392785457</v>
       </c>
       <c r="BK145" t="n">
         <v>345.0644464784065</v>
@@ -70438,7 +70438,7 @@
         <v>0</v>
       </c>
       <c r="BT145" t="n">
-        <v>368.8431323656582</v>
+        <v>368.8431323656581</v>
       </c>
       <c r="BU145" t="n">
         <v>0</v>
@@ -70450,7 +70450,7 @@
         <v>0</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.2992950392785458</v>
+        <v>0.2992950392785457</v>
       </c>
       <c r="BY145" t="n">
         <v>0</v>
@@ -70477,7 +70477,7 @@
         <v>1317.868247913658</v>
       </c>
       <c r="CH145" t="n">
-        <v>0.0006023891961929676</v>
+        <v>0.0006023891961929723</v>
       </c>
       <c r="CI145" t="n">
         <v>0</v>
@@ -70498,10 +70498,10 @@
         <v>1316.081963689343</v>
       </c>
       <c r="CP145" t="n">
-        <v>0.3085565348951335</v>
+        <v>0.3085565348951336</v>
       </c>
       <c r="CR145" t="n">
-        <v>368.5029498330161</v>
+        <v>368.502949833016</v>
       </c>
       <c r="CS145" t="n">
         <v>0</v>
@@ -70537,7 +70537,7 @@
         <v>0</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.3085565348951335</v>
+        <v>0.3085565348951336</v>
       </c>
       <c r="DF145" t="n">
         <v>0</v>
@@ -70564,7 +70564,7 @@
         <v>1413.853199676605</v>
       </c>
       <c r="DO145" t="n">
-        <v>0.0006265351216975992</v>
+        <v>0.0006265351216976043</v>
       </c>
       <c r="DP145" t="n">
         <v>0</v>
@@ -70651,7 +70651,7 @@
         <v>1516.829071039838</v>
       </c>
       <c r="EV145" t="n">
-        <v>0.0006595740362655187</v>
+        <v>0.0006595740362655239</v>
       </c>
       <c r="EW145" t="n">
         <v>0</v>
@@ -70672,7 +70672,7 @@
         <v>1515.151461539388</v>
       </c>
       <c r="FD145" t="n">
-        <v>0.3249985817040704</v>
+        <v>0.3249985817040705</v>
       </c>
       <c r="FF145" t="n">
         <v>424.2424092310285</v>
@@ -70711,7 +70711,7 @@
         <v>0</v>
       </c>
       <c r="FS145" t="n">
-        <v>0.3249985817040704</v>
+        <v>0.3249985817040705</v>
       </c>
       <c r="FT145" t="n">
         <v>0</v>
@@ -70895,7 +70895,7 @@
         <v>0</v>
       </c>
       <c r="BH146" t="n">
-        <v>1654.342253243208</v>
+        <v>1654.342253243209</v>
       </c>
       <c r="BI146" t="n">
         <v>0</v>
@@ -70982,7 +70982,7 @@
         <v>0</v>
       </c>
       <c r="CO146" t="n">
-        <v>1719.237724206011</v>
+        <v>1719.23772420601</v>
       </c>
       <c r="CP146" t="n">
         <v>0</v>
@@ -71469,7 +71469,7 @@
         <v>0</v>
       </c>
       <c r="CO147" t="n">
-        <v>21581.97326553029</v>
+        <v>21581.97326553028</v>
       </c>
       <c r="CP147" t="n">
         <v>0</v>
@@ -72269,7 +72269,7 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>4982.732591152118</v>
+        <v>4982.732591152117</v>
       </c>
       <c r="AB149" t="n">
         <v>0</v>
@@ -72443,7 +72443,7 @@
         <v>0</v>
       </c>
       <c r="CO149" t="n">
-        <v>5988.223452463469</v>
+        <v>5988.223452463466</v>
       </c>
       <c r="CP149" t="n">
         <v>0</v>
@@ -72756,7 +72756,7 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>3875.564691474047</v>
+        <v>3875.564691474046</v>
       </c>
       <c r="AB150" t="n">
         <v>0</v>
@@ -72930,7 +72930,7 @@
         <v>0</v>
       </c>
       <c r="CO150" t="n">
-        <v>3977.966968936626</v>
+        <v>3977.966968936625</v>
       </c>
       <c r="CP150" t="n">
         <v>0</v>
@@ -73243,7 +73243,7 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>657.7433366041547</v>
+        <v>657.7433366041546</v>
       </c>
       <c r="AB151" t="n">
         <v>0</v>
@@ -73330,7 +73330,7 @@
         <v>0</v>
       </c>
       <c r="BH151" t="n">
-        <v>667.1552362142934</v>
+        <v>667.1552362142935</v>
       </c>
       <c r="BI151" t="n">
         <v>0</v>
@@ -73417,7 +73417,7 @@
         <v>0</v>
       </c>
       <c r="CO151" t="n">
-        <v>675.1225886657384</v>
+        <v>675.1225886657381</v>
       </c>
       <c r="CP151" t="n">
         <v>0</v>
@@ -73724,13 +73724,13 @@
         <v>195.9338584934744</v>
       </c>
       <c r="X152" t="n">
-        <v>163.2782154112287</v>
+        <v>163.2782154112286</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>163.2782154112287</v>
+        <v>163.2782154112286</v>
       </c>
       <c r="AB152" t="n">
         <v>0</v>
@@ -73895,7 +73895,7 @@
         <v>1.434355544114585</v>
       </c>
       <c r="CK152" t="n">
-        <v>184.3705586980532</v>
+        <v>184.3705586980531</v>
       </c>
       <c r="CL152" t="n">
         <v>153.6421322483776</v>
